--- a/data/raw_results/lanupro_vocabulary_general.xlsx
+++ b/data/raw_results/lanupro_vocabulary_general.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1EB191B-38BE-4145-9DCB-50B4F5C72D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33F07B7-02CF-498E-A83D-6C065FDF983B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="277">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -867,6 +867,9 @@
   </si>
   <si>
     <t>sample_form</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -2192,7 +2195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB33DE6-D058-433F-9B7D-5598CD0261F2}">
-  <dimension ref="A1:AB106"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17" style="4" customWidth="1"/>
@@ -2209,7 +2212,7 @@
     <col min="28" max="28" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1">
+    <row r="1" spans="1:29" s="1" customFormat="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2294,8 +2297,11 @@
       <c r="AB1" s="6" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="2" spans="1:28">
+      <c r="AC1" s="6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" s="5" t="s">
         <v>129</v>
       </c>
@@ -2381,7 +2387,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:29">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -2437,7 +2443,7 @@
       <c r="AA3" s="8"/>
       <c r="AB3" s="8"/>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:29">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
@@ -2493,7 +2499,7 @@
       <c r="AA4" s="8"/>
       <c r="AB4" s="8"/>
     </row>
-    <row r="5" spans="1:28" ht="86.4">
+    <row r="5" spans="1:29" ht="86.4">
       <c r="A5" s="9" t="s">
         <v>6</v>
       </c>
@@ -2553,7 +2559,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:29">
       <c r="A6" s="5" t="s">
         <v>115</v>
       </c>
@@ -2603,7 +2609,7 @@
       <c r="AA6" s="8"/>
       <c r="AB6" s="8"/>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:29">
       <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
@@ -2647,7 +2653,7 @@
       <c r="AA7" s="8"/>
       <c r="AB7" s="8"/>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:29">
       <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
@@ -2691,7 +2697,7 @@
       <c r="AA8" s="8"/>
       <c r="AB8" s="8"/>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:29">
       <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
@@ -2735,7 +2741,7 @@
       <c r="AA9" s="8"/>
       <c r="AB9" s="8"/>
     </row>
-    <row r="10" spans="1:28">
+    <row r="10" spans="1:29">
       <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
@@ -2779,7 +2785,7 @@
       <c r="AA10" s="8"/>
       <c r="AB10" s="8"/>
     </row>
-    <row r="11" spans="1:28">
+    <row r="11" spans="1:29">
       <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
@@ -2821,7 +2827,7 @@
       <c r="AA11" s="8"/>
       <c r="AB11" s="8"/>
     </row>
-    <row r="12" spans="1:28">
+    <row r="12" spans="1:29">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
@@ -2863,7 +2869,7 @@
       <c r="AA12" s="8"/>
       <c r="AB12" s="8"/>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" spans="1:29">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -2903,7 +2909,7 @@
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
     </row>
-    <row r="14" spans="1:28">
+    <row r="14" spans="1:29">
       <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
@@ -2943,7 +2949,7 @@
       <c r="AA14" s="8"/>
       <c r="AB14" s="8"/>
     </row>
-    <row r="15" spans="1:28">
+    <row r="15" spans="1:29">
       <c r="A15" s="5" t="s">
         <v>18</v>
       </c>
@@ -2983,7 +2989,7 @@
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
     </row>
-    <row r="16" spans="1:28">
+    <row r="16" spans="1:29">
       <c r="A16" s="5" t="s">
         <v>19</v>
       </c>

--- a/data/raw_results/lanupro_vocabulary_general.xlsx
+++ b/data/raw_results/lanupro_vocabulary_general.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33F07B7-02CF-498E-A83D-6C065FDF983B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3258A069-DD77-4EDB-A287-170E060B084E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="278">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -870,6 +870,9 @@
   </si>
   <si>
     <t>test</t>
+  </si>
+  <si>
+    <t>test_field</t>
   </si>
 </sst>
 </file>
@@ -2386,6 +2389,9 @@
       <c r="AB2" s="8" t="s">
         <v>117</v>
       </c>
+      <c r="AC2" s="8" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="3" spans="1:29">
       <c r="A3" s="5" t="s">
@@ -2442,6 +2448,7 @@
       <c r="Z3" s="8"/>
       <c r="AA3" s="8"/>
       <c r="AB3" s="8"/>
+      <c r="AC3" s="8"/>
     </row>
     <row r="4" spans="1:29">
       <c r="A4" s="5" t="s">
@@ -2498,6 +2505,7 @@
       <c r="Z4" s="8"/>
       <c r="AA4" s="8"/>
       <c r="AB4" s="8"/>
+      <c r="AC4" s="8"/>
     </row>
     <row r="5" spans="1:29" ht="86.4">
       <c r="A5" s="9" t="s">
@@ -2557,6 +2565,9 @@
       <c r="AA5" s="10"/>
       <c r="AB5" s="10" t="s">
         <v>265</v>
+      </c>
+      <c r="AC5" s="8" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -2608,6 +2619,7 @@
       <c r="Z6" s="8"/>
       <c r="AA6" s="8"/>
       <c r="AB6" s="8"/>
+      <c r="AC6" s="8"/>
     </row>
     <row r="7" spans="1:29">
       <c r="A7" s="5" t="s">
@@ -2652,6 +2664,7 @@
       <c r="Z7" s="8"/>
       <c r="AA7" s="8"/>
       <c r="AB7" s="8"/>
+      <c r="AC7" s="8"/>
     </row>
     <row r="8" spans="1:29">
       <c r="A8" s="5" t="s">
@@ -2696,6 +2709,7 @@
       <c r="Z8" s="8"/>
       <c r="AA8" s="8"/>
       <c r="AB8" s="8"/>
+      <c r="AC8" s="8"/>
     </row>
     <row r="9" spans="1:29">
       <c r="A9" s="5" t="s">
@@ -2740,6 +2754,7 @@
       <c r="Z9" s="8"/>
       <c r="AA9" s="8"/>
       <c r="AB9" s="8"/>
+      <c r="AC9" s="8"/>
     </row>
     <row r="10" spans="1:29">
       <c r="A10" s="5" t="s">
@@ -2784,6 +2799,7 @@
       <c r="Z10" s="8"/>
       <c r="AA10" s="8"/>
       <c r="AB10" s="8"/>
+      <c r="AC10" s="8"/>
     </row>
     <row r="11" spans="1:29">
       <c r="A11" s="5" t="s">
@@ -2826,6 +2842,7 @@
       <c r="Z11" s="8"/>
       <c r="AA11" s="8"/>
       <c r="AB11" s="8"/>
+      <c r="AC11" s="8"/>
     </row>
     <row r="12" spans="1:29">
       <c r="A12" s="5" t="s">
@@ -2868,6 +2885,7 @@
       <c r="Z12" s="8"/>
       <c r="AA12" s="8"/>
       <c r="AB12" s="8"/>
+      <c r="AC12" s="8"/>
     </row>
     <row r="13" spans="1:29">
       <c r="A13" s="5" t="s">
@@ -2908,6 +2926,7 @@
       <c r="Z13" s="8"/>
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
+      <c r="AC13" s="8"/>
     </row>
     <row r="14" spans="1:29">
       <c r="A14" s="5" t="s">
@@ -2948,6 +2967,7 @@
       <c r="Z14" s="8"/>
       <c r="AA14" s="8"/>
       <c r="AB14" s="8"/>
+      <c r="AC14" s="8"/>
     </row>
     <row r="15" spans="1:29">
       <c r="A15" s="5" t="s">
@@ -2988,6 +3008,7 @@
       <c r="Z15" s="8"/>
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
+      <c r="AC15" s="8"/>
     </row>
     <row r="16" spans="1:29">
       <c r="A16" s="5" t="s">
@@ -3028,8 +3049,9 @@
       <c r="Z16" s="8"/>
       <c r="AA16" s="8"/>
       <c r="AB16" s="8"/>
-    </row>
-    <row r="17" spans="1:28">
+      <c r="AC16" s="8"/>
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
@@ -3068,8 +3090,9 @@
       <c r="Z17" s="8"/>
       <c r="AA17" s="8"/>
       <c r="AB17" s="8"/>
-    </row>
-    <row r="18" spans="1:28">
+      <c r="AC17" s="8"/>
+    </row>
+    <row r="18" spans="1:29">
       <c r="A18" s="5" t="s">
         <v>21</v>
       </c>
@@ -3106,8 +3129,9 @@
       <c r="Z18" s="8"/>
       <c r="AA18" s="8"/>
       <c r="AB18" s="8"/>
-    </row>
-    <row r="19" spans="1:28">
+      <c r="AC18" s="8"/>
+    </row>
+    <row r="19" spans="1:29">
       <c r="A19" s="5" t="s">
         <v>22</v>
       </c>
@@ -3144,8 +3168,9 @@
       <c r="Z19" s="8"/>
       <c r="AA19" s="8"/>
       <c r="AB19" s="8"/>
-    </row>
-    <row r="20" spans="1:28">
+      <c r="AC19" s="8"/>
+    </row>
+    <row r="20" spans="1:29">
       <c r="A20" s="5" t="s">
         <v>23</v>
       </c>
@@ -3182,8 +3207,9 @@
       <c r="Z20" s="8"/>
       <c r="AA20" s="8"/>
       <c r="AB20" s="8"/>
-    </row>
-    <row r="21" spans="1:28">
+      <c r="AC20" s="8"/>
+    </row>
+    <row r="21" spans="1:29">
       <c r="A21" s="5" t="s">
         <v>24</v>
       </c>
@@ -3218,8 +3244,9 @@
       <c r="Z21" s="8"/>
       <c r="AA21" s="8"/>
       <c r="AB21" s="8"/>
-    </row>
-    <row r="22" spans="1:28">
+      <c r="AC21" s="8"/>
+    </row>
+    <row r="22" spans="1:29">
       <c r="A22" s="5" t="s">
         <v>25</v>
       </c>
@@ -3254,8 +3281,9 @@
       <c r="Z22" s="8"/>
       <c r="AA22" s="8"/>
       <c r="AB22" s="8"/>
-    </row>
-    <row r="23" spans="1:28">
+      <c r="AC22" s="8"/>
+    </row>
+    <row r="23" spans="1:29">
       <c r="A23" s="5" t="s">
         <v>26</v>
       </c>
@@ -3290,8 +3318,9 @@
       <c r="Z23" s="8"/>
       <c r="AA23" s="8"/>
       <c r="AB23" s="8"/>
-    </row>
-    <row r="24" spans="1:28">
+      <c r="AC23" s="8"/>
+    </row>
+    <row r="24" spans="1:29">
       <c r="A24" s="5" t="s">
         <v>27</v>
       </c>
@@ -3326,8 +3355,9 @@
       <c r="Z24" s="8"/>
       <c r="AA24" s="8"/>
       <c r="AB24" s="8"/>
-    </row>
-    <row r="25" spans="1:28">
+      <c r="AC24" s="8"/>
+    </row>
+    <row r="25" spans="1:29">
       <c r="A25" s="5" t="s">
         <v>28</v>
       </c>
@@ -3362,8 +3392,9 @@
       <c r="Z25" s="8"/>
       <c r="AA25" s="8"/>
       <c r="AB25" s="8"/>
-    </row>
-    <row r="26" spans="1:28">
+      <c r="AC25" s="8"/>
+    </row>
+    <row r="26" spans="1:29">
       <c r="A26" s="5" t="s">
         <v>29</v>
       </c>
@@ -3398,8 +3429,9 @@
       <c r="Z26" s="8"/>
       <c r="AA26" s="8"/>
       <c r="AB26" s="8"/>
-    </row>
-    <row r="27" spans="1:28">
+      <c r="AC26" s="8"/>
+    </row>
+    <row r="27" spans="1:29">
       <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
@@ -3434,8 +3466,9 @@
       <c r="Z27" s="8"/>
       <c r="AA27" s="8"/>
       <c r="AB27" s="8"/>
-    </row>
-    <row r="28" spans="1:28">
+      <c r="AC27" s="8"/>
+    </row>
+    <row r="28" spans="1:29">
       <c r="A28" s="5" t="s">
         <v>31</v>
       </c>
@@ -3470,8 +3503,9 @@
       <c r="Z28" s="8"/>
       <c r="AA28" s="8"/>
       <c r="AB28" s="8"/>
-    </row>
-    <row r="29" spans="1:28">
+      <c r="AC28" s="8"/>
+    </row>
+    <row r="29" spans="1:29">
       <c r="A29" s="5" t="s">
         <v>32</v>
       </c>
@@ -3506,8 +3540,9 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8"/>
-    </row>
-    <row r="30" spans="1:28">
+      <c r="AC29" s="8"/>
+    </row>
+    <row r="30" spans="1:29">
       <c r="A30" s="5" t="s">
         <v>33</v>
       </c>
@@ -3542,8 +3577,9 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8"/>
-    </row>
-    <row r="31" spans="1:28">
+      <c r="AC30" s="8"/>
+    </row>
+    <row r="31" spans="1:29">
       <c r="A31" s="5" t="s">
         <v>34</v>
       </c>
@@ -3578,8 +3614,9 @@
       <c r="Z31" s="8"/>
       <c r="AA31" s="8"/>
       <c r="AB31" s="8"/>
-    </row>
-    <row r="32" spans="1:28">
+      <c r="AC31" s="8"/>
+    </row>
+    <row r="32" spans="1:29">
       <c r="A32" s="5" t="s">
         <v>35</v>
       </c>
@@ -3614,8 +3651,9 @@
       <c r="Z32" s="8"/>
       <c r="AA32" s="8"/>
       <c r="AB32" s="8"/>
-    </row>
-    <row r="33" spans="1:28">
+      <c r="AC32" s="8"/>
+    </row>
+    <row r="33" spans="1:29">
       <c r="A33" s="5" t="s">
         <v>36</v>
       </c>
@@ -3650,8 +3688,9 @@
       <c r="Z33" s="8"/>
       <c r="AA33" s="8"/>
       <c r="AB33" s="8"/>
-    </row>
-    <row r="34" spans="1:28">
+      <c r="AC33" s="8"/>
+    </row>
+    <row r="34" spans="1:29">
       <c r="A34" s="5" t="s">
         <v>37</v>
       </c>
@@ -3686,8 +3725,9 @@
       <c r="Z34" s="8"/>
       <c r="AA34" s="8"/>
       <c r="AB34" s="8"/>
-    </row>
-    <row r="35" spans="1:28">
+      <c r="AC34" s="8"/>
+    </row>
+    <row r="35" spans="1:29">
       <c r="A35" s="5" t="s">
         <v>38</v>
       </c>
@@ -3722,8 +3762,9 @@
       <c r="Z35" s="8"/>
       <c r="AA35" s="8"/>
       <c r="AB35" s="8"/>
-    </row>
-    <row r="36" spans="1:28">
+      <c r="AC35" s="8"/>
+    </row>
+    <row r="36" spans="1:29">
       <c r="A36" s="5" t="s">
         <v>39</v>
       </c>
@@ -3756,8 +3797,9 @@
       <c r="Z36" s="8"/>
       <c r="AA36" s="8"/>
       <c r="AB36" s="8"/>
-    </row>
-    <row r="37" spans="1:28">
+      <c r="AC36" s="8"/>
+    </row>
+    <row r="37" spans="1:29">
       <c r="A37" s="5" t="s">
         <v>40</v>
       </c>
@@ -3790,8 +3832,9 @@
       <c r="Z37" s="8"/>
       <c r="AA37" s="8"/>
       <c r="AB37" s="8"/>
-    </row>
-    <row r="38" spans="1:28">
+      <c r="AC37" s="8"/>
+    </row>
+    <row r="38" spans="1:29">
       <c r="A38" s="5" t="s">
         <v>41</v>
       </c>
@@ -3824,8 +3867,9 @@
       <c r="Z38" s="8"/>
       <c r="AA38" s="8"/>
       <c r="AB38" s="8"/>
-    </row>
-    <row r="39" spans="1:28">
+      <c r="AC38" s="8"/>
+    </row>
+    <row r="39" spans="1:29">
       <c r="A39" s="5" t="s">
         <v>42</v>
       </c>
@@ -3858,8 +3902,9 @@
       <c r="Z39" s="8"/>
       <c r="AA39" s="8"/>
       <c r="AB39" s="8"/>
-    </row>
-    <row r="40" spans="1:28">
+      <c r="AC39" s="8"/>
+    </row>
+    <row r="40" spans="1:29">
       <c r="A40" s="5" t="s">
         <v>43</v>
       </c>
@@ -3892,8 +3937,9 @@
       <c r="Z40" s="8"/>
       <c r="AA40" s="8"/>
       <c r="AB40" s="8"/>
-    </row>
-    <row r="41" spans="1:28">
+      <c r="AC40" s="8"/>
+    </row>
+    <row r="41" spans="1:29">
       <c r="A41" s="5" t="s">
         <v>44</v>
       </c>
@@ -3926,8 +3972,9 @@
       <c r="Z41" s="8"/>
       <c r="AA41" s="8"/>
       <c r="AB41" s="8"/>
-    </row>
-    <row r="42" spans="1:28">
+      <c r="AC41" s="8"/>
+    </row>
+    <row r="42" spans="1:29">
       <c r="A42" s="5" t="s">
         <v>45</v>
       </c>
@@ -3960,8 +4007,9 @@
       <c r="Z42" s="8"/>
       <c r="AA42" s="8"/>
       <c r="AB42" s="8"/>
-    </row>
-    <row r="43" spans="1:28">
+      <c r="AC42" s="8"/>
+    </row>
+    <row r="43" spans="1:29">
       <c r="A43" s="5" t="s">
         <v>46</v>
       </c>
@@ -3994,8 +4042,9 @@
       <c r="Z43" s="8"/>
       <c r="AA43" s="8"/>
       <c r="AB43" s="8"/>
-    </row>
-    <row r="44" spans="1:28">
+      <c r="AC43" s="8"/>
+    </row>
+    <row r="44" spans="1:29">
       <c r="A44" s="5" t="s">
         <v>47</v>
       </c>
@@ -4026,8 +4075,9 @@
       <c r="Z44" s="8"/>
       <c r="AA44" s="8"/>
       <c r="AB44" s="8"/>
-    </row>
-    <row r="45" spans="1:28">
+      <c r="AC44" s="8"/>
+    </row>
+    <row r="45" spans="1:29">
       <c r="A45" s="5" t="s">
         <v>48</v>
       </c>
@@ -4058,8 +4108,9 @@
       <c r="Z45" s="8"/>
       <c r="AA45" s="8"/>
       <c r="AB45" s="8"/>
-    </row>
-    <row r="46" spans="1:28">
+      <c r="AC45" s="8"/>
+    </row>
+    <row r="46" spans="1:29">
       <c r="A46" s="5" t="s">
         <v>49</v>
       </c>
@@ -4090,8 +4141,9 @@
       <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
       <c r="AB46" s="8"/>
-    </row>
-    <row r="47" spans="1:28">
+      <c r="AC46" s="8"/>
+    </row>
+    <row r="47" spans="1:29">
       <c r="A47" s="5" t="s">
         <v>50</v>
       </c>
@@ -4122,8 +4174,9 @@
       <c r="Z47" s="8"/>
       <c r="AA47" s="8"/>
       <c r="AB47" s="8"/>
-    </row>
-    <row r="48" spans="1:28">
+      <c r="AC47" s="8"/>
+    </row>
+    <row r="48" spans="1:29">
       <c r="A48" s="5" t="s">
         <v>51</v>
       </c>
@@ -4154,8 +4207,9 @@
       <c r="Z48" s="8"/>
       <c r="AA48" s="8"/>
       <c r="AB48" s="8"/>
-    </row>
-    <row r="49" spans="1:28">
+      <c r="AC48" s="8"/>
+    </row>
+    <row r="49" spans="1:29">
       <c r="A49" s="5" t="s">
         <v>52</v>
       </c>
@@ -4186,8 +4240,9 @@
       <c r="Z49" s="8"/>
       <c r="AA49" s="8"/>
       <c r="AB49" s="8"/>
-    </row>
-    <row r="50" spans="1:28">
+      <c r="AC49" s="8"/>
+    </row>
+    <row r="50" spans="1:29">
       <c r="A50" s="5" t="s">
         <v>53</v>
       </c>
@@ -4218,8 +4273,9 @@
       <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
       <c r="AB50" s="8"/>
-    </row>
-    <row r="51" spans="1:28">
+      <c r="AC50" s="8"/>
+    </row>
+    <row r="51" spans="1:29">
       <c r="A51" s="5" t="s">
         <v>54</v>
       </c>
@@ -4250,8 +4306,9 @@
       <c r="Z51" s="8"/>
       <c r="AA51" s="8"/>
       <c r="AB51" s="8"/>
-    </row>
-    <row r="52" spans="1:28">
+      <c r="AC51" s="8"/>
+    </row>
+    <row r="52" spans="1:29">
       <c r="A52" s="5" t="s">
         <v>55</v>
       </c>
@@ -4282,8 +4339,9 @@
       <c r="Z52" s="8"/>
       <c r="AA52" s="8"/>
       <c r="AB52" s="8"/>
-    </row>
-    <row r="53" spans="1:28">
+      <c r="AC52" s="8"/>
+    </row>
+    <row r="53" spans="1:29">
       <c r="A53" s="5" t="s">
         <v>56</v>
       </c>
@@ -4314,8 +4372,9 @@
       <c r="Z53" s="8"/>
       <c r="AA53" s="8"/>
       <c r="AB53" s="8"/>
-    </row>
-    <row r="54" spans="1:28">
+      <c r="AC53" s="8"/>
+    </row>
+    <row r="54" spans="1:29">
       <c r="A54" s="5" t="s">
         <v>57</v>
       </c>
@@ -4346,8 +4405,9 @@
       <c r="Z54" s="8"/>
       <c r="AA54" s="8"/>
       <c r="AB54" s="8"/>
-    </row>
-    <row r="55" spans="1:28">
+      <c r="AC54" s="8"/>
+    </row>
+    <row r="55" spans="1:29">
       <c r="A55" s="5" t="s">
         <v>58</v>
       </c>
@@ -4378,8 +4438,9 @@
       <c r="Z55" s="8"/>
       <c r="AA55" s="8"/>
       <c r="AB55" s="8"/>
-    </row>
-    <row r="56" spans="1:28">
+      <c r="AC55" s="8"/>
+    </row>
+    <row r="56" spans="1:29">
       <c r="A56" s="5" t="s">
         <v>59</v>
       </c>
@@ -4410,8 +4471,9 @@
       <c r="Z56" s="8"/>
       <c r="AA56" s="8"/>
       <c r="AB56" s="8"/>
-    </row>
-    <row r="57" spans="1:28">
+      <c r="AC56" s="8"/>
+    </row>
+    <row r="57" spans="1:29">
       <c r="A57" s="5" t="s">
         <v>60</v>
       </c>
@@ -4442,8 +4504,9 @@
       <c r="Z57" s="8"/>
       <c r="AA57" s="8"/>
       <c r="AB57" s="8"/>
-    </row>
-    <row r="58" spans="1:28">
+      <c r="AC57" s="8"/>
+    </row>
+    <row r="58" spans="1:29">
       <c r="A58" s="5" t="s">
         <v>61</v>
       </c>
@@ -4474,8 +4537,9 @@
       <c r="Z58" s="8"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-    </row>
-    <row r="59" spans="1:28">
+      <c r="AC58" s="8"/>
+    </row>
+    <row r="59" spans="1:29">
       <c r="A59" s="5" t="s">
         <v>62</v>
       </c>
@@ -4506,8 +4570,9 @@
       <c r="Z59" s="8"/>
       <c r="AA59" s="8"/>
       <c r="AB59" s="8"/>
-    </row>
-    <row r="60" spans="1:28">
+      <c r="AC59" s="8"/>
+    </row>
+    <row r="60" spans="1:29">
       <c r="A60" s="5" t="s">
         <v>63</v>
       </c>
@@ -4538,8 +4603,9 @@
       <c r="Z60" s="8"/>
       <c r="AA60" s="8"/>
       <c r="AB60" s="8"/>
-    </row>
-    <row r="61" spans="1:28">
+      <c r="AC60" s="8"/>
+    </row>
+    <row r="61" spans="1:29">
       <c r="A61" s="5" t="s">
         <v>64</v>
       </c>
@@ -4570,8 +4636,9 @@
       <c r="Z61" s="8"/>
       <c r="AA61" s="8"/>
       <c r="AB61" s="8"/>
-    </row>
-    <row r="62" spans="1:28">
+      <c r="AC61" s="8"/>
+    </row>
+    <row r="62" spans="1:29">
       <c r="A62" s="5" t="s">
         <v>65</v>
       </c>
@@ -4602,8 +4669,9 @@
       <c r="Z62" s="8"/>
       <c r="AA62" s="8"/>
       <c r="AB62" s="8"/>
-    </row>
-    <row r="63" spans="1:28">
+      <c r="AC62" s="8"/>
+    </row>
+    <row r="63" spans="1:29">
       <c r="A63" s="5" t="s">
         <v>66</v>
       </c>
@@ -4634,8 +4702,9 @@
       <c r="Z63" s="8"/>
       <c r="AA63" s="8"/>
       <c r="AB63" s="8"/>
-    </row>
-    <row r="64" spans="1:28">
+      <c r="AC63" s="8"/>
+    </row>
+    <row r="64" spans="1:29">
       <c r="A64" s="5" t="s">
         <v>67</v>
       </c>
@@ -4666,8 +4735,9 @@
       <c r="Z64" s="8"/>
       <c r="AA64" s="8"/>
       <c r="AB64" s="8"/>
-    </row>
-    <row r="65" spans="1:28">
+      <c r="AC64" s="8"/>
+    </row>
+    <row r="65" spans="1:29">
       <c r="A65" s="5" t="s">
         <v>68</v>
       </c>
@@ -4698,8 +4768,9 @@
       <c r="Z65" s="8"/>
       <c r="AA65" s="8"/>
       <c r="AB65" s="8"/>
-    </row>
-    <row r="66" spans="1:28">
+      <c r="AC65" s="8"/>
+    </row>
+    <row r="66" spans="1:29">
       <c r="A66" s="5" t="s">
         <v>69</v>
       </c>
@@ -4730,8 +4801,9 @@
       <c r="Z66" s="8"/>
       <c r="AA66" s="8"/>
       <c r="AB66" s="8"/>
-    </row>
-    <row r="67" spans="1:28">
+      <c r="AC66" s="8"/>
+    </row>
+    <row r="67" spans="1:29">
       <c r="A67" s="5" t="s">
         <v>70</v>
       </c>
@@ -4762,8 +4834,9 @@
       <c r="Z67" s="8"/>
       <c r="AA67" s="8"/>
       <c r="AB67" s="8"/>
-    </row>
-    <row r="68" spans="1:28">
+      <c r="AC67" s="8"/>
+    </row>
+    <row r="68" spans="1:29">
       <c r="A68" s="5" t="s">
         <v>71</v>
       </c>
@@ -4794,8 +4867,9 @@
       <c r="Z68" s="8"/>
       <c r="AA68" s="8"/>
       <c r="AB68" s="8"/>
-    </row>
-    <row r="69" spans="1:28">
+      <c r="AC68" s="8"/>
+    </row>
+    <row r="69" spans="1:29">
       <c r="A69" s="5" t="s">
         <v>72</v>
       </c>
@@ -4826,8 +4900,9 @@
       <c r="Z69" s="8"/>
       <c r="AA69" s="8"/>
       <c r="AB69" s="8"/>
-    </row>
-    <row r="70" spans="1:28">
+      <c r="AC69" s="8"/>
+    </row>
+    <row r="70" spans="1:29">
       <c r="A70" s="5" t="s">
         <v>73</v>
       </c>
@@ -4858,8 +4933,9 @@
       <c r="Z70" s="8"/>
       <c r="AA70" s="8"/>
       <c r="AB70" s="8"/>
-    </row>
-    <row r="71" spans="1:28">
+      <c r="AC70" s="8"/>
+    </row>
+    <row r="71" spans="1:29">
       <c r="A71" s="5" t="s">
         <v>74</v>
       </c>
@@ -4890,8 +4966,9 @@
       <c r="Z71" s="8"/>
       <c r="AA71" s="8"/>
       <c r="AB71" s="8"/>
-    </row>
-    <row r="72" spans="1:28">
+      <c r="AC71" s="8"/>
+    </row>
+    <row r="72" spans="1:29">
       <c r="A72" s="5" t="s">
         <v>75</v>
       </c>
@@ -4922,8 +4999,9 @@
       <c r="Z72" s="8"/>
       <c r="AA72" s="8"/>
       <c r="AB72" s="8"/>
-    </row>
-    <row r="73" spans="1:28">
+      <c r="AC72" s="8"/>
+    </row>
+    <row r="73" spans="1:29">
       <c r="A73" s="5" t="s">
         <v>76</v>
       </c>
@@ -4954,8 +5032,9 @@
       <c r="Z73" s="8"/>
       <c r="AA73" s="8"/>
       <c r="AB73" s="8"/>
-    </row>
-    <row r="74" spans="1:28">
+      <c r="AC73" s="8"/>
+    </row>
+    <row r="74" spans="1:29">
       <c r="A74" s="5" t="s">
         <v>77</v>
       </c>
@@ -4986,8 +5065,9 @@
       <c r="Z74" s="8"/>
       <c r="AA74" s="8"/>
       <c r="AB74" s="8"/>
-    </row>
-    <row r="75" spans="1:28">
+      <c r="AC74" s="8"/>
+    </row>
+    <row r="75" spans="1:29">
       <c r="A75" s="5" t="s">
         <v>78</v>
       </c>
@@ -5018,8 +5098,9 @@
       <c r="Z75" s="8"/>
       <c r="AA75" s="8"/>
       <c r="AB75" s="8"/>
-    </row>
-    <row r="76" spans="1:28">
+      <c r="AC75" s="8"/>
+    </row>
+    <row r="76" spans="1:29">
       <c r="A76" s="5" t="s">
         <v>79</v>
       </c>
@@ -5050,8 +5131,9 @@
       <c r="Z76" s="8"/>
       <c r="AA76" s="8"/>
       <c r="AB76" s="8"/>
-    </row>
-    <row r="77" spans="1:28">
+      <c r="AC76" s="8"/>
+    </row>
+    <row r="77" spans="1:29">
       <c r="A77" s="5" t="s">
         <v>80</v>
       </c>
@@ -5082,8 +5164,9 @@
       <c r="Z77" s="8"/>
       <c r="AA77" s="8"/>
       <c r="AB77" s="8"/>
-    </row>
-    <row r="78" spans="1:28">
+      <c r="AC77" s="8"/>
+    </row>
+    <row r="78" spans="1:29">
       <c r="A78" s="5" t="s">
         <v>81</v>
       </c>
@@ -5114,8 +5197,9 @@
       <c r="Z78" s="8"/>
       <c r="AA78" s="8"/>
       <c r="AB78" s="8"/>
-    </row>
-    <row r="79" spans="1:28">
+      <c r="AC78" s="8"/>
+    </row>
+    <row r="79" spans="1:29">
       <c r="A79" s="5" t="s">
         <v>82</v>
       </c>
@@ -5146,8 +5230,9 @@
       <c r="Z79" s="8"/>
       <c r="AA79" s="8"/>
       <c r="AB79" s="8"/>
-    </row>
-    <row r="80" spans="1:28">
+      <c r="AC79" s="8"/>
+    </row>
+    <row r="80" spans="1:29">
       <c r="A80" s="5" t="s">
         <v>83</v>
       </c>
@@ -5178,8 +5263,9 @@
       <c r="Z80" s="8"/>
       <c r="AA80" s="8"/>
       <c r="AB80" s="8"/>
-    </row>
-    <row r="81" spans="1:28">
+      <c r="AC80" s="8"/>
+    </row>
+    <row r="81" spans="1:29">
       <c r="A81" s="5" t="s">
         <v>84</v>
       </c>
@@ -5210,8 +5296,9 @@
       <c r="Z81" s="8"/>
       <c r="AA81" s="8"/>
       <c r="AB81" s="8"/>
-    </row>
-    <row r="82" spans="1:28">
+      <c r="AC81" s="8"/>
+    </row>
+    <row r="82" spans="1:29">
       <c r="A82" s="5" t="s">
         <v>85</v>
       </c>
@@ -5242,8 +5329,9 @@
       <c r="Z82" s="8"/>
       <c r="AA82" s="8"/>
       <c r="AB82" s="8"/>
-    </row>
-    <row r="83" spans="1:28">
+      <c r="AC82" s="8"/>
+    </row>
+    <row r="83" spans="1:29">
       <c r="A83" s="5" t="s">
         <v>86</v>
       </c>
@@ -5274,8 +5362,9 @@
       <c r="Z83" s="8"/>
       <c r="AA83" s="8"/>
       <c r="AB83" s="8"/>
-    </row>
-    <row r="84" spans="1:28">
+      <c r="AC83" s="8"/>
+    </row>
+    <row r="84" spans="1:29">
       <c r="A84" s="5" t="s">
         <v>87</v>
       </c>
@@ -5306,8 +5395,9 @@
       <c r="Z84" s="8"/>
       <c r="AA84" s="8"/>
       <c r="AB84" s="8"/>
-    </row>
-    <row r="85" spans="1:28">
+      <c r="AC84" s="8"/>
+    </row>
+    <row r="85" spans="1:29">
       <c r="A85" s="5" t="s">
         <v>88</v>
       </c>
@@ -5338,8 +5428,9 @@
       <c r="Z85" s="8"/>
       <c r="AA85" s="8"/>
       <c r="AB85" s="8"/>
-    </row>
-    <row r="86" spans="1:28">
+      <c r="AC85" s="8"/>
+    </row>
+    <row r="86" spans="1:29">
       <c r="A86" s="5" t="s">
         <v>89</v>
       </c>
@@ -5370,8 +5461,9 @@
       <c r="Z86" s="8"/>
       <c r="AA86" s="8"/>
       <c r="AB86" s="8"/>
-    </row>
-    <row r="87" spans="1:28">
+      <c r="AC86" s="8"/>
+    </row>
+    <row r="87" spans="1:29">
       <c r="A87" s="5" t="s">
         <v>90</v>
       </c>
@@ -5402,8 +5494,9 @@
       <c r="Z87" s="8"/>
       <c r="AA87" s="8"/>
       <c r="AB87" s="8"/>
-    </row>
-    <row r="88" spans="1:28">
+      <c r="AC87" s="8"/>
+    </row>
+    <row r="88" spans="1:29">
       <c r="A88" s="5" t="s">
         <v>91</v>
       </c>
@@ -5434,8 +5527,9 @@
       <c r="Z88" s="8"/>
       <c r="AA88" s="8"/>
       <c r="AB88" s="8"/>
-    </row>
-    <row r="89" spans="1:28">
+      <c r="AC88" s="8"/>
+    </row>
+    <row r="89" spans="1:29">
       <c r="A89" s="5" t="s">
         <v>92</v>
       </c>
@@ -5466,8 +5560,9 @@
       <c r="Z89" s="8"/>
       <c r="AA89" s="8"/>
       <c r="AB89" s="8"/>
-    </row>
-    <row r="90" spans="1:28">
+      <c r="AC89" s="8"/>
+    </row>
+    <row r="90" spans="1:29">
       <c r="A90" s="5" t="s">
         <v>93</v>
       </c>
@@ -5498,8 +5593,9 @@
       <c r="Z90" s="8"/>
       <c r="AA90" s="8"/>
       <c r="AB90" s="8"/>
-    </row>
-    <row r="91" spans="1:28">
+      <c r="AC90" s="8"/>
+    </row>
+    <row r="91" spans="1:29">
       <c r="A91" s="5" t="s">
         <v>94</v>
       </c>
@@ -5530,8 +5626,9 @@
       <c r="Z91" s="8"/>
       <c r="AA91" s="8"/>
       <c r="AB91" s="8"/>
-    </row>
-    <row r="92" spans="1:28">
+      <c r="AC91" s="8"/>
+    </row>
+    <row r="92" spans="1:29">
       <c r="A92" s="5" t="s">
         <v>95</v>
       </c>
@@ -5562,8 +5659,9 @@
       <c r="Z92" s="8"/>
       <c r="AA92" s="8"/>
       <c r="AB92" s="8"/>
-    </row>
-    <row r="93" spans="1:28">
+      <c r="AC92" s="8"/>
+    </row>
+    <row r="93" spans="1:29">
       <c r="A93" s="5" t="s">
         <v>96</v>
       </c>
@@ -5594,8 +5692,9 @@
       <c r="Z93" s="8"/>
       <c r="AA93" s="8"/>
       <c r="AB93" s="8"/>
-    </row>
-    <row r="94" spans="1:28">
+      <c r="AC93" s="8"/>
+    </row>
+    <row r="94" spans="1:29">
       <c r="A94" s="5" t="s">
         <v>97</v>
       </c>
@@ -5626,8 +5725,9 @@
       <c r="Z94" s="8"/>
       <c r="AA94" s="8"/>
       <c r="AB94" s="8"/>
-    </row>
-    <row r="95" spans="1:28">
+      <c r="AC94" s="8"/>
+    </row>
+    <row r="95" spans="1:29">
       <c r="A95" s="5" t="s">
         <v>98</v>
       </c>
@@ -5658,8 +5758,9 @@
       <c r="Z95" s="8"/>
       <c r="AA95" s="8"/>
       <c r="AB95" s="8"/>
-    </row>
-    <row r="96" spans="1:28">
+      <c r="AC95" s="8"/>
+    </row>
+    <row r="96" spans="1:29">
       <c r="A96" s="5" t="s">
         <v>99</v>
       </c>
@@ -5690,8 +5791,9 @@
       <c r="Z96" s="8"/>
       <c r="AA96" s="8"/>
       <c r="AB96" s="8"/>
-    </row>
-    <row r="97" spans="1:28">
+      <c r="AC96" s="8"/>
+    </row>
+    <row r="97" spans="1:29">
       <c r="A97" s="5" t="s">
         <v>100</v>
       </c>
@@ -5722,8 +5824,9 @@
       <c r="Z97" s="8"/>
       <c r="AA97" s="8"/>
       <c r="AB97" s="8"/>
-    </row>
-    <row r="98" spans="1:28">
+      <c r="AC97" s="8"/>
+    </row>
+    <row r="98" spans="1:29">
       <c r="A98" s="5" t="s">
         <v>101</v>
       </c>
@@ -5754,8 +5857,9 @@
       <c r="Z98" s="8"/>
       <c r="AA98" s="8"/>
       <c r="AB98" s="8"/>
-    </row>
-    <row r="99" spans="1:28">
+      <c r="AC98" s="8"/>
+    </row>
+    <row r="99" spans="1:29">
       <c r="A99" s="5" t="s">
         <v>102</v>
       </c>
@@ -5786,8 +5890,9 @@
       <c r="Z99" s="8"/>
       <c r="AA99" s="8"/>
       <c r="AB99" s="8"/>
-    </row>
-    <row r="100" spans="1:28">
+      <c r="AC99" s="8"/>
+    </row>
+    <row r="100" spans="1:29">
       <c r="A100" s="5" t="s">
         <v>103</v>
       </c>
@@ -5818,8 +5923,9 @@
       <c r="Z100" s="8"/>
       <c r="AA100" s="8"/>
       <c r="AB100" s="8"/>
-    </row>
-    <row r="101" spans="1:28">
+      <c r="AC100" s="8"/>
+    </row>
+    <row r="101" spans="1:29">
       <c r="A101" s="5" t="s">
         <v>104</v>
       </c>
@@ -5850,8 +5956,9 @@
       <c r="Z101" s="8"/>
       <c r="AA101" s="8"/>
       <c r="AB101" s="8"/>
-    </row>
-    <row r="102" spans="1:28">
+      <c r="AC101" s="8"/>
+    </row>
+    <row r="102" spans="1:29">
       <c r="A102" s="5" t="s">
         <v>105</v>
       </c>
@@ -5882,8 +5989,9 @@
       <c r="Z102" s="8"/>
       <c r="AA102" s="8"/>
       <c r="AB102" s="8"/>
-    </row>
-    <row r="103" spans="1:28">
+      <c r="AC102" s="8"/>
+    </row>
+    <row r="103" spans="1:29">
       <c r="A103" s="5" t="s">
         <v>106</v>
       </c>
@@ -5914,8 +6022,9 @@
       <c r="Z103" s="8"/>
       <c r="AA103" s="8"/>
       <c r="AB103" s="8"/>
-    </row>
-    <row r="104" spans="1:28">
+      <c r="AC103" s="8"/>
+    </row>
+    <row r="104" spans="1:29">
       <c r="A104" s="5" t="s">
         <v>107</v>
       </c>
@@ -5946,8 +6055,9 @@
       <c r="Z104" s="8"/>
       <c r="AA104" s="8"/>
       <c r="AB104" s="8"/>
-    </row>
-    <row r="105" spans="1:28">
+      <c r="AC104" s="8"/>
+    </row>
+    <row r="105" spans="1:29">
       <c r="A105" s="5" t="s">
         <v>108</v>
       </c>
@@ -5978,8 +6088,9 @@
       <c r="Z105" s="8"/>
       <c r="AA105" s="8"/>
       <c r="AB105" s="8"/>
-    </row>
-    <row r="106" spans="1:28">
+      <c r="AC105" s="8"/>
+    </row>
+    <row r="106" spans="1:29">
       <c r="A106" s="5" t="s">
         <v>109</v>
       </c>
@@ -6010,6 +6121,7 @@
       <c r="Z106" s="8"/>
       <c r="AA106" s="8"/>
       <c r="AB106" s="8"/>
+      <c r="AC106" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/data/raw_results/lanupro_vocabulary_general.xlsx
+++ b/data/raw_results/lanupro_vocabulary_general.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3258A069-DD77-4EDB-A287-170E060B084E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F9EC3C-98BF-431A-824F-48223158C2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="278">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -2210,9 +2210,17 @@
     <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.88671875" customWidth="1"/>
+    <col min="19" max="19" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="22.5546875" customWidth="1"/>
-    <col min="27" max="27" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" s="1" customFormat="1">
@@ -2625,22 +2633,36 @@
       <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+      <c r="B7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>117</v>
+      </c>
       <c r="D7" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="8" t="s">
+        <v>117</v>
+      </c>
       <c r="F7" s="8" t="s">
         <v>117</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
+      <c r="H7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>117</v>
+      </c>
       <c r="L7" s="8" t="s">
         <v>173</v>
       </c>
@@ -2650,21 +2672,51 @@
       <c r="N7" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="8"/>
+      <c r="O7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="T7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="V7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="W7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="X7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AB7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC7" s="8" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="8" spans="1:29">
       <c r="A8" s="5" t="s">

--- a/data/raw_results/lanupro_vocabulary_general.xlsx
+++ b/data/raw_results/lanupro_vocabulary_general.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F9EC3C-98BF-431A-824F-48223158C2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45F3CF2-CE6E-4C0F-98B6-15E86D35207F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="279">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -869,10 +869,13 @@
     <t>sample_form</t>
   </si>
   <si>
-    <t>test</t>
-  </si>
-  <si>
     <t>test_field</t>
+  </si>
+  <si>
+    <t>test_01</t>
+  </si>
+  <si>
+    <t>test_02</t>
   </si>
 </sst>
 </file>
@@ -2198,7 +2201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB33DE6-D058-433F-9B7D-5598CD0261F2}">
-  <dimension ref="A1:AC106"/>
+  <dimension ref="A1:AD106"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17" style="4" customWidth="1"/>
@@ -2219,11 +2222,12 @@
     <col min="25" max="25" width="16" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.33203125" customWidth="1"/>
+    <col min="29" max="29" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="1" customFormat="1">
+    <row r="1" spans="1:30" s="1" customFormat="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2306,13 +2310,16 @@
         <v>261</v>
       </c>
       <c r="AB1" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="AC1" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="AC1" s="6" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29">
+      <c r="AD1" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30">
       <c r="A2" s="5" t="s">
         <v>129</v>
       </c>
@@ -2400,8 +2407,11 @@
       <c r="AC2" s="8" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="3" spans="1:29">
+      <c r="AD2" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -2457,8 +2467,9 @@
       <c r="AA3" s="8"/>
       <c r="AB3" s="8"/>
       <c r="AC3" s="8"/>
-    </row>
-    <row r="4" spans="1:29">
+      <c r="AD3" s="8"/>
+    </row>
+    <row r="4" spans="1:30">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
@@ -2514,8 +2525,9 @@
       <c r="AA4" s="8"/>
       <c r="AB4" s="8"/>
       <c r="AC4" s="8"/>
-    </row>
-    <row r="5" spans="1:29" ht="86.4">
+      <c r="AD4" s="8"/>
+    </row>
+    <row r="5" spans="1:30" ht="86.4">
       <c r="A5" s="9" t="s">
         <v>6</v>
       </c>
@@ -2571,14 +2583,15 @@
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
-      <c r="AB5" s="10" t="s">
+      <c r="AB5" s="10"/>
+      <c r="AC5" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="AC5" s="8" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29">
+      <c r="AD5" s="8" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30">
       <c r="A6" s="5" t="s">
         <v>115</v>
       </c>
@@ -2628,8 +2641,9 @@
       <c r="AA6" s="8"/>
       <c r="AB6" s="8"/>
       <c r="AC6" s="8"/>
-    </row>
-    <row r="7" spans="1:29">
+      <c r="AD6" s="8"/>
+    </row>
+    <row r="7" spans="1:30">
       <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
@@ -2717,8 +2731,11 @@
       <c r="AC7" s="8" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="8" spans="1:29">
+      <c r="AD7" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30">
       <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
@@ -2762,8 +2779,9 @@
       <c r="AA8" s="8"/>
       <c r="AB8" s="8"/>
       <c r="AC8" s="8"/>
-    </row>
-    <row r="9" spans="1:29">
+      <c r="AD8" s="8"/>
+    </row>
+    <row r="9" spans="1:30">
       <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
@@ -2807,8 +2825,9 @@
       <c r="AA9" s="8"/>
       <c r="AB9" s="8"/>
       <c r="AC9" s="8"/>
-    </row>
-    <row r="10" spans="1:29">
+      <c r="AD9" s="8"/>
+    </row>
+    <row r="10" spans="1:30">
       <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
@@ -2852,8 +2871,9 @@
       <c r="AA10" s="8"/>
       <c r="AB10" s="8"/>
       <c r="AC10" s="8"/>
-    </row>
-    <row r="11" spans="1:29">
+      <c r="AD10" s="8"/>
+    </row>
+    <row r="11" spans="1:30">
       <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
@@ -2895,8 +2915,9 @@
       <c r="AA11" s="8"/>
       <c r="AB11" s="8"/>
       <c r="AC11" s="8"/>
-    </row>
-    <row r="12" spans="1:29">
+      <c r="AD11" s="8"/>
+    </row>
+    <row r="12" spans="1:30">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
@@ -2938,8 +2959,9 @@
       <c r="AA12" s="8"/>
       <c r="AB12" s="8"/>
       <c r="AC12" s="8"/>
-    </row>
-    <row r="13" spans="1:29">
+      <c r="AD12" s="8"/>
+    </row>
+    <row r="13" spans="1:30">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -2979,8 +3001,9 @@
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
       <c r="AC13" s="8"/>
-    </row>
-    <row r="14" spans="1:29">
+      <c r="AD13" s="8"/>
+    </row>
+    <row r="14" spans="1:30">
       <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
@@ -3020,8 +3043,9 @@
       <c r="AA14" s="8"/>
       <c r="AB14" s="8"/>
       <c r="AC14" s="8"/>
-    </row>
-    <row r="15" spans="1:29">
+      <c r="AD14" s="8"/>
+    </row>
+    <row r="15" spans="1:30">
       <c r="A15" s="5" t="s">
         <v>18</v>
       </c>
@@ -3061,8 +3085,9 @@
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
       <c r="AC15" s="8"/>
-    </row>
-    <row r="16" spans="1:29">
+      <c r="AD15" s="8"/>
+    </row>
+    <row r="16" spans="1:30">
       <c r="A16" s="5" t="s">
         <v>19</v>
       </c>
@@ -3102,8 +3127,9 @@
       <c r="AA16" s="8"/>
       <c r="AB16" s="8"/>
       <c r="AC16" s="8"/>
-    </row>
-    <row r="17" spans="1:29">
+      <c r="AD16" s="8"/>
+    </row>
+    <row r="17" spans="1:30">
       <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
@@ -3143,8 +3169,9 @@
       <c r="AA17" s="8"/>
       <c r="AB17" s="8"/>
       <c r="AC17" s="8"/>
-    </row>
-    <row r="18" spans="1:29">
+      <c r="AD17" s="8"/>
+    </row>
+    <row r="18" spans="1:30">
       <c r="A18" s="5" t="s">
         <v>21</v>
       </c>
@@ -3182,8 +3209,9 @@
       <c r="AA18" s="8"/>
       <c r="AB18" s="8"/>
       <c r="AC18" s="8"/>
-    </row>
-    <row r="19" spans="1:29">
+      <c r="AD18" s="8"/>
+    </row>
+    <row r="19" spans="1:30">
       <c r="A19" s="5" t="s">
         <v>22</v>
       </c>
@@ -3221,8 +3249,9 @@
       <c r="AA19" s="8"/>
       <c r="AB19" s="8"/>
       <c r="AC19" s="8"/>
-    </row>
-    <row r="20" spans="1:29">
+      <c r="AD19" s="8"/>
+    </row>
+    <row r="20" spans="1:30">
       <c r="A20" s="5" t="s">
         <v>23</v>
       </c>
@@ -3260,8 +3289,9 @@
       <c r="AA20" s="8"/>
       <c r="AB20" s="8"/>
       <c r="AC20" s="8"/>
-    </row>
-    <row r="21" spans="1:29">
+      <c r="AD20" s="8"/>
+    </row>
+    <row r="21" spans="1:30">
       <c r="A21" s="5" t="s">
         <v>24</v>
       </c>
@@ -3297,8 +3327,9 @@
       <c r="AA21" s="8"/>
       <c r="AB21" s="8"/>
       <c r="AC21" s="8"/>
-    </row>
-    <row r="22" spans="1:29">
+      <c r="AD21" s="8"/>
+    </row>
+    <row r="22" spans="1:30">
       <c r="A22" s="5" t="s">
         <v>25</v>
       </c>
@@ -3334,8 +3365,9 @@
       <c r="AA22" s="8"/>
       <c r="AB22" s="8"/>
       <c r="AC22" s="8"/>
-    </row>
-    <row r="23" spans="1:29">
+      <c r="AD22" s="8"/>
+    </row>
+    <row r="23" spans="1:30">
       <c r="A23" s="5" t="s">
         <v>26</v>
       </c>
@@ -3371,8 +3403,9 @@
       <c r="AA23" s="8"/>
       <c r="AB23" s="8"/>
       <c r="AC23" s="8"/>
-    </row>
-    <row r="24" spans="1:29">
+      <c r="AD23" s="8"/>
+    </row>
+    <row r="24" spans="1:30">
       <c r="A24" s="5" t="s">
         <v>27</v>
       </c>
@@ -3408,8 +3441,9 @@
       <c r="AA24" s="8"/>
       <c r="AB24" s="8"/>
       <c r="AC24" s="8"/>
-    </row>
-    <row r="25" spans="1:29">
+      <c r="AD24" s="8"/>
+    </row>
+    <row r="25" spans="1:30">
       <c r="A25" s="5" t="s">
         <v>28</v>
       </c>
@@ -3445,8 +3479,9 @@
       <c r="AA25" s="8"/>
       <c r="AB25" s="8"/>
       <c r="AC25" s="8"/>
-    </row>
-    <row r="26" spans="1:29">
+      <c r="AD25" s="8"/>
+    </row>
+    <row r="26" spans="1:30">
       <c r="A26" s="5" t="s">
         <v>29</v>
       </c>
@@ -3482,8 +3517,9 @@
       <c r="AA26" s="8"/>
       <c r="AB26" s="8"/>
       <c r="AC26" s="8"/>
-    </row>
-    <row r="27" spans="1:29">
+      <c r="AD26" s="8"/>
+    </row>
+    <row r="27" spans="1:30">
       <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
@@ -3519,8 +3555,9 @@
       <c r="AA27" s="8"/>
       <c r="AB27" s="8"/>
       <c r="AC27" s="8"/>
-    </row>
-    <row r="28" spans="1:29">
+      <c r="AD27" s="8"/>
+    </row>
+    <row r="28" spans="1:30">
       <c r="A28" s="5" t="s">
         <v>31</v>
       </c>
@@ -3556,8 +3593,9 @@
       <c r="AA28" s="8"/>
       <c r="AB28" s="8"/>
       <c r="AC28" s="8"/>
-    </row>
-    <row r="29" spans="1:29">
+      <c r="AD28" s="8"/>
+    </row>
+    <row r="29" spans="1:30">
       <c r="A29" s="5" t="s">
         <v>32</v>
       </c>
@@ -3593,8 +3631,9 @@
       <c r="AA29" s="8"/>
       <c r="AB29" s="8"/>
       <c r="AC29" s="8"/>
-    </row>
-    <row r="30" spans="1:29">
+      <c r="AD29" s="8"/>
+    </row>
+    <row r="30" spans="1:30">
       <c r="A30" s="5" t="s">
         <v>33</v>
       </c>
@@ -3630,8 +3669,9 @@
       <c r="AA30" s="8"/>
       <c r="AB30" s="8"/>
       <c r="AC30" s="8"/>
-    </row>
-    <row r="31" spans="1:29">
+      <c r="AD30" s="8"/>
+    </row>
+    <row r="31" spans="1:30">
       <c r="A31" s="5" t="s">
         <v>34</v>
       </c>
@@ -3667,8 +3707,9 @@
       <c r="AA31" s="8"/>
       <c r="AB31" s="8"/>
       <c r="AC31" s="8"/>
-    </row>
-    <row r="32" spans="1:29">
+      <c r="AD31" s="8"/>
+    </row>
+    <row r="32" spans="1:30">
       <c r="A32" s="5" t="s">
         <v>35</v>
       </c>
@@ -3704,8 +3745,9 @@
       <c r="AA32" s="8"/>
       <c r="AB32" s="8"/>
       <c r="AC32" s="8"/>
-    </row>
-    <row r="33" spans="1:29">
+      <c r="AD32" s="8"/>
+    </row>
+    <row r="33" spans="1:30">
       <c r="A33" s="5" t="s">
         <v>36</v>
       </c>
@@ -3741,8 +3783,9 @@
       <c r="AA33" s="8"/>
       <c r="AB33" s="8"/>
       <c r="AC33" s="8"/>
-    </row>
-    <row r="34" spans="1:29">
+      <c r="AD33" s="8"/>
+    </row>
+    <row r="34" spans="1:30">
       <c r="A34" s="5" t="s">
         <v>37</v>
       </c>
@@ -3778,8 +3821,9 @@
       <c r="AA34" s="8"/>
       <c r="AB34" s="8"/>
       <c r="AC34" s="8"/>
-    </row>
-    <row r="35" spans="1:29">
+      <c r="AD34" s="8"/>
+    </row>
+    <row r="35" spans="1:30">
       <c r="A35" s="5" t="s">
         <v>38</v>
       </c>
@@ -3815,8 +3859,9 @@
       <c r="AA35" s="8"/>
       <c r="AB35" s="8"/>
       <c r="AC35" s="8"/>
-    </row>
-    <row r="36" spans="1:29">
+      <c r="AD35" s="8"/>
+    </row>
+    <row r="36" spans="1:30">
       <c r="A36" s="5" t="s">
         <v>39</v>
       </c>
@@ -3850,8 +3895,9 @@
       <c r="AA36" s="8"/>
       <c r="AB36" s="8"/>
       <c r="AC36" s="8"/>
-    </row>
-    <row r="37" spans="1:29">
+      <c r="AD36" s="8"/>
+    </row>
+    <row r="37" spans="1:30">
       <c r="A37" s="5" t="s">
         <v>40</v>
       </c>
@@ -3885,8 +3931,9 @@
       <c r="AA37" s="8"/>
       <c r="AB37" s="8"/>
       <c r="AC37" s="8"/>
-    </row>
-    <row r="38" spans="1:29">
+      <c r="AD37" s="8"/>
+    </row>
+    <row r="38" spans="1:30">
       <c r="A38" s="5" t="s">
         <v>41</v>
       </c>
@@ -3920,8 +3967,9 @@
       <c r="AA38" s="8"/>
       <c r="AB38" s="8"/>
       <c r="AC38" s="8"/>
-    </row>
-    <row r="39" spans="1:29">
+      <c r="AD38" s="8"/>
+    </row>
+    <row r="39" spans="1:30">
       <c r="A39" s="5" t="s">
         <v>42</v>
       </c>
@@ -3955,8 +4003,9 @@
       <c r="AA39" s="8"/>
       <c r="AB39" s="8"/>
       <c r="AC39" s="8"/>
-    </row>
-    <row r="40" spans="1:29">
+      <c r="AD39" s="8"/>
+    </row>
+    <row r="40" spans="1:30">
       <c r="A40" s="5" t="s">
         <v>43</v>
       </c>
@@ -3990,8 +4039,9 @@
       <c r="AA40" s="8"/>
       <c r="AB40" s="8"/>
       <c r="AC40" s="8"/>
-    </row>
-    <row r="41" spans="1:29">
+      <c r="AD40" s="8"/>
+    </row>
+    <row r="41" spans="1:30">
       <c r="A41" s="5" t="s">
         <v>44</v>
       </c>
@@ -4025,8 +4075,9 @@
       <c r="AA41" s="8"/>
       <c r="AB41" s="8"/>
       <c r="AC41" s="8"/>
-    </row>
-    <row r="42" spans="1:29">
+      <c r="AD41" s="8"/>
+    </row>
+    <row r="42" spans="1:30">
       <c r="A42" s="5" t="s">
         <v>45</v>
       </c>
@@ -4060,8 +4111,9 @@
       <c r="AA42" s="8"/>
       <c r="AB42" s="8"/>
       <c r="AC42" s="8"/>
-    </row>
-    <row r="43" spans="1:29">
+      <c r="AD42" s="8"/>
+    </row>
+    <row r="43" spans="1:30">
       <c r="A43" s="5" t="s">
         <v>46</v>
       </c>
@@ -4095,8 +4147,9 @@
       <c r="AA43" s="8"/>
       <c r="AB43" s="8"/>
       <c r="AC43" s="8"/>
-    </row>
-    <row r="44" spans="1:29">
+      <c r="AD43" s="8"/>
+    </row>
+    <row r="44" spans="1:30">
       <c r="A44" s="5" t="s">
         <v>47</v>
       </c>
@@ -4128,8 +4181,9 @@
       <c r="AA44" s="8"/>
       <c r="AB44" s="8"/>
       <c r="AC44" s="8"/>
-    </row>
-    <row r="45" spans="1:29">
+      <c r="AD44" s="8"/>
+    </row>
+    <row r="45" spans="1:30">
       <c r="A45" s="5" t="s">
         <v>48</v>
       </c>
@@ -4161,8 +4215,9 @@
       <c r="AA45" s="8"/>
       <c r="AB45" s="8"/>
       <c r="AC45" s="8"/>
-    </row>
-    <row r="46" spans="1:29">
+      <c r="AD45" s="8"/>
+    </row>
+    <row r="46" spans="1:30">
       <c r="A46" s="5" t="s">
         <v>49</v>
       </c>
@@ -4194,8 +4249,9 @@
       <c r="AA46" s="8"/>
       <c r="AB46" s="8"/>
       <c r="AC46" s="8"/>
-    </row>
-    <row r="47" spans="1:29">
+      <c r="AD46" s="8"/>
+    </row>
+    <row r="47" spans="1:30">
       <c r="A47" s="5" t="s">
         <v>50</v>
       </c>
@@ -4227,8 +4283,9 @@
       <c r="AA47" s="8"/>
       <c r="AB47" s="8"/>
       <c r="AC47" s="8"/>
-    </row>
-    <row r="48" spans="1:29">
+      <c r="AD47" s="8"/>
+    </row>
+    <row r="48" spans="1:30">
       <c r="A48" s="5" t="s">
         <v>51</v>
       </c>
@@ -4260,8 +4317,9 @@
       <c r="AA48" s="8"/>
       <c r="AB48" s="8"/>
       <c r="AC48" s="8"/>
-    </row>
-    <row r="49" spans="1:29">
+      <c r="AD48" s="8"/>
+    </row>
+    <row r="49" spans="1:30">
       <c r="A49" s="5" t="s">
         <v>52</v>
       </c>
@@ -4293,8 +4351,9 @@
       <c r="AA49" s="8"/>
       <c r="AB49" s="8"/>
       <c r="AC49" s="8"/>
-    </row>
-    <row r="50" spans="1:29">
+      <c r="AD49" s="8"/>
+    </row>
+    <row r="50" spans="1:30">
       <c r="A50" s="5" t="s">
         <v>53</v>
       </c>
@@ -4326,8 +4385,9 @@
       <c r="AA50" s="8"/>
       <c r="AB50" s="8"/>
       <c r="AC50" s="8"/>
-    </row>
-    <row r="51" spans="1:29">
+      <c r="AD50" s="8"/>
+    </row>
+    <row r="51" spans="1:30">
       <c r="A51" s="5" t="s">
         <v>54</v>
       </c>
@@ -4359,8 +4419,9 @@
       <c r="AA51" s="8"/>
       <c r="AB51" s="8"/>
       <c r="AC51" s="8"/>
-    </row>
-    <row r="52" spans="1:29">
+      <c r="AD51" s="8"/>
+    </row>
+    <row r="52" spans="1:30">
       <c r="A52" s="5" t="s">
         <v>55</v>
       </c>
@@ -4392,8 +4453,9 @@
       <c r="AA52" s="8"/>
       <c r="AB52" s="8"/>
       <c r="AC52" s="8"/>
-    </row>
-    <row r="53" spans="1:29">
+      <c r="AD52" s="8"/>
+    </row>
+    <row r="53" spans="1:30">
       <c r="A53" s="5" t="s">
         <v>56</v>
       </c>
@@ -4425,8 +4487,9 @@
       <c r="AA53" s="8"/>
       <c r="AB53" s="8"/>
       <c r="AC53" s="8"/>
-    </row>
-    <row r="54" spans="1:29">
+      <c r="AD53" s="8"/>
+    </row>
+    <row r="54" spans="1:30">
       <c r="A54" s="5" t="s">
         <v>57</v>
       </c>
@@ -4458,8 +4521,9 @@
       <c r="AA54" s="8"/>
       <c r="AB54" s="8"/>
       <c r="AC54" s="8"/>
-    </row>
-    <row r="55" spans="1:29">
+      <c r="AD54" s="8"/>
+    </row>
+    <row r="55" spans="1:30">
       <c r="A55" s="5" t="s">
         <v>58</v>
       </c>
@@ -4491,8 +4555,9 @@
       <c r="AA55" s="8"/>
       <c r="AB55" s="8"/>
       <c r="AC55" s="8"/>
-    </row>
-    <row r="56" spans="1:29">
+      <c r="AD55" s="8"/>
+    </row>
+    <row r="56" spans="1:30">
       <c r="A56" s="5" t="s">
         <v>59</v>
       </c>
@@ -4524,8 +4589,9 @@
       <c r="AA56" s="8"/>
       <c r="AB56" s="8"/>
       <c r="AC56" s="8"/>
-    </row>
-    <row r="57" spans="1:29">
+      <c r="AD56" s="8"/>
+    </row>
+    <row r="57" spans="1:30">
       <c r="A57" s="5" t="s">
         <v>60</v>
       </c>
@@ -4557,8 +4623,9 @@
       <c r="AA57" s="8"/>
       <c r="AB57" s="8"/>
       <c r="AC57" s="8"/>
-    </row>
-    <row r="58" spans="1:29">
+      <c r="AD57" s="8"/>
+    </row>
+    <row r="58" spans="1:30">
       <c r="A58" s="5" t="s">
         <v>61</v>
       </c>
@@ -4590,8 +4657,9 @@
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
       <c r="AC58" s="8"/>
-    </row>
-    <row r="59" spans="1:29">
+      <c r="AD58" s="8"/>
+    </row>
+    <row r="59" spans="1:30">
       <c r="A59" s="5" t="s">
         <v>62</v>
       </c>
@@ -4623,8 +4691,9 @@
       <c r="AA59" s="8"/>
       <c r="AB59" s="8"/>
       <c r="AC59" s="8"/>
-    </row>
-    <row r="60" spans="1:29">
+      <c r="AD59" s="8"/>
+    </row>
+    <row r="60" spans="1:30">
       <c r="A60" s="5" t="s">
         <v>63</v>
       </c>
@@ -4656,8 +4725,9 @@
       <c r="AA60" s="8"/>
       <c r="AB60" s="8"/>
       <c r="AC60" s="8"/>
-    </row>
-    <row r="61" spans="1:29">
+      <c r="AD60" s="8"/>
+    </row>
+    <row r="61" spans="1:30">
       <c r="A61" s="5" t="s">
         <v>64</v>
       </c>
@@ -4689,8 +4759,9 @@
       <c r="AA61" s="8"/>
       <c r="AB61" s="8"/>
       <c r="AC61" s="8"/>
-    </row>
-    <row r="62" spans="1:29">
+      <c r="AD61" s="8"/>
+    </row>
+    <row r="62" spans="1:30">
       <c r="A62" s="5" t="s">
         <v>65</v>
       </c>
@@ -4722,8 +4793,9 @@
       <c r="AA62" s="8"/>
       <c r="AB62" s="8"/>
       <c r="AC62" s="8"/>
-    </row>
-    <row r="63" spans="1:29">
+      <c r="AD62" s="8"/>
+    </row>
+    <row r="63" spans="1:30">
       <c r="A63" s="5" t="s">
         <v>66</v>
       </c>
@@ -4755,8 +4827,9 @@
       <c r="AA63" s="8"/>
       <c r="AB63" s="8"/>
       <c r="AC63" s="8"/>
-    </row>
-    <row r="64" spans="1:29">
+      <c r="AD63" s="8"/>
+    </row>
+    <row r="64" spans="1:30">
       <c r="A64" s="5" t="s">
         <v>67</v>
       </c>
@@ -4788,8 +4861,9 @@
       <c r="AA64" s="8"/>
       <c r="AB64" s="8"/>
       <c r="AC64" s="8"/>
-    </row>
-    <row r="65" spans="1:29">
+      <c r="AD64" s="8"/>
+    </row>
+    <row r="65" spans="1:30">
       <c r="A65" s="5" t="s">
         <v>68</v>
       </c>
@@ -4821,8 +4895,9 @@
       <c r="AA65" s="8"/>
       <c r="AB65" s="8"/>
       <c r="AC65" s="8"/>
-    </row>
-    <row r="66" spans="1:29">
+      <c r="AD65" s="8"/>
+    </row>
+    <row r="66" spans="1:30">
       <c r="A66" s="5" t="s">
         <v>69</v>
       </c>
@@ -4854,8 +4929,9 @@
       <c r="AA66" s="8"/>
       <c r="AB66" s="8"/>
       <c r="AC66" s="8"/>
-    </row>
-    <row r="67" spans="1:29">
+      <c r="AD66" s="8"/>
+    </row>
+    <row r="67" spans="1:30">
       <c r="A67" s="5" t="s">
         <v>70</v>
       </c>
@@ -4887,8 +4963,9 @@
       <c r="AA67" s="8"/>
       <c r="AB67" s="8"/>
       <c r="AC67" s="8"/>
-    </row>
-    <row r="68" spans="1:29">
+      <c r="AD67" s="8"/>
+    </row>
+    <row r="68" spans="1:30">
       <c r="A68" s="5" t="s">
         <v>71</v>
       </c>
@@ -4920,8 +4997,9 @@
       <c r="AA68" s="8"/>
       <c r="AB68" s="8"/>
       <c r="AC68" s="8"/>
-    </row>
-    <row r="69" spans="1:29">
+      <c r="AD68" s="8"/>
+    </row>
+    <row r="69" spans="1:30">
       <c r="A69" s="5" t="s">
         <v>72</v>
       </c>
@@ -4953,8 +5031,9 @@
       <c r="AA69" s="8"/>
       <c r="AB69" s="8"/>
       <c r="AC69" s="8"/>
-    </row>
-    <row r="70" spans="1:29">
+      <c r="AD69" s="8"/>
+    </row>
+    <row r="70" spans="1:30">
       <c r="A70" s="5" t="s">
         <v>73</v>
       </c>
@@ -4986,8 +5065,9 @@
       <c r="AA70" s="8"/>
       <c r="AB70" s="8"/>
       <c r="AC70" s="8"/>
-    </row>
-    <row r="71" spans="1:29">
+      <c r="AD70" s="8"/>
+    </row>
+    <row r="71" spans="1:30">
       <c r="A71" s="5" t="s">
         <v>74</v>
       </c>
@@ -5019,8 +5099,9 @@
       <c r="AA71" s="8"/>
       <c r="AB71" s="8"/>
       <c r="AC71" s="8"/>
-    </row>
-    <row r="72" spans="1:29">
+      <c r="AD71" s="8"/>
+    </row>
+    <row r="72" spans="1:30">
       <c r="A72" s="5" t="s">
         <v>75</v>
       </c>
@@ -5052,8 +5133,9 @@
       <c r="AA72" s="8"/>
       <c r="AB72" s="8"/>
       <c r="AC72" s="8"/>
-    </row>
-    <row r="73" spans="1:29">
+      <c r="AD72" s="8"/>
+    </row>
+    <row r="73" spans="1:30">
       <c r="A73" s="5" t="s">
         <v>76</v>
       </c>
@@ -5085,8 +5167,9 @@
       <c r="AA73" s="8"/>
       <c r="AB73" s="8"/>
       <c r="AC73" s="8"/>
-    </row>
-    <row r="74" spans="1:29">
+      <c r="AD73" s="8"/>
+    </row>
+    <row r="74" spans="1:30">
       <c r="A74" s="5" t="s">
         <v>77</v>
       </c>
@@ -5118,8 +5201,9 @@
       <c r="AA74" s="8"/>
       <c r="AB74" s="8"/>
       <c r="AC74" s="8"/>
-    </row>
-    <row r="75" spans="1:29">
+      <c r="AD74" s="8"/>
+    </row>
+    <row r="75" spans="1:30">
       <c r="A75" s="5" t="s">
         <v>78</v>
       </c>
@@ -5151,8 +5235,9 @@
       <c r="AA75" s="8"/>
       <c r="AB75" s="8"/>
       <c r="AC75" s="8"/>
-    </row>
-    <row r="76" spans="1:29">
+      <c r="AD75" s="8"/>
+    </row>
+    <row r="76" spans="1:30">
       <c r="A76" s="5" t="s">
         <v>79</v>
       </c>
@@ -5184,8 +5269,9 @@
       <c r="AA76" s="8"/>
       <c r="AB76" s="8"/>
       <c r="AC76" s="8"/>
-    </row>
-    <row r="77" spans="1:29">
+      <c r="AD76" s="8"/>
+    </row>
+    <row r="77" spans="1:30">
       <c r="A77" s="5" t="s">
         <v>80</v>
       </c>
@@ -5217,8 +5303,9 @@
       <c r="AA77" s="8"/>
       <c r="AB77" s="8"/>
       <c r="AC77" s="8"/>
-    </row>
-    <row r="78" spans="1:29">
+      <c r="AD77" s="8"/>
+    </row>
+    <row r="78" spans="1:30">
       <c r="A78" s="5" t="s">
         <v>81</v>
       </c>
@@ -5250,8 +5337,9 @@
       <c r="AA78" s="8"/>
       <c r="AB78" s="8"/>
       <c r="AC78" s="8"/>
-    </row>
-    <row r="79" spans="1:29">
+      <c r="AD78" s="8"/>
+    </row>
+    <row r="79" spans="1:30">
       <c r="A79" s="5" t="s">
         <v>82</v>
       </c>
@@ -5283,8 +5371,9 @@
       <c r="AA79" s="8"/>
       <c r="AB79" s="8"/>
       <c r="AC79" s="8"/>
-    </row>
-    <row r="80" spans="1:29">
+      <c r="AD79" s="8"/>
+    </row>
+    <row r="80" spans="1:30">
       <c r="A80" s="5" t="s">
         <v>83</v>
       </c>
@@ -5316,8 +5405,9 @@
       <c r="AA80" s="8"/>
       <c r="AB80" s="8"/>
       <c r="AC80" s="8"/>
-    </row>
-    <row r="81" spans="1:29">
+      <c r="AD80" s="8"/>
+    </row>
+    <row r="81" spans="1:30">
       <c r="A81" s="5" t="s">
         <v>84</v>
       </c>
@@ -5349,8 +5439,9 @@
       <c r="AA81" s="8"/>
       <c r="AB81" s="8"/>
       <c r="AC81" s="8"/>
-    </row>
-    <row r="82" spans="1:29">
+      <c r="AD81" s="8"/>
+    </row>
+    <row r="82" spans="1:30">
       <c r="A82" s="5" t="s">
         <v>85</v>
       </c>
@@ -5382,8 +5473,9 @@
       <c r="AA82" s="8"/>
       <c r="AB82" s="8"/>
       <c r="AC82" s="8"/>
-    </row>
-    <row r="83" spans="1:29">
+      <c r="AD82" s="8"/>
+    </row>
+    <row r="83" spans="1:30">
       <c r="A83" s="5" t="s">
         <v>86</v>
       </c>
@@ -5415,8 +5507,9 @@
       <c r="AA83" s="8"/>
       <c r="AB83" s="8"/>
       <c r="AC83" s="8"/>
-    </row>
-    <row r="84" spans="1:29">
+      <c r="AD83" s="8"/>
+    </row>
+    <row r="84" spans="1:30">
       <c r="A84" s="5" t="s">
         <v>87</v>
       </c>
@@ -5448,8 +5541,9 @@
       <c r="AA84" s="8"/>
       <c r="AB84" s="8"/>
       <c r="AC84" s="8"/>
-    </row>
-    <row r="85" spans="1:29">
+      <c r="AD84" s="8"/>
+    </row>
+    <row r="85" spans="1:30">
       <c r="A85" s="5" t="s">
         <v>88</v>
       </c>
@@ -5481,8 +5575,9 @@
       <c r="AA85" s="8"/>
       <c r="AB85" s="8"/>
       <c r="AC85" s="8"/>
-    </row>
-    <row r="86" spans="1:29">
+      <c r="AD85" s="8"/>
+    </row>
+    <row r="86" spans="1:30">
       <c r="A86" s="5" t="s">
         <v>89</v>
       </c>
@@ -5514,8 +5609,9 @@
       <c r="AA86" s="8"/>
       <c r="AB86" s="8"/>
       <c r="AC86" s="8"/>
-    </row>
-    <row r="87" spans="1:29">
+      <c r="AD86" s="8"/>
+    </row>
+    <row r="87" spans="1:30">
       <c r="A87" s="5" t="s">
         <v>90</v>
       </c>
@@ -5547,8 +5643,9 @@
       <c r="AA87" s="8"/>
       <c r="AB87" s="8"/>
       <c r="AC87" s="8"/>
-    </row>
-    <row r="88" spans="1:29">
+      <c r="AD87" s="8"/>
+    </row>
+    <row r="88" spans="1:30">
       <c r="A88" s="5" t="s">
         <v>91</v>
       </c>
@@ -5580,8 +5677,9 @@
       <c r="AA88" s="8"/>
       <c r="AB88" s="8"/>
       <c r="AC88" s="8"/>
-    </row>
-    <row r="89" spans="1:29">
+      <c r="AD88" s="8"/>
+    </row>
+    <row r="89" spans="1:30">
       <c r="A89" s="5" t="s">
         <v>92</v>
       </c>
@@ -5613,8 +5711,9 @@
       <c r="AA89" s="8"/>
       <c r="AB89" s="8"/>
       <c r="AC89" s="8"/>
-    </row>
-    <row r="90" spans="1:29">
+      <c r="AD89" s="8"/>
+    </row>
+    <row r="90" spans="1:30">
       <c r="A90" s="5" t="s">
         <v>93</v>
       </c>
@@ -5646,8 +5745,9 @@
       <c r="AA90" s="8"/>
       <c r="AB90" s="8"/>
       <c r="AC90" s="8"/>
-    </row>
-    <row r="91" spans="1:29">
+      <c r="AD90" s="8"/>
+    </row>
+    <row r="91" spans="1:30">
       <c r="A91" s="5" t="s">
         <v>94</v>
       </c>
@@ -5679,8 +5779,9 @@
       <c r="AA91" s="8"/>
       <c r="AB91" s="8"/>
       <c r="AC91" s="8"/>
-    </row>
-    <row r="92" spans="1:29">
+      <c r="AD91" s="8"/>
+    </row>
+    <row r="92" spans="1:30">
       <c r="A92" s="5" t="s">
         <v>95</v>
       </c>
@@ -5712,8 +5813,9 @@
       <c r="AA92" s="8"/>
       <c r="AB92" s="8"/>
       <c r="AC92" s="8"/>
-    </row>
-    <row r="93" spans="1:29">
+      <c r="AD92" s="8"/>
+    </row>
+    <row r="93" spans="1:30">
       <c r="A93" s="5" t="s">
         <v>96</v>
       </c>
@@ -5745,8 +5847,9 @@
       <c r="AA93" s="8"/>
       <c r="AB93" s="8"/>
       <c r="AC93" s="8"/>
-    </row>
-    <row r="94" spans="1:29">
+      <c r="AD93" s="8"/>
+    </row>
+    <row r="94" spans="1:30">
       <c r="A94" s="5" t="s">
         <v>97</v>
       </c>
@@ -5778,8 +5881,9 @@
       <c r="AA94" s="8"/>
       <c r="AB94" s="8"/>
       <c r="AC94" s="8"/>
-    </row>
-    <row r="95" spans="1:29">
+      <c r="AD94" s="8"/>
+    </row>
+    <row r="95" spans="1:30">
       <c r="A95" s="5" t="s">
         <v>98</v>
       </c>
@@ -5811,8 +5915,9 @@
       <c r="AA95" s="8"/>
       <c r="AB95" s="8"/>
       <c r="AC95" s="8"/>
-    </row>
-    <row r="96" spans="1:29">
+      <c r="AD95" s="8"/>
+    </row>
+    <row r="96" spans="1:30">
       <c r="A96" s="5" t="s">
         <v>99</v>
       </c>
@@ -5844,8 +5949,9 @@
       <c r="AA96" s="8"/>
       <c r="AB96" s="8"/>
       <c r="AC96" s="8"/>
-    </row>
-    <row r="97" spans="1:29">
+      <c r="AD96" s="8"/>
+    </row>
+    <row r="97" spans="1:30">
       <c r="A97" s="5" t="s">
         <v>100</v>
       </c>
@@ -5877,8 +5983,9 @@
       <c r="AA97" s="8"/>
       <c r="AB97" s="8"/>
       <c r="AC97" s="8"/>
-    </row>
-    <row r="98" spans="1:29">
+      <c r="AD97" s="8"/>
+    </row>
+    <row r="98" spans="1:30">
       <c r="A98" s="5" t="s">
         <v>101</v>
       </c>
@@ -5910,8 +6017,9 @@
       <c r="AA98" s="8"/>
       <c r="AB98" s="8"/>
       <c r="AC98" s="8"/>
-    </row>
-    <row r="99" spans="1:29">
+      <c r="AD98" s="8"/>
+    </row>
+    <row r="99" spans="1:30">
       <c r="A99" s="5" t="s">
         <v>102</v>
       </c>
@@ -5943,8 +6051,9 @@
       <c r="AA99" s="8"/>
       <c r="AB99" s="8"/>
       <c r="AC99" s="8"/>
-    </row>
-    <row r="100" spans="1:29">
+      <c r="AD99" s="8"/>
+    </row>
+    <row r="100" spans="1:30">
       <c r="A100" s="5" t="s">
         <v>103</v>
       </c>
@@ -5976,8 +6085,9 @@
       <c r="AA100" s="8"/>
       <c r="AB100" s="8"/>
       <c r="AC100" s="8"/>
-    </row>
-    <row r="101" spans="1:29">
+      <c r="AD100" s="8"/>
+    </row>
+    <row r="101" spans="1:30">
       <c r="A101" s="5" t="s">
         <v>104</v>
       </c>
@@ -6009,8 +6119,9 @@
       <c r="AA101" s="8"/>
       <c r="AB101" s="8"/>
       <c r="AC101" s="8"/>
-    </row>
-    <row r="102" spans="1:29">
+      <c r="AD101" s="8"/>
+    </row>
+    <row r="102" spans="1:30">
       <c r="A102" s="5" t="s">
         <v>105</v>
       </c>
@@ -6042,8 +6153,9 @@
       <c r="AA102" s="8"/>
       <c r="AB102" s="8"/>
       <c r="AC102" s="8"/>
-    </row>
-    <row r="103" spans="1:29">
+      <c r="AD102" s="8"/>
+    </row>
+    <row r="103" spans="1:30">
       <c r="A103" s="5" t="s">
         <v>106</v>
       </c>
@@ -6075,8 +6187,9 @@
       <c r="AA103" s="8"/>
       <c r="AB103" s="8"/>
       <c r="AC103" s="8"/>
-    </row>
-    <row r="104" spans="1:29">
+      <c r="AD103" s="8"/>
+    </row>
+    <row r="104" spans="1:30">
       <c r="A104" s="5" t="s">
         <v>107</v>
       </c>
@@ -6108,8 +6221,9 @@
       <c r="AA104" s="8"/>
       <c r="AB104" s="8"/>
       <c r="AC104" s="8"/>
-    </row>
-    <row r="105" spans="1:29">
+      <c r="AD104" s="8"/>
+    </row>
+    <row r="105" spans="1:30">
       <c r="A105" s="5" t="s">
         <v>108</v>
       </c>
@@ -6141,8 +6255,9 @@
       <c r="AA105" s="8"/>
       <c r="AB105" s="8"/>
       <c r="AC105" s="8"/>
-    </row>
-    <row r="106" spans="1:29">
+      <c r="AD105" s="8"/>
+    </row>
+    <row r="106" spans="1:30">
       <c r="A106" s="5" t="s">
         <v>109</v>
       </c>
@@ -6174,11 +6289,12 @@
       <c r="AA106" s="8"/>
       <c r="AB106" s="8"/>
       <c r="AC106" s="8"/>
+      <c r="AD106" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:F6" xr:uid="{865A20BB-1F5D-416D-8AD5-2BCD3ABC6B25}">
-      <formula1>$G$6:$DD$6</formula1>
+      <formula1>$G$6:$DE$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6189,7 +6305,7 @@
           <x14:formula1>
             <xm:f>description!$E$6:$I$6</xm:f>
           </x14:formula1>
-          <xm:sqref>B3:AB3</xm:sqref>
+          <xm:sqref>B3:AC3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A60B9CC8-BE80-475D-B087-1A2396777CC1}">
           <x14:formula1>

--- a/data/raw_results/lanupro_vocabulary_general.xlsx
+++ b/data/raw_results/lanupro_vocabulary_general.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45F3CF2-CE6E-4C0F-98B6-15E86D35207F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E6B858-88E0-4B8C-B8D5-EEE2C6A5C119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="279">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -2777,7 +2777,9 @@
       <c r="Y8" s="8"/>
       <c r="Z8" s="8"/>
       <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
+      <c r="AB8" s="8" t="s">
+        <v>117</v>
+      </c>
       <c r="AC8" s="8"/>
       <c r="AD8" s="8"/>
     </row>

--- a/data/raw_results/lanupro_vocabulary_general.xlsx
+++ b/data/raw_results/lanupro_vocabulary_general.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E6B858-88E0-4B8C-B8D5-EEE2C6A5C119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384F1B35-75D4-4EEE-ADC4-87D7F8857D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="280">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -876,6 +876,9 @@
   </si>
   <si>
     <t>test_02</t>
+  </si>
+  <si>
+    <t>test_03</t>
   </si>
 </sst>
 </file>
@@ -2201,7 +2204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB33DE6-D058-433F-9B7D-5598CD0261F2}">
-  <dimension ref="A1:AD106"/>
+  <dimension ref="A1:AE106"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17" style="4" customWidth="1"/>
@@ -2222,12 +2225,12 @@
     <col min="25" max="25" width="16" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.33203125" customWidth="1"/>
-    <col min="29" max="29" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="11.33203125" customWidth="1"/>
+    <col min="30" max="30" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="1" customFormat="1">
+    <row r="1" spans="1:31" s="1" customFormat="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2313,13 +2316,16 @@
         <v>278</v>
       </c>
       <c r="AC1" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="AD1" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:31">
       <c r="A2" s="5" t="s">
         <v>129</v>
       </c>
@@ -2410,8 +2416,11 @@
       <c r="AD2" s="8" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="3" spans="1:30">
+      <c r="AE2" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -2468,8 +2477,9 @@
       <c r="AB3" s="8"/>
       <c r="AC3" s="8"/>
       <c r="AD3" s="8"/>
-    </row>
-    <row r="4" spans="1:30">
+      <c r="AE3" s="8"/>
+    </row>
+    <row r="4" spans="1:31">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
@@ -2526,8 +2536,9 @@
       <c r="AB4" s="8"/>
       <c r="AC4" s="8"/>
       <c r="AD4" s="8"/>
-    </row>
-    <row r="5" spans="1:30" ht="86.4">
+      <c r="AE4" s="8"/>
+    </row>
+    <row r="5" spans="1:31" ht="86.4">
       <c r="A5" s="9" t="s">
         <v>6</v>
       </c>
@@ -2584,14 +2595,15 @@
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
       <c r="AB5" s="10"/>
-      <c r="AC5" s="10" t="s">
+      <c r="AC5" s="10"/>
+      <c r="AD5" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="AD5" s="8" t="s">
+      <c r="AE5" s="8" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" s="5" t="s">
         <v>115</v>
       </c>
@@ -2642,8 +2654,9 @@
       <c r="AB6" s="8"/>
       <c r="AC6" s="8"/>
       <c r="AD6" s="8"/>
-    </row>
-    <row r="7" spans="1:30">
+      <c r="AE6" s="8"/>
+    </row>
+    <row r="7" spans="1:31">
       <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
@@ -2728,14 +2741,15 @@
       <c r="AB7" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="AC7" s="8" t="s">
-        <v>117</v>
-      </c>
+      <c r="AC7" s="8"/>
       <c r="AD7" s="8" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="8" spans="1:30">
+      <c r="AE7" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31">
       <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
@@ -2782,8 +2796,9 @@
       </c>
       <c r="AC8" s="8"/>
       <c r="AD8" s="8"/>
-    </row>
-    <row r="9" spans="1:30">
+      <c r="AE8" s="8"/>
+    </row>
+    <row r="9" spans="1:31">
       <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
@@ -2828,8 +2843,9 @@
       <c r="AB9" s="8"/>
       <c r="AC9" s="8"/>
       <c r="AD9" s="8"/>
-    </row>
-    <row r="10" spans="1:30">
+      <c r="AE9" s="8"/>
+    </row>
+    <row r="10" spans="1:31">
       <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
@@ -2874,8 +2890,9 @@
       <c r="AB10" s="8"/>
       <c r="AC10" s="8"/>
       <c r="AD10" s="8"/>
-    </row>
-    <row r="11" spans="1:30">
+      <c r="AE10" s="8"/>
+    </row>
+    <row r="11" spans="1:31">
       <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
@@ -2918,8 +2935,9 @@
       <c r="AB11" s="8"/>
       <c r="AC11" s="8"/>
       <c r="AD11" s="8"/>
-    </row>
-    <row r="12" spans="1:30">
+      <c r="AE11" s="8"/>
+    </row>
+    <row r="12" spans="1:31">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
@@ -2962,8 +2980,9 @@
       <c r="AB12" s="8"/>
       <c r="AC12" s="8"/>
       <c r="AD12" s="8"/>
-    </row>
-    <row r="13" spans="1:30">
+      <c r="AE12" s="8"/>
+    </row>
+    <row r="13" spans="1:31">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -3004,8 +3023,9 @@
       <c r="AB13" s="8"/>
       <c r="AC13" s="8"/>
       <c r="AD13" s="8"/>
-    </row>
-    <row r="14" spans="1:30">
+      <c r="AE13" s="8"/>
+    </row>
+    <row r="14" spans="1:31">
       <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
@@ -3046,8 +3066,9 @@
       <c r="AB14" s="8"/>
       <c r="AC14" s="8"/>
       <c r="AD14" s="8"/>
-    </row>
-    <row r="15" spans="1:30">
+      <c r="AE14" s="8"/>
+    </row>
+    <row r="15" spans="1:31">
       <c r="A15" s="5" t="s">
         <v>18</v>
       </c>
@@ -3088,8 +3109,9 @@
       <c r="AB15" s="8"/>
       <c r="AC15" s="8"/>
       <c r="AD15" s="8"/>
-    </row>
-    <row r="16" spans="1:30">
+      <c r="AE15" s="8"/>
+    </row>
+    <row r="16" spans="1:31">
       <c r="A16" s="5" t="s">
         <v>19</v>
       </c>
@@ -3130,8 +3152,9 @@
       <c r="AB16" s="8"/>
       <c r="AC16" s="8"/>
       <c r="AD16" s="8"/>
-    </row>
-    <row r="17" spans="1:30">
+      <c r="AE16" s="8"/>
+    </row>
+    <row r="17" spans="1:31">
       <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
@@ -3172,8 +3195,9 @@
       <c r="AB17" s="8"/>
       <c r="AC17" s="8"/>
       <c r="AD17" s="8"/>
-    </row>
-    <row r="18" spans="1:30">
+      <c r="AE17" s="8"/>
+    </row>
+    <row r="18" spans="1:31">
       <c r="A18" s="5" t="s">
         <v>21</v>
       </c>
@@ -3212,8 +3236,9 @@
       <c r="AB18" s="8"/>
       <c r="AC18" s="8"/>
       <c r="AD18" s="8"/>
-    </row>
-    <row r="19" spans="1:30">
+      <c r="AE18" s="8"/>
+    </row>
+    <row r="19" spans="1:31">
       <c r="A19" s="5" t="s">
         <v>22</v>
       </c>
@@ -3252,8 +3277,9 @@
       <c r="AB19" s="8"/>
       <c r="AC19" s="8"/>
       <c r="AD19" s="8"/>
-    </row>
-    <row r="20" spans="1:30">
+      <c r="AE19" s="8"/>
+    </row>
+    <row r="20" spans="1:31">
       <c r="A20" s="5" t="s">
         <v>23</v>
       </c>
@@ -3292,8 +3318,9 @@
       <c r="AB20" s="8"/>
       <c r="AC20" s="8"/>
       <c r="AD20" s="8"/>
-    </row>
-    <row r="21" spans="1:30">
+      <c r="AE20" s="8"/>
+    </row>
+    <row r="21" spans="1:31">
       <c r="A21" s="5" t="s">
         <v>24</v>
       </c>
@@ -3330,8 +3357,9 @@
       <c r="AB21" s="8"/>
       <c r="AC21" s="8"/>
       <c r="AD21" s="8"/>
-    </row>
-    <row r="22" spans="1:30">
+      <c r="AE21" s="8"/>
+    </row>
+    <row r="22" spans="1:31">
       <c r="A22" s="5" t="s">
         <v>25</v>
       </c>
@@ -3368,8 +3396,9 @@
       <c r="AB22" s="8"/>
       <c r="AC22" s="8"/>
       <c r="AD22" s="8"/>
-    </row>
-    <row r="23" spans="1:30">
+      <c r="AE22" s="8"/>
+    </row>
+    <row r="23" spans="1:31">
       <c r="A23" s="5" t="s">
         <v>26</v>
       </c>
@@ -3406,8 +3435,9 @@
       <c r="AB23" s="8"/>
       <c r="AC23" s="8"/>
       <c r="AD23" s="8"/>
-    </row>
-    <row r="24" spans="1:30">
+      <c r="AE23" s="8"/>
+    </row>
+    <row r="24" spans="1:31">
       <c r="A24" s="5" t="s">
         <v>27</v>
       </c>
@@ -3444,8 +3474,9 @@
       <c r="AB24" s="8"/>
       <c r="AC24" s="8"/>
       <c r="AD24" s="8"/>
-    </row>
-    <row r="25" spans="1:30">
+      <c r="AE24" s="8"/>
+    </row>
+    <row r="25" spans="1:31">
       <c r="A25" s="5" t="s">
         <v>28</v>
       </c>
@@ -3482,8 +3513,9 @@
       <c r="AB25" s="8"/>
       <c r="AC25" s="8"/>
       <c r="AD25" s="8"/>
-    </row>
-    <row r="26" spans="1:30">
+      <c r="AE25" s="8"/>
+    </row>
+    <row r="26" spans="1:31">
       <c r="A26" s="5" t="s">
         <v>29</v>
       </c>
@@ -3520,8 +3552,9 @@
       <c r="AB26" s="8"/>
       <c r="AC26" s="8"/>
       <c r="AD26" s="8"/>
-    </row>
-    <row r="27" spans="1:30">
+      <c r="AE26" s="8"/>
+    </row>
+    <row r="27" spans="1:31">
       <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
@@ -3558,8 +3591,9 @@
       <c r="AB27" s="8"/>
       <c r="AC27" s="8"/>
       <c r="AD27" s="8"/>
-    </row>
-    <row r="28" spans="1:30">
+      <c r="AE27" s="8"/>
+    </row>
+    <row r="28" spans="1:31">
       <c r="A28" s="5" t="s">
         <v>31</v>
       </c>
@@ -3596,8 +3630,9 @@
       <c r="AB28" s="8"/>
       <c r="AC28" s="8"/>
       <c r="AD28" s="8"/>
-    </row>
-    <row r="29" spans="1:30">
+      <c r="AE28" s="8"/>
+    </row>
+    <row r="29" spans="1:31">
       <c r="A29" s="5" t="s">
         <v>32</v>
       </c>
@@ -3634,8 +3669,9 @@
       <c r="AB29" s="8"/>
       <c r="AC29" s="8"/>
       <c r="AD29" s="8"/>
-    </row>
-    <row r="30" spans="1:30">
+      <c r="AE29" s="8"/>
+    </row>
+    <row r="30" spans="1:31">
       <c r="A30" s="5" t="s">
         <v>33</v>
       </c>
@@ -3672,8 +3708,9 @@
       <c r="AB30" s="8"/>
       <c r="AC30" s="8"/>
       <c r="AD30" s="8"/>
-    </row>
-    <row r="31" spans="1:30">
+      <c r="AE30" s="8"/>
+    </row>
+    <row r="31" spans="1:31">
       <c r="A31" s="5" t="s">
         <v>34</v>
       </c>
@@ -3710,8 +3747,9 @@
       <c r="AB31" s="8"/>
       <c r="AC31" s="8"/>
       <c r="AD31" s="8"/>
-    </row>
-    <row r="32" spans="1:30">
+      <c r="AE31" s="8"/>
+    </row>
+    <row r="32" spans="1:31">
       <c r="A32" s="5" t="s">
         <v>35</v>
       </c>
@@ -3748,8 +3786,9 @@
       <c r="AB32" s="8"/>
       <c r="AC32" s="8"/>
       <c r="AD32" s="8"/>
-    </row>
-    <row r="33" spans="1:30">
+      <c r="AE32" s="8"/>
+    </row>
+    <row r="33" spans="1:31">
       <c r="A33" s="5" t="s">
         <v>36</v>
       </c>
@@ -3786,8 +3825,9 @@
       <c r="AB33" s="8"/>
       <c r="AC33" s="8"/>
       <c r="AD33" s="8"/>
-    </row>
-    <row r="34" spans="1:30">
+      <c r="AE33" s="8"/>
+    </row>
+    <row r="34" spans="1:31">
       <c r="A34" s="5" t="s">
         <v>37</v>
       </c>
@@ -3824,8 +3864,9 @@
       <c r="AB34" s="8"/>
       <c r="AC34" s="8"/>
       <c r="AD34" s="8"/>
-    </row>
-    <row r="35" spans="1:30">
+      <c r="AE34" s="8"/>
+    </row>
+    <row r="35" spans="1:31">
       <c r="A35" s="5" t="s">
         <v>38</v>
       </c>
@@ -3862,8 +3903,9 @@
       <c r="AB35" s="8"/>
       <c r="AC35" s="8"/>
       <c r="AD35" s="8"/>
-    </row>
-    <row r="36" spans="1:30">
+      <c r="AE35" s="8"/>
+    </row>
+    <row r="36" spans="1:31">
       <c r="A36" s="5" t="s">
         <v>39</v>
       </c>
@@ -3898,8 +3940,9 @@
       <c r="AB36" s="8"/>
       <c r="AC36" s="8"/>
       <c r="AD36" s="8"/>
-    </row>
-    <row r="37" spans="1:30">
+      <c r="AE36" s="8"/>
+    </row>
+    <row r="37" spans="1:31">
       <c r="A37" s="5" t="s">
         <v>40</v>
       </c>
@@ -3934,8 +3977,9 @@
       <c r="AB37" s="8"/>
       <c r="AC37" s="8"/>
       <c r="AD37" s="8"/>
-    </row>
-    <row r="38" spans="1:30">
+      <c r="AE37" s="8"/>
+    </row>
+    <row r="38" spans="1:31">
       <c r="A38" s="5" t="s">
         <v>41</v>
       </c>
@@ -3970,8 +4014,9 @@
       <c r="AB38" s="8"/>
       <c r="AC38" s="8"/>
       <c r="AD38" s="8"/>
-    </row>
-    <row r="39" spans="1:30">
+      <c r="AE38" s="8"/>
+    </row>
+    <row r="39" spans="1:31">
       <c r="A39" s="5" t="s">
         <v>42</v>
       </c>
@@ -4006,8 +4051,9 @@
       <c r="AB39" s="8"/>
       <c r="AC39" s="8"/>
       <c r="AD39" s="8"/>
-    </row>
-    <row r="40" spans="1:30">
+      <c r="AE39" s="8"/>
+    </row>
+    <row r="40" spans="1:31">
       <c r="A40" s="5" t="s">
         <v>43</v>
       </c>
@@ -4042,8 +4088,9 @@
       <c r="AB40" s="8"/>
       <c r="AC40" s="8"/>
       <c r="AD40" s="8"/>
-    </row>
-    <row r="41" spans="1:30">
+      <c r="AE40" s="8"/>
+    </row>
+    <row r="41" spans="1:31">
       <c r="A41" s="5" t="s">
         <v>44</v>
       </c>
@@ -4078,8 +4125,9 @@
       <c r="AB41" s="8"/>
       <c r="AC41" s="8"/>
       <c r="AD41" s="8"/>
-    </row>
-    <row r="42" spans="1:30">
+      <c r="AE41" s="8"/>
+    </row>
+    <row r="42" spans="1:31">
       <c r="A42" s="5" t="s">
         <v>45</v>
       </c>
@@ -4114,8 +4162,9 @@
       <c r="AB42" s="8"/>
       <c r="AC42" s="8"/>
       <c r="AD42" s="8"/>
-    </row>
-    <row r="43" spans="1:30">
+      <c r="AE42" s="8"/>
+    </row>
+    <row r="43" spans="1:31">
       <c r="A43" s="5" t="s">
         <v>46</v>
       </c>
@@ -4150,8 +4199,9 @@
       <c r="AB43" s="8"/>
       <c r="AC43" s="8"/>
       <c r="AD43" s="8"/>
-    </row>
-    <row r="44" spans="1:30">
+      <c r="AE43" s="8"/>
+    </row>
+    <row r="44" spans="1:31">
       <c r="A44" s="5" t="s">
         <v>47</v>
       </c>
@@ -4184,8 +4234,9 @@
       <c r="AB44" s="8"/>
       <c r="AC44" s="8"/>
       <c r="AD44" s="8"/>
-    </row>
-    <row r="45" spans="1:30">
+      <c r="AE44" s="8"/>
+    </row>
+    <row r="45" spans="1:31">
       <c r="A45" s="5" t="s">
         <v>48</v>
       </c>
@@ -4218,8 +4269,9 @@
       <c r="AB45" s="8"/>
       <c r="AC45" s="8"/>
       <c r="AD45" s="8"/>
-    </row>
-    <row r="46" spans="1:30">
+      <c r="AE45" s="8"/>
+    </row>
+    <row r="46" spans="1:31">
       <c r="A46" s="5" t="s">
         <v>49</v>
       </c>
@@ -4252,8 +4304,9 @@
       <c r="AB46" s="8"/>
       <c r="AC46" s="8"/>
       <c r="AD46" s="8"/>
-    </row>
-    <row r="47" spans="1:30">
+      <c r="AE46" s="8"/>
+    </row>
+    <row r="47" spans="1:31">
       <c r="A47" s="5" t="s">
         <v>50</v>
       </c>
@@ -4286,8 +4339,9 @@
       <c r="AB47" s="8"/>
       <c r="AC47" s="8"/>
       <c r="AD47" s="8"/>
-    </row>
-    <row r="48" spans="1:30">
+      <c r="AE47" s="8"/>
+    </row>
+    <row r="48" spans="1:31">
       <c r="A48" s="5" t="s">
         <v>51</v>
       </c>
@@ -4320,8 +4374,9 @@
       <c r="AB48" s="8"/>
       <c r="AC48" s="8"/>
       <c r="AD48" s="8"/>
-    </row>
-    <row r="49" spans="1:30">
+      <c r="AE48" s="8"/>
+    </row>
+    <row r="49" spans="1:31">
       <c r="A49" s="5" t="s">
         <v>52</v>
       </c>
@@ -4354,8 +4409,9 @@
       <c r="AB49" s="8"/>
       <c r="AC49" s="8"/>
       <c r="AD49" s="8"/>
-    </row>
-    <row r="50" spans="1:30">
+      <c r="AE49" s="8"/>
+    </row>
+    <row r="50" spans="1:31">
       <c r="A50" s="5" t="s">
         <v>53</v>
       </c>
@@ -4388,8 +4444,9 @@
       <c r="AB50" s="8"/>
       <c r="AC50" s="8"/>
       <c r="AD50" s="8"/>
-    </row>
-    <row r="51" spans="1:30">
+      <c r="AE50" s="8"/>
+    </row>
+    <row r="51" spans="1:31">
       <c r="A51" s="5" t="s">
         <v>54</v>
       </c>
@@ -4422,8 +4479,9 @@
       <c r="AB51" s="8"/>
       <c r="AC51" s="8"/>
       <c r="AD51" s="8"/>
-    </row>
-    <row r="52" spans="1:30">
+      <c r="AE51" s="8"/>
+    </row>
+    <row r="52" spans="1:31">
       <c r="A52" s="5" t="s">
         <v>55</v>
       </c>
@@ -4456,8 +4514,9 @@
       <c r="AB52" s="8"/>
       <c r="AC52" s="8"/>
       <c r="AD52" s="8"/>
-    </row>
-    <row r="53" spans="1:30">
+      <c r="AE52" s="8"/>
+    </row>
+    <row r="53" spans="1:31">
       <c r="A53" s="5" t="s">
         <v>56</v>
       </c>
@@ -4490,8 +4549,9 @@
       <c r="AB53" s="8"/>
       <c r="AC53" s="8"/>
       <c r="AD53" s="8"/>
-    </row>
-    <row r="54" spans="1:30">
+      <c r="AE53" s="8"/>
+    </row>
+    <row r="54" spans="1:31">
       <c r="A54" s="5" t="s">
         <v>57</v>
       </c>
@@ -4524,8 +4584,9 @@
       <c r="AB54" s="8"/>
       <c r="AC54" s="8"/>
       <c r="AD54" s="8"/>
-    </row>
-    <row r="55" spans="1:30">
+      <c r="AE54" s="8"/>
+    </row>
+    <row r="55" spans="1:31">
       <c r="A55" s="5" t="s">
         <v>58</v>
       </c>
@@ -4558,8 +4619,9 @@
       <c r="AB55" s="8"/>
       <c r="AC55" s="8"/>
       <c r="AD55" s="8"/>
-    </row>
-    <row r="56" spans="1:30">
+      <c r="AE55" s="8"/>
+    </row>
+    <row r="56" spans="1:31">
       <c r="A56" s="5" t="s">
         <v>59</v>
       </c>
@@ -4592,8 +4654,9 @@
       <c r="AB56" s="8"/>
       <c r="AC56" s="8"/>
       <c r="AD56" s="8"/>
-    </row>
-    <row r="57" spans="1:30">
+      <c r="AE56" s="8"/>
+    </row>
+    <row r="57" spans="1:31">
       <c r="A57" s="5" t="s">
         <v>60</v>
       </c>
@@ -4626,8 +4689,9 @@
       <c r="AB57" s="8"/>
       <c r="AC57" s="8"/>
       <c r="AD57" s="8"/>
-    </row>
-    <row r="58" spans="1:30">
+      <c r="AE57" s="8"/>
+    </row>
+    <row r="58" spans="1:31">
       <c r="A58" s="5" t="s">
         <v>61</v>
       </c>
@@ -4660,8 +4724,9 @@
       <c r="AB58" s="8"/>
       <c r="AC58" s="8"/>
       <c r="AD58" s="8"/>
-    </row>
-    <row r="59" spans="1:30">
+      <c r="AE58" s="8"/>
+    </row>
+    <row r="59" spans="1:31">
       <c r="A59" s="5" t="s">
         <v>62</v>
       </c>
@@ -4694,8 +4759,9 @@
       <c r="AB59" s="8"/>
       <c r="AC59" s="8"/>
       <c r="AD59" s="8"/>
-    </row>
-    <row r="60" spans="1:30">
+      <c r="AE59" s="8"/>
+    </row>
+    <row r="60" spans="1:31">
       <c r="A60" s="5" t="s">
         <v>63</v>
       </c>
@@ -4728,8 +4794,9 @@
       <c r="AB60" s="8"/>
       <c r="AC60" s="8"/>
       <c r="AD60" s="8"/>
-    </row>
-    <row r="61" spans="1:30">
+      <c r="AE60" s="8"/>
+    </row>
+    <row r="61" spans="1:31">
       <c r="A61" s="5" t="s">
         <v>64</v>
       </c>
@@ -4762,8 +4829,9 @@
       <c r="AB61" s="8"/>
       <c r="AC61" s="8"/>
       <c r="AD61" s="8"/>
-    </row>
-    <row r="62" spans="1:30">
+      <c r="AE61" s="8"/>
+    </row>
+    <row r="62" spans="1:31">
       <c r="A62" s="5" t="s">
         <v>65</v>
       </c>
@@ -4796,8 +4864,9 @@
       <c r="AB62" s="8"/>
       <c r="AC62" s="8"/>
       <c r="AD62" s="8"/>
-    </row>
-    <row r="63" spans="1:30">
+      <c r="AE62" s="8"/>
+    </row>
+    <row r="63" spans="1:31">
       <c r="A63" s="5" t="s">
         <v>66</v>
       </c>
@@ -4830,8 +4899,9 @@
       <c r="AB63" s="8"/>
       <c r="AC63" s="8"/>
       <c r="AD63" s="8"/>
-    </row>
-    <row r="64" spans="1:30">
+      <c r="AE63" s="8"/>
+    </row>
+    <row r="64" spans="1:31">
       <c r="A64" s="5" t="s">
         <v>67</v>
       </c>
@@ -4864,8 +4934,9 @@
       <c r="AB64" s="8"/>
       <c r="AC64" s="8"/>
       <c r="AD64" s="8"/>
-    </row>
-    <row r="65" spans="1:30">
+      <c r="AE64" s="8"/>
+    </row>
+    <row r="65" spans="1:31">
       <c r="A65" s="5" t="s">
         <v>68</v>
       </c>
@@ -4898,8 +4969,9 @@
       <c r="AB65" s="8"/>
       <c r="AC65" s="8"/>
       <c r="AD65" s="8"/>
-    </row>
-    <row r="66" spans="1:30">
+      <c r="AE65" s="8"/>
+    </row>
+    <row r="66" spans="1:31">
       <c r="A66" s="5" t="s">
         <v>69</v>
       </c>
@@ -4932,8 +5004,9 @@
       <c r="AB66" s="8"/>
       <c r="AC66" s="8"/>
       <c r="AD66" s="8"/>
-    </row>
-    <row r="67" spans="1:30">
+      <c r="AE66" s="8"/>
+    </row>
+    <row r="67" spans="1:31">
       <c r="A67" s="5" t="s">
         <v>70</v>
       </c>
@@ -4966,8 +5039,9 @@
       <c r="AB67" s="8"/>
       <c r="AC67" s="8"/>
       <c r="AD67" s="8"/>
-    </row>
-    <row r="68" spans="1:30">
+      <c r="AE67" s="8"/>
+    </row>
+    <row r="68" spans="1:31">
       <c r="A68" s="5" t="s">
         <v>71</v>
       </c>
@@ -5000,8 +5074,9 @@
       <c r="AB68" s="8"/>
       <c r="AC68" s="8"/>
       <c r="AD68" s="8"/>
-    </row>
-    <row r="69" spans="1:30">
+      <c r="AE68" s="8"/>
+    </row>
+    <row r="69" spans="1:31">
       <c r="A69" s="5" t="s">
         <v>72</v>
       </c>
@@ -5034,8 +5109,9 @@
       <c r="AB69" s="8"/>
       <c r="AC69" s="8"/>
       <c r="AD69" s="8"/>
-    </row>
-    <row r="70" spans="1:30">
+      <c r="AE69" s="8"/>
+    </row>
+    <row r="70" spans="1:31">
       <c r="A70" s="5" t="s">
         <v>73</v>
       </c>
@@ -5068,8 +5144,9 @@
       <c r="AB70" s="8"/>
       <c r="AC70" s="8"/>
       <c r="AD70" s="8"/>
-    </row>
-    <row r="71" spans="1:30">
+      <c r="AE70" s="8"/>
+    </row>
+    <row r="71" spans="1:31">
       <c r="A71" s="5" t="s">
         <v>74</v>
       </c>
@@ -5102,8 +5179,9 @@
       <c r="AB71" s="8"/>
       <c r="AC71" s="8"/>
       <c r="AD71" s="8"/>
-    </row>
-    <row r="72" spans="1:30">
+      <c r="AE71" s="8"/>
+    </row>
+    <row r="72" spans="1:31">
       <c r="A72" s="5" t="s">
         <v>75</v>
       </c>
@@ -5136,8 +5214,9 @@
       <c r="AB72" s="8"/>
       <c r="AC72" s="8"/>
       <c r="AD72" s="8"/>
-    </row>
-    <row r="73" spans="1:30">
+      <c r="AE72" s="8"/>
+    </row>
+    <row r="73" spans="1:31">
       <c r="A73" s="5" t="s">
         <v>76</v>
       </c>
@@ -5170,8 +5249,9 @@
       <c r="AB73" s="8"/>
       <c r="AC73" s="8"/>
       <c r="AD73" s="8"/>
-    </row>
-    <row r="74" spans="1:30">
+      <c r="AE73" s="8"/>
+    </row>
+    <row r="74" spans="1:31">
       <c r="A74" s="5" t="s">
         <v>77</v>
       </c>
@@ -5204,8 +5284,9 @@
       <c r="AB74" s="8"/>
       <c r="AC74" s="8"/>
       <c r="AD74" s="8"/>
-    </row>
-    <row r="75" spans="1:30">
+      <c r="AE74" s="8"/>
+    </row>
+    <row r="75" spans="1:31">
       <c r="A75" s="5" t="s">
         <v>78</v>
       </c>
@@ -5238,8 +5319,9 @@
       <c r="AB75" s="8"/>
       <c r="AC75" s="8"/>
       <c r="AD75" s="8"/>
-    </row>
-    <row r="76" spans="1:30">
+      <c r="AE75" s="8"/>
+    </row>
+    <row r="76" spans="1:31">
       <c r="A76" s="5" t="s">
         <v>79</v>
       </c>
@@ -5272,8 +5354,9 @@
       <c r="AB76" s="8"/>
       <c r="AC76" s="8"/>
       <c r="AD76" s="8"/>
-    </row>
-    <row r="77" spans="1:30">
+      <c r="AE76" s="8"/>
+    </row>
+    <row r="77" spans="1:31">
       <c r="A77" s="5" t="s">
         <v>80</v>
       </c>
@@ -5306,8 +5389,9 @@
       <c r="AB77" s="8"/>
       <c r="AC77" s="8"/>
       <c r="AD77" s="8"/>
-    </row>
-    <row r="78" spans="1:30">
+      <c r="AE77" s="8"/>
+    </row>
+    <row r="78" spans="1:31">
       <c r="A78" s="5" t="s">
         <v>81</v>
       </c>
@@ -5340,8 +5424,9 @@
       <c r="AB78" s="8"/>
       <c r="AC78" s="8"/>
       <c r="AD78" s="8"/>
-    </row>
-    <row r="79" spans="1:30">
+      <c r="AE78" s="8"/>
+    </row>
+    <row r="79" spans="1:31">
       <c r="A79" s="5" t="s">
         <v>82</v>
       </c>
@@ -5374,8 +5459,9 @@
       <c r="AB79" s="8"/>
       <c r="AC79" s="8"/>
       <c r="AD79" s="8"/>
-    </row>
-    <row r="80" spans="1:30">
+      <c r="AE79" s="8"/>
+    </row>
+    <row r="80" spans="1:31">
       <c r="A80" s="5" t="s">
         <v>83</v>
       </c>
@@ -5408,8 +5494,9 @@
       <c r="AB80" s="8"/>
       <c r="AC80" s="8"/>
       <c r="AD80" s="8"/>
-    </row>
-    <row r="81" spans="1:30">
+      <c r="AE80" s="8"/>
+    </row>
+    <row r="81" spans="1:31">
       <c r="A81" s="5" t="s">
         <v>84</v>
       </c>
@@ -5442,8 +5529,9 @@
       <c r="AB81" s="8"/>
       <c r="AC81" s="8"/>
       <c r="AD81" s="8"/>
-    </row>
-    <row r="82" spans="1:30">
+      <c r="AE81" s="8"/>
+    </row>
+    <row r="82" spans="1:31">
       <c r="A82" s="5" t="s">
         <v>85</v>
       </c>
@@ -5476,8 +5564,9 @@
       <c r="AB82" s="8"/>
       <c r="AC82" s="8"/>
       <c r="AD82" s="8"/>
-    </row>
-    <row r="83" spans="1:30">
+      <c r="AE82" s="8"/>
+    </row>
+    <row r="83" spans="1:31">
       <c r="A83" s="5" t="s">
         <v>86</v>
       </c>
@@ -5510,8 +5599,9 @@
       <c r="AB83" s="8"/>
       <c r="AC83" s="8"/>
       <c r="AD83" s="8"/>
-    </row>
-    <row r="84" spans="1:30">
+      <c r="AE83" s="8"/>
+    </row>
+    <row r="84" spans="1:31">
       <c r="A84" s="5" t="s">
         <v>87</v>
       </c>
@@ -5544,8 +5634,9 @@
       <c r="AB84" s="8"/>
       <c r="AC84" s="8"/>
       <c r="AD84" s="8"/>
-    </row>
-    <row r="85" spans="1:30">
+      <c r="AE84" s="8"/>
+    </row>
+    <row r="85" spans="1:31">
       <c r="A85" s="5" t="s">
         <v>88</v>
       </c>
@@ -5578,8 +5669,9 @@
       <c r="AB85" s="8"/>
       <c r="AC85" s="8"/>
       <c r="AD85" s="8"/>
-    </row>
-    <row r="86" spans="1:30">
+      <c r="AE85" s="8"/>
+    </row>
+    <row r="86" spans="1:31">
       <c r="A86" s="5" t="s">
         <v>89</v>
       </c>
@@ -5612,8 +5704,9 @@
       <c r="AB86" s="8"/>
       <c r="AC86" s="8"/>
       <c r="AD86" s="8"/>
-    </row>
-    <row r="87" spans="1:30">
+      <c r="AE86" s="8"/>
+    </row>
+    <row r="87" spans="1:31">
       <c r="A87" s="5" t="s">
         <v>90</v>
       </c>
@@ -5646,8 +5739,9 @@
       <c r="AB87" s="8"/>
       <c r="AC87" s="8"/>
       <c r="AD87" s="8"/>
-    </row>
-    <row r="88" spans="1:30">
+      <c r="AE87" s="8"/>
+    </row>
+    <row r="88" spans="1:31">
       <c r="A88" s="5" t="s">
         <v>91</v>
       </c>
@@ -5680,8 +5774,9 @@
       <c r="AB88" s="8"/>
       <c r="AC88" s="8"/>
       <c r="AD88" s="8"/>
-    </row>
-    <row r="89" spans="1:30">
+      <c r="AE88" s="8"/>
+    </row>
+    <row r="89" spans="1:31">
       <c r="A89" s="5" t="s">
         <v>92</v>
       </c>
@@ -5714,8 +5809,9 @@
       <c r="AB89" s="8"/>
       <c r="AC89" s="8"/>
       <c r="AD89" s="8"/>
-    </row>
-    <row r="90" spans="1:30">
+      <c r="AE89" s="8"/>
+    </row>
+    <row r="90" spans="1:31">
       <c r="A90" s="5" t="s">
         <v>93</v>
       </c>
@@ -5748,8 +5844,9 @@
       <c r="AB90" s="8"/>
       <c r="AC90" s="8"/>
       <c r="AD90" s="8"/>
-    </row>
-    <row r="91" spans="1:30">
+      <c r="AE90" s="8"/>
+    </row>
+    <row r="91" spans="1:31">
       <c r="A91" s="5" t="s">
         <v>94</v>
       </c>
@@ -5782,8 +5879,9 @@
       <c r="AB91" s="8"/>
       <c r="AC91" s="8"/>
       <c r="AD91" s="8"/>
-    </row>
-    <row r="92" spans="1:30">
+      <c r="AE91" s="8"/>
+    </row>
+    <row r="92" spans="1:31">
       <c r="A92" s="5" t="s">
         <v>95</v>
       </c>
@@ -5816,8 +5914,9 @@
       <c r="AB92" s="8"/>
       <c r="AC92" s="8"/>
       <c r="AD92" s="8"/>
-    </row>
-    <row r="93" spans="1:30">
+      <c r="AE92" s="8"/>
+    </row>
+    <row r="93" spans="1:31">
       <c r="A93" s="5" t="s">
         <v>96</v>
       </c>
@@ -5850,8 +5949,9 @@
       <c r="AB93" s="8"/>
       <c r="AC93" s="8"/>
       <c r="AD93" s="8"/>
-    </row>
-    <row r="94" spans="1:30">
+      <c r="AE93" s="8"/>
+    </row>
+    <row r="94" spans="1:31">
       <c r="A94" s="5" t="s">
         <v>97</v>
       </c>
@@ -5884,8 +5984,9 @@
       <c r="AB94" s="8"/>
       <c r="AC94" s="8"/>
       <c r="AD94" s="8"/>
-    </row>
-    <row r="95" spans="1:30">
+      <c r="AE94" s="8"/>
+    </row>
+    <row r="95" spans="1:31">
       <c r="A95" s="5" t="s">
         <v>98</v>
       </c>
@@ -5918,8 +6019,9 @@
       <c r="AB95" s="8"/>
       <c r="AC95" s="8"/>
       <c r="AD95" s="8"/>
-    </row>
-    <row r="96" spans="1:30">
+      <c r="AE95" s="8"/>
+    </row>
+    <row r="96" spans="1:31">
       <c r="A96" s="5" t="s">
         <v>99</v>
       </c>
@@ -5952,8 +6054,9 @@
       <c r="AB96" s="8"/>
       <c r="AC96" s="8"/>
       <c r="AD96" s="8"/>
-    </row>
-    <row r="97" spans="1:30">
+      <c r="AE96" s="8"/>
+    </row>
+    <row r="97" spans="1:31">
       <c r="A97" s="5" t="s">
         <v>100</v>
       </c>
@@ -5986,8 +6089,9 @@
       <c r="AB97" s="8"/>
       <c r="AC97" s="8"/>
       <c r="AD97" s="8"/>
-    </row>
-    <row r="98" spans="1:30">
+      <c r="AE97" s="8"/>
+    </row>
+    <row r="98" spans="1:31">
       <c r="A98" s="5" t="s">
         <v>101</v>
       </c>
@@ -6020,8 +6124,9 @@
       <c r="AB98" s="8"/>
       <c r="AC98" s="8"/>
       <c r="AD98" s="8"/>
-    </row>
-    <row r="99" spans="1:30">
+      <c r="AE98" s="8"/>
+    </row>
+    <row r="99" spans="1:31">
       <c r="A99" s="5" t="s">
         <v>102</v>
       </c>
@@ -6054,8 +6159,9 @@
       <c r="AB99" s="8"/>
       <c r="AC99" s="8"/>
       <c r="AD99" s="8"/>
-    </row>
-    <row r="100" spans="1:30">
+      <c r="AE99" s="8"/>
+    </row>
+    <row r="100" spans="1:31">
       <c r="A100" s="5" t="s">
         <v>103</v>
       </c>
@@ -6088,8 +6194,9 @@
       <c r="AB100" s="8"/>
       <c r="AC100" s="8"/>
       <c r="AD100" s="8"/>
-    </row>
-    <row r="101" spans="1:30">
+      <c r="AE100" s="8"/>
+    </row>
+    <row r="101" spans="1:31">
       <c r="A101" s="5" t="s">
         <v>104</v>
       </c>
@@ -6122,8 +6229,9 @@
       <c r="AB101" s="8"/>
       <c r="AC101" s="8"/>
       <c r="AD101" s="8"/>
-    </row>
-    <row r="102" spans="1:30">
+      <c r="AE101" s="8"/>
+    </row>
+    <row r="102" spans="1:31">
       <c r="A102" s="5" t="s">
         <v>105</v>
       </c>
@@ -6156,8 +6264,9 @@
       <c r="AB102" s="8"/>
       <c r="AC102" s="8"/>
       <c r="AD102" s="8"/>
-    </row>
-    <row r="103" spans="1:30">
+      <c r="AE102" s="8"/>
+    </row>
+    <row r="103" spans="1:31">
       <c r="A103" s="5" t="s">
         <v>106</v>
       </c>
@@ -6190,8 +6299,9 @@
       <c r="AB103" s="8"/>
       <c r="AC103" s="8"/>
       <c r="AD103" s="8"/>
-    </row>
-    <row r="104" spans="1:30">
+      <c r="AE103" s="8"/>
+    </row>
+    <row r="104" spans="1:31">
       <c r="A104" s="5" t="s">
         <v>107</v>
       </c>
@@ -6224,8 +6334,9 @@
       <c r="AB104" s="8"/>
       <c r="AC104" s="8"/>
       <c r="AD104" s="8"/>
-    </row>
-    <row r="105" spans="1:30">
+      <c r="AE104" s="8"/>
+    </row>
+    <row r="105" spans="1:31">
       <c r="A105" s="5" t="s">
         <v>108</v>
       </c>
@@ -6258,8 +6369,9 @@
       <c r="AB105" s="8"/>
       <c r="AC105" s="8"/>
       <c r="AD105" s="8"/>
-    </row>
-    <row r="106" spans="1:30">
+      <c r="AE105" s="8"/>
+    </row>
+    <row r="106" spans="1:31">
       <c r="A106" s="5" t="s">
         <v>109</v>
       </c>
@@ -6292,11 +6404,12 @@
       <c r="AB106" s="8"/>
       <c r="AC106" s="8"/>
       <c r="AD106" s="8"/>
+      <c r="AE106" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:F6" xr:uid="{865A20BB-1F5D-416D-8AD5-2BCD3ABC6B25}">
-      <formula1>$G$6:$DE$6</formula1>
+      <formula1>$G$6:$DF$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6307,7 +6420,7 @@
           <x14:formula1>
             <xm:f>description!$E$6:$I$6</xm:f>
           </x14:formula1>
-          <xm:sqref>B3:AC3</xm:sqref>
+          <xm:sqref>B3:AD3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A60B9CC8-BE80-475D-B087-1A2396777CC1}">
           <x14:formula1>

--- a/data/raw_results/lanupro_vocabulary_general.xlsx
+++ b/data/raw_results/lanupro_vocabulary_general.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384F1B35-75D4-4EEE-ADC4-87D7F8857D03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3979118-5C9D-4A38-BE91-1AE5A8F77419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="279">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -876,9 +876,6 @@
   </si>
   <si>
     <t>test_02</t>
-  </si>
-  <si>
-    <t>test_03</t>
   </si>
 </sst>
 </file>
@@ -2222,10 +2219,11 @@
     <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="22.5546875" customWidth="1"/>
     <col min="24" max="24" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="11.33203125" customWidth="1"/>
+    <col min="25" max="25" width="19.88671875" customWidth="1"/>
+    <col min="26" max="26" width="16" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.33203125" customWidth="1"/>
     <col min="30" max="30" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="8.21875" bestFit="1" customWidth="1"/>
   </cols>
@@ -2304,19 +2302,19 @@
         <v>258</v>
       </c>
       <c r="Y1" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z1" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>278</v>
-      </c>
-      <c r="AC1" s="6" t="s">
-        <v>279</v>
       </c>
       <c r="AD1" s="6" t="s">
         <v>262</v>
@@ -2398,17 +2396,15 @@
       <c r="X2" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="Y2" s="8" t="s">
-        <v>117</v>
-      </c>
+      <c r="Y2" s="8"/>
       <c r="Z2" s="8" t="s">
         <v>117</v>
       </c>
       <c r="AA2" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AB2" s="8" t="s">
         <v>273</v>
-      </c>
-      <c r="AB2" s="8" t="s">
-        <v>117</v>
       </c>
       <c r="AC2" s="8" t="s">
         <v>117</v>
@@ -2729,9 +2725,7 @@
       <c r="X7" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="Y7" s="8" t="s">
-        <v>117</v>
-      </c>
+      <c r="Y7" s="8"/>
       <c r="Z7" s="8" t="s">
         <v>117</v>
       </c>
@@ -2741,7 +2735,9 @@
       <c r="AB7" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="8" t="s">
+        <v>117</v>
+      </c>
       <c r="AD7" s="8" t="s">
         <v>117</v>
       </c>
@@ -2791,10 +2787,10 @@
       <c r="Y8" s="8"/>
       <c r="Z8" s="8"/>
       <c r="AA8" s="8"/>
-      <c r="AB8" s="8" t="s">
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="AC8" s="8"/>
       <c r="AD8" s="8"/>
       <c r="AE8" s="8"/>
     </row>
@@ -6416,17 +6412,17 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A60B9CC8-BE80-475D-B087-1A2396777CC1}">
+          <x14:formula1>
+            <xm:f>description!$E$7:$H$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>B4:Q4</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5D11CD02-4B1B-4864-99D9-48419F1D75FF}">
           <x14:formula1>
             <xm:f>description!$E$6:$I$6</xm:f>
           </x14:formula1>
           <xm:sqref>B3:AD3</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A60B9CC8-BE80-475D-B087-1A2396777CC1}">
-          <x14:formula1>
-            <xm:f>description!$E$7:$H$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>B4:Q4</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/raw_results/lanupro_vocabulary_general.xlsx
+++ b/data/raw_results/lanupro_vocabulary_general.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3979118-5C9D-4A38-BE91-1AE5A8F77419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41FFF019-06BE-4ED1-B53C-FB92AE6FC931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="280">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -876,6 +876,9 @@
   </si>
   <si>
     <t>test_02</t>
+  </si>
+  <si>
+    <t>test_field_bis</t>
   </si>
 </sst>
 </file>
@@ -2201,7 +2204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB33DE6-D058-433F-9B7D-5598CD0261F2}">
-  <dimension ref="A1:AE106"/>
+  <dimension ref="A1:AF106"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17" style="4" customWidth="1"/>
@@ -2217,18 +2220,18 @@
     <col min="20" max="20" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="22.5546875" customWidth="1"/>
-    <col min="24" max="24" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.88671875" customWidth="1"/>
-    <col min="26" max="26" width="16" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.33203125" customWidth="1"/>
-    <col min="30" max="30" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="22.5546875" customWidth="1"/>
+    <col min="25" max="25" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.88671875" customWidth="1"/>
+    <col min="27" max="27" width="16" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.33203125" customWidth="1"/>
+    <col min="31" max="31" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="1" customFormat="1">
+    <row r="1" spans="1:32" s="1" customFormat="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2298,32 +2301,35 @@
       <c r="W1" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="X1" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="Y1" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:32">
       <c r="A2" s="5" t="s">
         <v>129</v>
       </c>
@@ -2393,21 +2399,19 @@
       <c r="W2" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="X2" s="8" t="s">
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8" t="s">
-        <v>117</v>
-      </c>
+      <c r="Z2" s="8"/>
       <c r="AA2" s="8" t="s">
         <v>117</v>
       </c>
       <c r="AB2" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="AC2" s="8" t="s">
         <v>273</v>
-      </c>
-      <c r="AC2" s="8" t="s">
-        <v>117</v>
       </c>
       <c r="AD2" s="8" t="s">
         <v>117</v>
@@ -2415,8 +2419,11 @@
       <c r="AE2" s="8" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="3" spans="1:31">
+      <c r="AF2" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
@@ -2474,8 +2481,9 @@
       <c r="AC3" s="8"/>
       <c r="AD3" s="8"/>
       <c r="AE3" s="8"/>
-    </row>
-    <row r="4" spans="1:31">
+      <c r="AF3" s="8"/>
+    </row>
+    <row r="4" spans="1:32">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
@@ -2533,8 +2541,9 @@
       <c r="AC4" s="8"/>
       <c r="AD4" s="8"/>
       <c r="AE4" s="8"/>
-    </row>
-    <row r="5" spans="1:31" ht="86.4">
+      <c r="AF4" s="8"/>
+    </row>
+    <row r="5" spans="1:32" ht="86.4">
       <c r="A5" s="9" t="s">
         <v>6</v>
       </c>
@@ -2586,20 +2595,21 @@
       <c r="U5" s="10"/>
       <c r="V5" s="10"/>
       <c r="W5" s="11"/>
-      <c r="X5" s="10"/>
+      <c r="X5" s="11"/>
       <c r="Y5" s="10"/>
       <c r="Z5" s="10"/>
       <c r="AA5" s="10"/>
       <c r="AB5" s="10"/>
       <c r="AC5" s="10"/>
-      <c r="AD5" s="10" t="s">
+      <c r="AD5" s="10"/>
+      <c r="AE5" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="AE5" s="8" t="s">
+      <c r="AF5" s="8" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" s="5" t="s">
         <v>115</v>
       </c>
@@ -2651,8 +2661,9 @@
       <c r="AC6" s="8"/>
       <c r="AD6" s="8"/>
       <c r="AE6" s="8"/>
-    </row>
-    <row r="7" spans="1:31">
+      <c r="AF6" s="8"/>
+    </row>
+    <row r="7" spans="1:32">
       <c r="A7" s="5" t="s">
         <v>10</v>
       </c>
@@ -2722,13 +2733,11 @@
       <c r="W7" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="X7" s="8" t="s">
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8" t="s">
-        <v>117</v>
-      </c>
+      <c r="Z7" s="8"/>
       <c r="AA7" s="8" t="s">
         <v>117</v>
       </c>
@@ -2744,8 +2753,11 @@
       <c r="AE7" s="8" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="8" spans="1:31">
+      <c r="AF7" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32">
       <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
@@ -2788,13 +2800,14 @@
       <c r="Z8" s="8"/>
       <c r="AA8" s="8"/>
       <c r="AB8" s="8"/>
-      <c r="AC8" s="8" t="s">
+      <c r="AC8" s="8"/>
+      <c r="AD8" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="AD8" s="8"/>
       <c r="AE8" s="8"/>
-    </row>
-    <row r="9" spans="1:31">
+      <c r="AF8" s="8"/>
+    </row>
+    <row r="9" spans="1:32">
       <c r="A9" s="5" t="s">
         <v>12</v>
       </c>
@@ -2840,8 +2853,9 @@
       <c r="AC9" s="8"/>
       <c r="AD9" s="8"/>
       <c r="AE9" s="8"/>
-    </row>
-    <row r="10" spans="1:31">
+      <c r="AF9" s="8"/>
+    </row>
+    <row r="10" spans="1:32">
       <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
@@ -2887,8 +2901,9 @@
       <c r="AC10" s="8"/>
       <c r="AD10" s="8"/>
       <c r="AE10" s="8"/>
-    </row>
-    <row r="11" spans="1:31">
+      <c r="AF10" s="8"/>
+    </row>
+    <row r="11" spans="1:32">
       <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
@@ -2932,8 +2947,9 @@
       <c r="AC11" s="8"/>
       <c r="AD11" s="8"/>
       <c r="AE11" s="8"/>
-    </row>
-    <row r="12" spans="1:31">
+      <c r="AF11" s="8"/>
+    </row>
+    <row r="12" spans="1:32">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
@@ -2977,8 +2993,9 @@
       <c r="AC12" s="8"/>
       <c r="AD12" s="8"/>
       <c r="AE12" s="8"/>
-    </row>
-    <row r="13" spans="1:31">
+      <c r="AF12" s="8"/>
+    </row>
+    <row r="13" spans="1:32">
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
@@ -3020,8 +3037,9 @@
       <c r="AC13" s="8"/>
       <c r="AD13" s="8"/>
       <c r="AE13" s="8"/>
-    </row>
-    <row r="14" spans="1:31">
+      <c r="AF13" s="8"/>
+    </row>
+    <row r="14" spans="1:32">
       <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
@@ -3063,8 +3081,9 @@
       <c r="AC14" s="8"/>
       <c r="AD14" s="8"/>
       <c r="AE14" s="8"/>
-    </row>
-    <row r="15" spans="1:31">
+      <c r="AF14" s="8"/>
+    </row>
+    <row r="15" spans="1:32">
       <c r="A15" s="5" t="s">
         <v>18</v>
       </c>
@@ -3106,8 +3125,9 @@
       <c r="AC15" s="8"/>
       <c r="AD15" s="8"/>
       <c r="AE15" s="8"/>
-    </row>
-    <row r="16" spans="1:31">
+      <c r="AF15" s="8"/>
+    </row>
+    <row r="16" spans="1:32">
       <c r="A16" s="5" t="s">
         <v>19</v>
       </c>
@@ -3149,8 +3169,9 @@
       <c r="AC16" s="8"/>
       <c r="AD16" s="8"/>
       <c r="AE16" s="8"/>
-    </row>
-    <row r="17" spans="1:31">
+      <c r="AF16" s="8"/>
+    </row>
+    <row r="17" spans="1:32">
       <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
@@ -3192,8 +3213,9 @@
       <c r="AC17" s="8"/>
       <c r="AD17" s="8"/>
       <c r="AE17" s="8"/>
-    </row>
-    <row r="18" spans="1:31">
+      <c r="AF17" s="8"/>
+    </row>
+    <row r="18" spans="1:32">
       <c r="A18" s="5" t="s">
         <v>21</v>
       </c>
@@ -3233,8 +3255,9 @@
       <c r="AC18" s="8"/>
       <c r="AD18" s="8"/>
       <c r="AE18" s="8"/>
-    </row>
-    <row r="19" spans="1:31">
+      <c r="AF18" s="8"/>
+    </row>
+    <row r="19" spans="1:32">
       <c r="A19" s="5" t="s">
         <v>22</v>
       </c>
@@ -3274,8 +3297,9 @@
       <c r="AC19" s="8"/>
       <c r="AD19" s="8"/>
       <c r="AE19" s="8"/>
-    </row>
-    <row r="20" spans="1:31">
+      <c r="AF19" s="8"/>
+    </row>
+    <row r="20" spans="1:32">
       <c r="A20" s="5" t="s">
         <v>23</v>
       </c>
@@ -3315,8 +3339,9 @@
       <c r="AC20" s="8"/>
       <c r="AD20" s="8"/>
       <c r="AE20" s="8"/>
-    </row>
-    <row r="21" spans="1:31">
+      <c r="AF20" s="8"/>
+    </row>
+    <row r="21" spans="1:32">
       <c r="A21" s="5" t="s">
         <v>24</v>
       </c>
@@ -3354,8 +3379,9 @@
       <c r="AC21" s="8"/>
       <c r="AD21" s="8"/>
       <c r="AE21" s="8"/>
-    </row>
-    <row r="22" spans="1:31">
+      <c r="AF21" s="8"/>
+    </row>
+    <row r="22" spans="1:32">
       <c r="A22" s="5" t="s">
         <v>25</v>
       </c>
@@ -3393,8 +3419,9 @@
       <c r="AC22" s="8"/>
       <c r="AD22" s="8"/>
       <c r="AE22" s="8"/>
-    </row>
-    <row r="23" spans="1:31">
+      <c r="AF22" s="8"/>
+    </row>
+    <row r="23" spans="1:32">
       <c r="A23" s="5" t="s">
         <v>26</v>
       </c>
@@ -3432,8 +3459,9 @@
       <c r="AC23" s="8"/>
       <c r="AD23" s="8"/>
       <c r="AE23" s="8"/>
-    </row>
-    <row r="24" spans="1:31">
+      <c r="AF23" s="8"/>
+    </row>
+    <row r="24" spans="1:32">
       <c r="A24" s="5" t="s">
         <v>27</v>
       </c>
@@ -3471,8 +3499,9 @@
       <c r="AC24" s="8"/>
       <c r="AD24" s="8"/>
       <c r="AE24" s="8"/>
-    </row>
-    <row r="25" spans="1:31">
+      <c r="AF24" s="8"/>
+    </row>
+    <row r="25" spans="1:32">
       <c r="A25" s="5" t="s">
         <v>28</v>
       </c>
@@ -3510,8 +3539,9 @@
       <c r="AC25" s="8"/>
       <c r="AD25" s="8"/>
       <c r="AE25" s="8"/>
-    </row>
-    <row r="26" spans="1:31">
+      <c r="AF25" s="8"/>
+    </row>
+    <row r="26" spans="1:32">
       <c r="A26" s="5" t="s">
         <v>29</v>
       </c>
@@ -3549,8 +3579,9 @@
       <c r="AC26" s="8"/>
       <c r="AD26" s="8"/>
       <c r="AE26" s="8"/>
-    </row>
-    <row r="27" spans="1:31">
+      <c r="AF26" s="8"/>
+    </row>
+    <row r="27" spans="1:32">
       <c r="A27" s="5" t="s">
         <v>30</v>
       </c>
@@ -3588,8 +3619,9 @@
       <c r="AC27" s="8"/>
       <c r="AD27" s="8"/>
       <c r="AE27" s="8"/>
-    </row>
-    <row r="28" spans="1:31">
+      <c r="AF27" s="8"/>
+    </row>
+    <row r="28" spans="1:32">
       <c r="A28" s="5" t="s">
         <v>31</v>
       </c>
@@ -3627,8 +3659,9 @@
       <c r="AC28" s="8"/>
       <c r="AD28" s="8"/>
       <c r="AE28" s="8"/>
-    </row>
-    <row r="29" spans="1:31">
+      <c r="AF28" s="8"/>
+    </row>
+    <row r="29" spans="1:32">
       <c r="A29" s="5" t="s">
         <v>32</v>
       </c>
@@ -3666,8 +3699,9 @@
       <c r="AC29" s="8"/>
       <c r="AD29" s="8"/>
       <c r="AE29" s="8"/>
-    </row>
-    <row r="30" spans="1:31">
+      <c r="AF29" s="8"/>
+    </row>
+    <row r="30" spans="1:32">
       <c r="A30" s="5" t="s">
         <v>33</v>
       </c>
@@ -3705,8 +3739,9 @@
       <c r="AC30" s="8"/>
       <c r="AD30" s="8"/>
       <c r="AE30" s="8"/>
-    </row>
-    <row r="31" spans="1:31">
+      <c r="AF30" s="8"/>
+    </row>
+    <row r="31" spans="1:32">
       <c r="A31" s="5" t="s">
         <v>34</v>
       </c>
@@ -3744,8 +3779,9 @@
       <c r="AC31" s="8"/>
       <c r="AD31" s="8"/>
       <c r="AE31" s="8"/>
-    </row>
-    <row r="32" spans="1:31">
+      <c r="AF31" s="8"/>
+    </row>
+    <row r="32" spans="1:32">
       <c r="A32" s="5" t="s">
         <v>35</v>
       </c>
@@ -3783,8 +3819,9 @@
       <c r="AC32" s="8"/>
       <c r="AD32" s="8"/>
       <c r="AE32" s="8"/>
-    </row>
-    <row r="33" spans="1:31">
+      <c r="AF32" s="8"/>
+    </row>
+    <row r="33" spans="1:32">
       <c r="A33" s="5" t="s">
         <v>36</v>
       </c>
@@ -3822,8 +3859,9 @@
       <c r="AC33" s="8"/>
       <c r="AD33" s="8"/>
       <c r="AE33" s="8"/>
-    </row>
-    <row r="34" spans="1:31">
+      <c r="AF33" s="8"/>
+    </row>
+    <row r="34" spans="1:32">
       <c r="A34" s="5" t="s">
         <v>37</v>
       </c>
@@ -3861,8 +3899,9 @@
       <c r="AC34" s="8"/>
       <c r="AD34" s="8"/>
       <c r="AE34" s="8"/>
-    </row>
-    <row r="35" spans="1:31">
+      <c r="AF34" s="8"/>
+    </row>
+    <row r="35" spans="1:32">
       <c r="A35" s="5" t="s">
         <v>38</v>
       </c>
@@ -3900,8 +3939,9 @@
       <c r="AC35" s="8"/>
       <c r="AD35" s="8"/>
       <c r="AE35" s="8"/>
-    </row>
-    <row r="36" spans="1:31">
+      <c r="AF35" s="8"/>
+    </row>
+    <row r="36" spans="1:32">
       <c r="A36" s="5" t="s">
         <v>39</v>
       </c>
@@ -3937,8 +3977,9 @@
       <c r="AC36" s="8"/>
       <c r="AD36" s="8"/>
       <c r="AE36" s="8"/>
-    </row>
-    <row r="37" spans="1:31">
+      <c r="AF36" s="8"/>
+    </row>
+    <row r="37" spans="1:32">
       <c r="A37" s="5" t="s">
         <v>40</v>
       </c>
@@ -3974,8 +4015,9 @@
       <c r="AC37" s="8"/>
       <c r="AD37" s="8"/>
       <c r="AE37" s="8"/>
-    </row>
-    <row r="38" spans="1:31">
+      <c r="AF37" s="8"/>
+    </row>
+    <row r="38" spans="1:32">
       <c r="A38" s="5" t="s">
         <v>41</v>
       </c>
@@ -4011,8 +4053,9 @@
       <c r="AC38" s="8"/>
       <c r="AD38" s="8"/>
       <c r="AE38" s="8"/>
-    </row>
-    <row r="39" spans="1:31">
+      <c r="AF38" s="8"/>
+    </row>
+    <row r="39" spans="1:32">
       <c r="A39" s="5" t="s">
         <v>42</v>
       </c>
@@ -4048,8 +4091,9 @@
       <c r="AC39" s="8"/>
       <c r="AD39" s="8"/>
       <c r="AE39" s="8"/>
-    </row>
-    <row r="40" spans="1:31">
+      <c r="AF39" s="8"/>
+    </row>
+    <row r="40" spans="1:32">
       <c r="A40" s="5" t="s">
         <v>43</v>
       </c>
@@ -4085,8 +4129,9 @@
       <c r="AC40" s="8"/>
       <c r="AD40" s="8"/>
       <c r="AE40" s="8"/>
-    </row>
-    <row r="41" spans="1:31">
+      <c r="AF40" s="8"/>
+    </row>
+    <row r="41" spans="1:32">
       <c r="A41" s="5" t="s">
         <v>44</v>
       </c>
@@ -4122,8 +4167,9 @@
       <c r="AC41" s="8"/>
       <c r="AD41" s="8"/>
       <c r="AE41" s="8"/>
-    </row>
-    <row r="42" spans="1:31">
+      <c r="AF41" s="8"/>
+    </row>
+    <row r="42" spans="1:32">
       <c r="A42" s="5" t="s">
         <v>45</v>
       </c>
@@ -4159,8 +4205,9 @@
       <c r="AC42" s="8"/>
       <c r="AD42" s="8"/>
       <c r="AE42" s="8"/>
-    </row>
-    <row r="43" spans="1:31">
+      <c r="AF42" s="8"/>
+    </row>
+    <row r="43" spans="1:32">
       <c r="A43" s="5" t="s">
         <v>46</v>
       </c>
@@ -4196,8 +4243,9 @@
       <c r="AC43" s="8"/>
       <c r="AD43" s="8"/>
       <c r="AE43" s="8"/>
-    </row>
-    <row r="44" spans="1:31">
+      <c r="AF43" s="8"/>
+    </row>
+    <row r="44" spans="1:32">
       <c r="A44" s="5" t="s">
         <v>47</v>
       </c>
@@ -4231,8 +4279,9 @@
       <c r="AC44" s="8"/>
       <c r="AD44" s="8"/>
       <c r="AE44" s="8"/>
-    </row>
-    <row r="45" spans="1:31">
+      <c r="AF44" s="8"/>
+    </row>
+    <row r="45" spans="1:32">
       <c r="A45" s="5" t="s">
         <v>48</v>
       </c>
@@ -4266,8 +4315,9 @@
       <c r="AC45" s="8"/>
       <c r="AD45" s="8"/>
       <c r="AE45" s="8"/>
-    </row>
-    <row r="46" spans="1:31">
+      <c r="AF45" s="8"/>
+    </row>
+    <row r="46" spans="1:32">
       <c r="A46" s="5" t="s">
         <v>49</v>
       </c>
@@ -4301,8 +4351,9 @@
       <c r="AC46" s="8"/>
       <c r="AD46" s="8"/>
       <c r="AE46" s="8"/>
-    </row>
-    <row r="47" spans="1:31">
+      <c r="AF46" s="8"/>
+    </row>
+    <row r="47" spans="1:32">
       <c r="A47" s="5" t="s">
         <v>50</v>
       </c>
@@ -4336,8 +4387,9 @@
       <c r="AC47" s="8"/>
       <c r="AD47" s="8"/>
       <c r="AE47" s="8"/>
-    </row>
-    <row r="48" spans="1:31">
+      <c r="AF47" s="8"/>
+    </row>
+    <row r="48" spans="1:32">
       <c r="A48" s="5" t="s">
         <v>51</v>
       </c>
@@ -4371,8 +4423,9 @@
       <c r="AC48" s="8"/>
       <c r="AD48" s="8"/>
       <c r="AE48" s="8"/>
-    </row>
-    <row r="49" spans="1:31">
+      <c r="AF48" s="8"/>
+    </row>
+    <row r="49" spans="1:32">
       <c r="A49" s="5" t="s">
         <v>52</v>
       </c>
@@ -4406,8 +4459,9 @@
       <c r="AC49" s="8"/>
       <c r="AD49" s="8"/>
       <c r="AE49" s="8"/>
-    </row>
-    <row r="50" spans="1:31">
+      <c r="AF49" s="8"/>
+    </row>
+    <row r="50" spans="1:32">
       <c r="A50" s="5" t="s">
         <v>53</v>
       </c>
@@ -4441,8 +4495,9 @@
       <c r="AC50" s="8"/>
       <c r="AD50" s="8"/>
       <c r="AE50" s="8"/>
-    </row>
-    <row r="51" spans="1:31">
+      <c r="AF50" s="8"/>
+    </row>
+    <row r="51" spans="1:32">
       <c r="A51" s="5" t="s">
         <v>54</v>
       </c>
@@ -4476,8 +4531,9 @@
       <c r="AC51" s="8"/>
       <c r="AD51" s="8"/>
       <c r="AE51" s="8"/>
-    </row>
-    <row r="52" spans="1:31">
+      <c r="AF51" s="8"/>
+    </row>
+    <row r="52" spans="1:32">
       <c r="A52" s="5" t="s">
         <v>55</v>
       </c>
@@ -4511,8 +4567,9 @@
       <c r="AC52" s="8"/>
       <c r="AD52" s="8"/>
       <c r="AE52" s="8"/>
-    </row>
-    <row r="53" spans="1:31">
+      <c r="AF52" s="8"/>
+    </row>
+    <row r="53" spans="1:32">
       <c r="A53" s="5" t="s">
         <v>56</v>
       </c>
@@ -4546,8 +4603,9 @@
       <c r="AC53" s="8"/>
       <c r="AD53" s="8"/>
       <c r="AE53" s="8"/>
-    </row>
-    <row r="54" spans="1:31">
+      <c r="AF53" s="8"/>
+    </row>
+    <row r="54" spans="1:32">
       <c r="A54" s="5" t="s">
         <v>57</v>
       </c>
@@ -4581,8 +4639,9 @@
       <c r="AC54" s="8"/>
       <c r="AD54" s="8"/>
       <c r="AE54" s="8"/>
-    </row>
-    <row r="55" spans="1:31">
+      <c r="AF54" s="8"/>
+    </row>
+    <row r="55" spans="1:32">
       <c r="A55" s="5" t="s">
         <v>58</v>
       </c>
@@ -4616,8 +4675,9 @@
       <c r="AC55" s="8"/>
       <c r="AD55" s="8"/>
       <c r="AE55" s="8"/>
-    </row>
-    <row r="56" spans="1:31">
+      <c r="AF55" s="8"/>
+    </row>
+    <row r="56" spans="1:32">
       <c r="A56" s="5" t="s">
         <v>59</v>
       </c>
@@ -4651,8 +4711,9 @@
       <c r="AC56" s="8"/>
       <c r="AD56" s="8"/>
       <c r="AE56" s="8"/>
-    </row>
-    <row r="57" spans="1:31">
+      <c r="AF56" s="8"/>
+    </row>
+    <row r="57" spans="1:32">
       <c r="A57" s="5" t="s">
         <v>60</v>
       </c>
@@ -4686,8 +4747,9 @@
       <c r="AC57" s="8"/>
       <c r="AD57" s="8"/>
       <c r="AE57" s="8"/>
-    </row>
-    <row r="58" spans="1:31">
+      <c r="AF57" s="8"/>
+    </row>
+    <row r="58" spans="1:32">
       <c r="A58" s="5" t="s">
         <v>61</v>
       </c>
@@ -4721,8 +4783,9 @@
       <c r="AC58" s="8"/>
       <c r="AD58" s="8"/>
       <c r="AE58" s="8"/>
-    </row>
-    <row r="59" spans="1:31">
+      <c r="AF58" s="8"/>
+    </row>
+    <row r="59" spans="1:32">
       <c r="A59" s="5" t="s">
         <v>62</v>
       </c>
@@ -4756,8 +4819,9 @@
       <c r="AC59" s="8"/>
       <c r="AD59" s="8"/>
       <c r="AE59" s="8"/>
-    </row>
-    <row r="60" spans="1:31">
+      <c r="AF59" s="8"/>
+    </row>
+    <row r="60" spans="1:32">
       <c r="A60" s="5" t="s">
         <v>63</v>
       </c>
@@ -4791,8 +4855,9 @@
       <c r="AC60" s="8"/>
       <c r="AD60" s="8"/>
       <c r="AE60" s="8"/>
-    </row>
-    <row r="61" spans="1:31">
+      <c r="AF60" s="8"/>
+    </row>
+    <row r="61" spans="1:32">
       <c r="A61" s="5" t="s">
         <v>64</v>
       </c>
@@ -4826,8 +4891,9 @@
       <c r="AC61" s="8"/>
       <c r="AD61" s="8"/>
       <c r="AE61" s="8"/>
-    </row>
-    <row r="62" spans="1:31">
+      <c r="AF61" s="8"/>
+    </row>
+    <row r="62" spans="1:32">
       <c r="A62" s="5" t="s">
         <v>65</v>
       </c>
@@ -4861,8 +4927,9 @@
       <c r="AC62" s="8"/>
       <c r="AD62" s="8"/>
       <c r="AE62" s="8"/>
-    </row>
-    <row r="63" spans="1:31">
+      <c r="AF62" s="8"/>
+    </row>
+    <row r="63" spans="1:32">
       <c r="A63" s="5" t="s">
         <v>66</v>
       </c>
@@ -4896,8 +4963,9 @@
       <c r="AC63" s="8"/>
       <c r="AD63" s="8"/>
       <c r="AE63" s="8"/>
-    </row>
-    <row r="64" spans="1:31">
+      <c r="AF63" s="8"/>
+    </row>
+    <row r="64" spans="1:32">
       <c r="A64" s="5" t="s">
         <v>67</v>
       </c>
@@ -4931,8 +4999,9 @@
       <c r="AC64" s="8"/>
       <c r="AD64" s="8"/>
       <c r="AE64" s="8"/>
-    </row>
-    <row r="65" spans="1:31">
+      <c r="AF64" s="8"/>
+    </row>
+    <row r="65" spans="1:32">
       <c r="A65" s="5" t="s">
         <v>68</v>
       </c>
@@ -4966,8 +5035,9 @@
       <c r="AC65" s="8"/>
       <c r="AD65" s="8"/>
       <c r="AE65" s="8"/>
-    </row>
-    <row r="66" spans="1:31">
+      <c r="AF65" s="8"/>
+    </row>
+    <row r="66" spans="1:32">
       <c r="A66" s="5" t="s">
         <v>69</v>
       </c>
@@ -5001,8 +5071,9 @@
       <c r="AC66" s="8"/>
       <c r="AD66" s="8"/>
       <c r="AE66" s="8"/>
-    </row>
-    <row r="67" spans="1:31">
+      <c r="AF66" s="8"/>
+    </row>
+    <row r="67" spans="1:32">
       <c r="A67" s="5" t="s">
         <v>70</v>
       </c>
@@ -5036,8 +5107,9 @@
       <c r="AC67" s="8"/>
       <c r="AD67" s="8"/>
       <c r="AE67" s="8"/>
-    </row>
-    <row r="68" spans="1:31">
+      <c r="AF67" s="8"/>
+    </row>
+    <row r="68" spans="1:32">
       <c r="A68" s="5" t="s">
         <v>71</v>
       </c>
@@ -5071,8 +5143,9 @@
       <c r="AC68" s="8"/>
       <c r="AD68" s="8"/>
       <c r="AE68" s="8"/>
-    </row>
-    <row r="69" spans="1:31">
+      <c r="AF68" s="8"/>
+    </row>
+    <row r="69" spans="1:32">
       <c r="A69" s="5" t="s">
         <v>72</v>
       </c>
@@ -5106,8 +5179,9 @@
       <c r="AC69" s="8"/>
       <c r="AD69" s="8"/>
       <c r="AE69" s="8"/>
-    </row>
-    <row r="70" spans="1:31">
+      <c r="AF69" s="8"/>
+    </row>
+    <row r="70" spans="1:32">
       <c r="A70" s="5" t="s">
         <v>73</v>
       </c>
@@ -5141,8 +5215,9 @@
       <c r="AC70" s="8"/>
       <c r="AD70" s="8"/>
       <c r="AE70" s="8"/>
-    </row>
-    <row r="71" spans="1:31">
+      <c r="AF70" s="8"/>
+    </row>
+    <row r="71" spans="1:32">
       <c r="A71" s="5" t="s">
         <v>74</v>
       </c>
@@ -5176,8 +5251,9 @@
       <c r="AC71" s="8"/>
       <c r="AD71" s="8"/>
       <c r="AE71" s="8"/>
-    </row>
-    <row r="72" spans="1:31">
+      <c r="AF71" s="8"/>
+    </row>
+    <row r="72" spans="1:32">
       <c r="A72" s="5" t="s">
         <v>75</v>
       </c>
@@ -5211,8 +5287,9 @@
       <c r="AC72" s="8"/>
       <c r="AD72" s="8"/>
       <c r="AE72" s="8"/>
-    </row>
-    <row r="73" spans="1:31">
+      <c r="AF72" s="8"/>
+    </row>
+    <row r="73" spans="1:32">
       <c r="A73" s="5" t="s">
         <v>76</v>
       </c>
@@ -5246,8 +5323,9 @@
       <c r="AC73" s="8"/>
       <c r="AD73" s="8"/>
       <c r="AE73" s="8"/>
-    </row>
-    <row r="74" spans="1:31">
+      <c r="AF73" s="8"/>
+    </row>
+    <row r="74" spans="1:32">
       <c r="A74" s="5" t="s">
         <v>77</v>
       </c>
@@ -5281,8 +5359,9 @@
       <c r="AC74" s="8"/>
       <c r="AD74" s="8"/>
       <c r="AE74" s="8"/>
-    </row>
-    <row r="75" spans="1:31">
+      <c r="AF74" s="8"/>
+    </row>
+    <row r="75" spans="1:32">
       <c r="A75" s="5" t="s">
         <v>78</v>
       </c>
@@ -5316,8 +5395,9 @@
       <c r="AC75" s="8"/>
       <c r="AD75" s="8"/>
       <c r="AE75" s="8"/>
-    </row>
-    <row r="76" spans="1:31">
+      <c r="AF75" s="8"/>
+    </row>
+    <row r="76" spans="1:32">
       <c r="A76" s="5" t="s">
         <v>79</v>
       </c>
@@ -5351,8 +5431,9 @@
       <c r="AC76" s="8"/>
       <c r="AD76" s="8"/>
       <c r="AE76" s="8"/>
-    </row>
-    <row r="77" spans="1:31">
+      <c r="AF76" s="8"/>
+    </row>
+    <row r="77" spans="1:32">
       <c r="A77" s="5" t="s">
         <v>80</v>
       </c>
@@ -5386,8 +5467,9 @@
       <c r="AC77" s="8"/>
       <c r="AD77" s="8"/>
       <c r="AE77" s="8"/>
-    </row>
-    <row r="78" spans="1:31">
+      <c r="AF77" s="8"/>
+    </row>
+    <row r="78" spans="1:32">
       <c r="A78" s="5" t="s">
         <v>81</v>
       </c>
@@ -5421,8 +5503,9 @@
       <c r="AC78" s="8"/>
       <c r="AD78" s="8"/>
       <c r="AE78" s="8"/>
-    </row>
-    <row r="79" spans="1:31">
+      <c r="AF78" s="8"/>
+    </row>
+    <row r="79" spans="1:32">
       <c r="A79" s="5" t="s">
         <v>82</v>
       </c>
@@ -5456,8 +5539,9 @@
       <c r="AC79" s="8"/>
       <c r="AD79" s="8"/>
       <c r="AE79" s="8"/>
-    </row>
-    <row r="80" spans="1:31">
+      <c r="AF79" s="8"/>
+    </row>
+    <row r="80" spans="1:32">
       <c r="A80" s="5" t="s">
         <v>83</v>
       </c>
@@ -5491,8 +5575,9 @@
       <c r="AC80" s="8"/>
       <c r="AD80" s="8"/>
       <c r="AE80" s="8"/>
-    </row>
-    <row r="81" spans="1:31">
+      <c r="AF80" s="8"/>
+    </row>
+    <row r="81" spans="1:32">
       <c r="A81" s="5" t="s">
         <v>84</v>
       </c>
@@ -5526,8 +5611,9 @@
       <c r="AC81" s="8"/>
       <c r="AD81" s="8"/>
       <c r="AE81" s="8"/>
-    </row>
-    <row r="82" spans="1:31">
+      <c r="AF81" s="8"/>
+    </row>
+    <row r="82" spans="1:32">
       <c r="A82" s="5" t="s">
         <v>85</v>
       </c>
@@ -5561,8 +5647,9 @@
       <c r="AC82" s="8"/>
       <c r="AD82" s="8"/>
       <c r="AE82" s="8"/>
-    </row>
-    <row r="83" spans="1:31">
+      <c r="AF82" s="8"/>
+    </row>
+    <row r="83" spans="1:32">
       <c r="A83" s="5" t="s">
         <v>86</v>
       </c>
@@ -5596,8 +5683,9 @@
       <c r="AC83" s="8"/>
       <c r="AD83" s="8"/>
       <c r="AE83" s="8"/>
-    </row>
-    <row r="84" spans="1:31">
+      <c r="AF83" s="8"/>
+    </row>
+    <row r="84" spans="1:32">
       <c r="A84" s="5" t="s">
         <v>87</v>
       </c>
@@ -5631,8 +5719,9 @@
       <c r="AC84" s="8"/>
       <c r="AD84" s="8"/>
       <c r="AE84" s="8"/>
-    </row>
-    <row r="85" spans="1:31">
+      <c r="AF84" s="8"/>
+    </row>
+    <row r="85" spans="1:32">
       <c r="A85" s="5" t="s">
         <v>88</v>
       </c>
@@ -5666,8 +5755,9 @@
       <c r="AC85" s="8"/>
       <c r="AD85" s="8"/>
       <c r="AE85" s="8"/>
-    </row>
-    <row r="86" spans="1:31">
+      <c r="AF85" s="8"/>
+    </row>
+    <row r="86" spans="1:32">
       <c r="A86" s="5" t="s">
         <v>89</v>
       </c>
@@ -5701,8 +5791,9 @@
       <c r="AC86" s="8"/>
       <c r="AD86" s="8"/>
       <c r="AE86" s="8"/>
-    </row>
-    <row r="87" spans="1:31">
+      <c r="AF86" s="8"/>
+    </row>
+    <row r="87" spans="1:32">
       <c r="A87" s="5" t="s">
         <v>90</v>
       </c>
@@ -5736,8 +5827,9 @@
       <c r="AC87" s="8"/>
       <c r="AD87" s="8"/>
       <c r="AE87" s="8"/>
-    </row>
-    <row r="88" spans="1:31">
+      <c r="AF87" s="8"/>
+    </row>
+    <row r="88" spans="1:32">
       <c r="A88" s="5" t="s">
         <v>91</v>
       </c>
@@ -5771,8 +5863,9 @@
       <c r="AC88" s="8"/>
       <c r="AD88" s="8"/>
       <c r="AE88" s="8"/>
-    </row>
-    <row r="89" spans="1:31">
+      <c r="AF88" s="8"/>
+    </row>
+    <row r="89" spans="1:32">
       <c r="A89" s="5" t="s">
         <v>92</v>
       </c>
@@ -5806,8 +5899,9 @@
       <c r="AC89" s="8"/>
       <c r="AD89" s="8"/>
       <c r="AE89" s="8"/>
-    </row>
-    <row r="90" spans="1:31">
+      <c r="AF89" s="8"/>
+    </row>
+    <row r="90" spans="1:32">
       <c r="A90" s="5" t="s">
         <v>93</v>
       </c>
@@ -5841,8 +5935,9 @@
       <c r="AC90" s="8"/>
       <c r="AD90" s="8"/>
       <c r="AE90" s="8"/>
-    </row>
-    <row r="91" spans="1:31">
+      <c r="AF90" s="8"/>
+    </row>
+    <row r="91" spans="1:32">
       <c r="A91" s="5" t="s">
         <v>94</v>
       </c>
@@ -5876,8 +5971,9 @@
       <c r="AC91" s="8"/>
       <c r="AD91" s="8"/>
       <c r="AE91" s="8"/>
-    </row>
-    <row r="92" spans="1:31">
+      <c r="AF91" s="8"/>
+    </row>
+    <row r="92" spans="1:32">
       <c r="A92" s="5" t="s">
         <v>95</v>
       </c>
@@ -5911,8 +6007,9 @@
       <c r="AC92" s="8"/>
       <c r="AD92" s="8"/>
       <c r="AE92" s="8"/>
-    </row>
-    <row r="93" spans="1:31">
+      <c r="AF92" s="8"/>
+    </row>
+    <row r="93" spans="1:32">
       <c r="A93" s="5" t="s">
         <v>96</v>
       </c>
@@ -5946,8 +6043,9 @@
       <c r="AC93" s="8"/>
       <c r="AD93" s="8"/>
       <c r="AE93" s="8"/>
-    </row>
-    <row r="94" spans="1:31">
+      <c r="AF93" s="8"/>
+    </row>
+    <row r="94" spans="1:32">
       <c r="A94" s="5" t="s">
         <v>97</v>
       </c>
@@ -5981,8 +6079,9 @@
       <c r="AC94" s="8"/>
       <c r="AD94" s="8"/>
       <c r="AE94" s="8"/>
-    </row>
-    <row r="95" spans="1:31">
+      <c r="AF94" s="8"/>
+    </row>
+    <row r="95" spans="1:32">
       <c r="A95" s="5" t="s">
         <v>98</v>
       </c>
@@ -6016,8 +6115,9 @@
       <c r="AC95" s="8"/>
       <c r="AD95" s="8"/>
       <c r="AE95" s="8"/>
-    </row>
-    <row r="96" spans="1:31">
+      <c r="AF95" s="8"/>
+    </row>
+    <row r="96" spans="1:32">
       <c r="A96" s="5" t="s">
         <v>99</v>
       </c>
@@ -6051,8 +6151,9 @@
       <c r="AC96" s="8"/>
       <c r="AD96" s="8"/>
       <c r="AE96" s="8"/>
-    </row>
-    <row r="97" spans="1:31">
+      <c r="AF96" s="8"/>
+    </row>
+    <row r="97" spans="1:32">
       <c r="A97" s="5" t="s">
         <v>100</v>
       </c>
@@ -6086,8 +6187,9 @@
       <c r="AC97" s="8"/>
       <c r="AD97" s="8"/>
       <c r="AE97" s="8"/>
-    </row>
-    <row r="98" spans="1:31">
+      <c r="AF97" s="8"/>
+    </row>
+    <row r="98" spans="1:32">
       <c r="A98" s="5" t="s">
         <v>101</v>
       </c>
@@ -6121,8 +6223,9 @@
       <c r="AC98" s="8"/>
       <c r="AD98" s="8"/>
       <c r="AE98" s="8"/>
-    </row>
-    <row r="99" spans="1:31">
+      <c r="AF98" s="8"/>
+    </row>
+    <row r="99" spans="1:32">
       <c r="A99" s="5" t="s">
         <v>102</v>
       </c>
@@ -6156,8 +6259,9 @@
       <c r="AC99" s="8"/>
       <c r="AD99" s="8"/>
       <c r="AE99" s="8"/>
-    </row>
-    <row r="100" spans="1:31">
+      <c r="AF99" s="8"/>
+    </row>
+    <row r="100" spans="1:32">
       <c r="A100" s="5" t="s">
         <v>103</v>
       </c>
@@ -6191,8 +6295,9 @@
       <c r="AC100" s="8"/>
       <c r="AD100" s="8"/>
       <c r="AE100" s="8"/>
-    </row>
-    <row r="101" spans="1:31">
+      <c r="AF100" s="8"/>
+    </row>
+    <row r="101" spans="1:32">
       <c r="A101" s="5" t="s">
         <v>104</v>
       </c>
@@ -6226,8 +6331,9 @@
       <c r="AC101" s="8"/>
       <c r="AD101" s="8"/>
       <c r="AE101" s="8"/>
-    </row>
-    <row r="102" spans="1:31">
+      <c r="AF101" s="8"/>
+    </row>
+    <row r="102" spans="1:32">
       <c r="A102" s="5" t="s">
         <v>105</v>
       </c>
@@ -6261,8 +6367,9 @@
       <c r="AC102" s="8"/>
       <c r="AD102" s="8"/>
       <c r="AE102" s="8"/>
-    </row>
-    <row r="103" spans="1:31">
+      <c r="AF102" s="8"/>
+    </row>
+    <row r="103" spans="1:32">
       <c r="A103" s="5" t="s">
         <v>106</v>
       </c>
@@ -6296,8 +6403,9 @@
       <c r="AC103" s="8"/>
       <c r="AD103" s="8"/>
       <c r="AE103" s="8"/>
-    </row>
-    <row r="104" spans="1:31">
+      <c r="AF103" s="8"/>
+    </row>
+    <row r="104" spans="1:32">
       <c r="A104" s="5" t="s">
         <v>107</v>
       </c>
@@ -6331,8 +6439,9 @@
       <c r="AC104" s="8"/>
       <c r="AD104" s="8"/>
       <c r="AE104" s="8"/>
-    </row>
-    <row r="105" spans="1:31">
+      <c r="AF104" s="8"/>
+    </row>
+    <row r="105" spans="1:32">
       <c r="A105" s="5" t="s">
         <v>108</v>
       </c>
@@ -6366,8 +6475,9 @@
       <c r="AC105" s="8"/>
       <c r="AD105" s="8"/>
       <c r="AE105" s="8"/>
-    </row>
-    <row r="106" spans="1:31">
+      <c r="AF105" s="8"/>
+    </row>
+    <row r="106" spans="1:32">
       <c r="A106" s="5" t="s">
         <v>109</v>
       </c>
@@ -6401,11 +6511,12 @@
       <c r="AC106" s="8"/>
       <c r="AD106" s="8"/>
       <c r="AE106" s="8"/>
+      <c r="AF106" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:F6" xr:uid="{865A20BB-1F5D-416D-8AD5-2BCD3ABC6B25}">
-      <formula1>$G$6:$DF$6</formula1>
+      <formula1>$G$6:$DG$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6422,7 +6533,7 @@
           <x14:formula1>
             <xm:f>description!$E$6:$I$6</xm:f>
           </x14:formula1>
-          <xm:sqref>B3:AD3</xm:sqref>
+          <xm:sqref>B3:AE3</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/raw_results/lanupro_vocabulary_general.xlsx
+++ b/data/raw_results/lanupro_vocabulary_general.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41FFF019-06BE-4ED1-B53C-FB92AE6FC931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B848A5-0F2B-4CE8-B7F1-2AF1AF1F67FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="272">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -54,15 +54,9 @@
     <t>attribute</t>
   </si>
   <si>
-    <t>category</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
-    <t>qualitative</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
@@ -373,9 +367,6 @@
   </si>
   <si>
     <t>identifier</t>
-  </si>
-  <si>
-    <t>quantitative</t>
   </si>
   <si>
     <t>numeric</t>
@@ -482,12 +473,6 @@
 In some cases the synonym depends on the sample type. E.g. in lanupro_ontology a generic name is used for e.g. fatty acids independent of the sample type, while ATOL uses separate numbers for milk or meat.</t>
   </si>
   <si>
-    <t>data category</t>
-  </si>
-  <si>
-    <t>dtring or numeric</t>
-  </si>
-  <si>
     <t>default variable unit when no units are specified in the variable name</t>
   </si>
   <si>
@@ -869,16 +854,7 @@
     <t>sample_form</t>
   </si>
   <si>
-    <t>test_field</t>
-  </si>
-  <si>
-    <t>test_01</t>
-  </si>
-  <si>
-    <t>test_02</t>
-  </si>
-  <si>
-    <t>test_field_bis</t>
+    <t>Format of the variable</t>
   </si>
 </sst>
 </file>
@@ -2204,7 +2180,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB33DE6-D058-433F-9B7D-5598CD0261F2}">
-  <dimension ref="A1:AF106"/>
+  <dimension ref="A1:AB105"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17" style="4" customWidth="1"/>
@@ -2220,571 +2196,540 @@
     <col min="20" max="20" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13.77734375" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="22.5546875" customWidth="1"/>
-    <col min="25" max="25" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.88671875" customWidth="1"/>
-    <col min="27" max="27" width="16" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.33203125" customWidth="1"/>
-    <col min="31" max="31" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="22.5546875" customWidth="1"/>
+    <col min="24" max="24" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="1" customFormat="1">
+    <row r="1" spans="1:28" s="1" customFormat="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q1" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="R1" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y2" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z2" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA2" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AB2" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28">
+      <c r="A3" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="H1" s="6" t="s">
+      <c r="E3" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="T3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z3" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA3" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="AB3" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="86.4">
+      <c r="A4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="O4" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="V1" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="W1" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="X1" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="Y1" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="Z1" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="AA1" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="AB1" s="6" t="s">
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="11"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="AC1" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="AD1" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="AE1" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="AF1" s="6" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32">
-      <c r="A2" s="5" t="s">
+    </row>
+    <row r="5" spans="1:28">
+      <c r="A5" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="8"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8"/>
+      <c r="AA5" s="8"/>
+      <c r="AB5" s="8"/>
+    </row>
+    <row r="6" spans="1:28">
+      <c r="A6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="S6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="T6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="U6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="V6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="W6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="X6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="AB6" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28">
+      <c r="A7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="V2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="AC2" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="AD2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="AE2" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF2" s="8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32">
-      <c r="A3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8"/>
-      <c r="Z3" s="8"/>
-      <c r="AA3" s="8"/>
-      <c r="AB3" s="8"/>
-      <c r="AC3" s="8"/>
-      <c r="AD3" s="8"/>
-      <c r="AE3" s="8"/>
-      <c r="AF3" s="8"/>
-    </row>
-    <row r="4" spans="1:32">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="8" t="s">
+      <c r="E7" s="8"/>
+      <c r="F7" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="8"/>
-      <c r="AA4" s="8"/>
-      <c r="AB4" s="8"/>
-      <c r="AC4" s="8"/>
-      <c r="AD4" s="8"/>
-      <c r="AE4" s="8"/>
-      <c r="AF4" s="8"/>
-    </row>
-    <row r="5" spans="1:32" ht="86.4">
-      <c r="A5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="O5" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10"/>
-      <c r="AB5" s="10"/>
-      <c r="AC5" s="10"/>
-      <c r="AD5" s="10"/>
-      <c r="AE5" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="AF5" s="8" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32">
-      <c r="A6" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="8"/>
-      <c r="AF6" s="8"/>
-    </row>
-    <row r="7" spans="1:32">
-      <c r="A7" s="5" t="s">
+      <c r="G7" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="8"/>
+      <c r="AB7" s="8"/>
+    </row>
+    <row r="8" spans="1:28">
+      <c r="A8" s="5" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="S7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="T7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="U7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="V7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="W7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="AB7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="AC7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="AD7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="AE7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF7" s="8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32">
-      <c r="A8" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8" t="s">
-        <v>116</v>
+        <v>258</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -2800,41 +2745,35 @@
       <c r="Z8" s="8"/>
       <c r="AA8" s="8"/>
       <c r="AB8" s="8"/>
-      <c r="AC8" s="8"/>
-      <c r="AD8" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="AE8" s="8"/>
-      <c r="AF8" s="8"/>
-    </row>
-    <row r="9" spans="1:32">
+    </row>
+    <row r="9" spans="1:28">
       <c r="A9" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
@@ -2850,39 +2789,33 @@
       <c r="Z9" s="8"/>
       <c r="AA9" s="8"/>
       <c r="AB9" s="8"/>
-      <c r="AC9" s="8"/>
-      <c r="AD9" s="8"/>
-      <c r="AE9" s="8"/>
-      <c r="AF9" s="8"/>
-    </row>
-    <row r="10" spans="1:32">
+    </row>
+    <row r="10" spans="1:28">
       <c r="A10" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="8" t="s">
-        <v>264</v>
-      </c>
+      <c r="F10" s="8"/>
       <c r="G10" s="8" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
       <c r="L10" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -2898,37 +2831,33 @@
       <c r="Z10" s="8"/>
       <c r="AA10" s="8"/>
       <c r="AB10" s="8"/>
-      <c r="AC10" s="8"/>
-      <c r="AD10" s="8"/>
-      <c r="AE10" s="8"/>
-      <c r="AF10" s="8"/>
-    </row>
-    <row r="11" spans="1:32">
+    </row>
+    <row r="11" spans="1:28">
       <c r="A11" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -2944,37 +2873,31 @@
       <c r="Z11" s="8"/>
       <c r="AA11" s="8"/>
       <c r="AB11" s="8"/>
-      <c r="AC11" s="8"/>
-      <c r="AD11" s="8"/>
-      <c r="AE11" s="8"/>
-      <c r="AF11" s="8"/>
-    </row>
-    <row r="12" spans="1:32">
+    </row>
+    <row r="12" spans="1:28">
       <c r="A12" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
-      <c r="G12" s="8" t="s">
-        <v>172</v>
-      </c>
+      <c r="G12" s="8"/>
       <c r="H12" s="8"/>
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
@@ -2990,19 +2913,15 @@
       <c r="Z12" s="8"/>
       <c r="AA12" s="8"/>
       <c r="AB12" s="8"/>
-      <c r="AC12" s="8"/>
-      <c r="AD12" s="8"/>
-      <c r="AE12" s="8"/>
-      <c r="AF12" s="8"/>
-    </row>
-    <row r="13" spans="1:32">
+    </row>
+    <row r="13" spans="1:28">
       <c r="A13" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
@@ -3012,13 +2931,13 @@
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -3034,19 +2953,15 @@
       <c r="Z13" s="8"/>
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="8"/>
-      <c r="AF13" s="8"/>
-    </row>
-    <row r="14" spans="1:32">
+    </row>
+    <row r="14" spans="1:28">
       <c r="A14" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
@@ -3056,13 +2971,13 @@
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -3078,19 +2993,15 @@
       <c r="Z14" s="8"/>
       <c r="AA14" s="8"/>
       <c r="AB14" s="8"/>
-      <c r="AC14" s="8"/>
-      <c r="AD14" s="8"/>
-      <c r="AE14" s="8"/>
-      <c r="AF14" s="8"/>
-    </row>
-    <row r="15" spans="1:32">
+    </row>
+    <row r="15" spans="1:28">
       <c r="A15" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
@@ -3100,13 +3011,13 @@
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
@@ -3122,19 +3033,15 @@
       <c r="Z15" s="8"/>
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
-      <c r="AC15" s="8"/>
-      <c r="AD15" s="8"/>
-      <c r="AE15" s="8"/>
-      <c r="AF15" s="8"/>
-    </row>
-    <row r="16" spans="1:32">
+    </row>
+    <row r="16" spans="1:28">
       <c r="A16" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
@@ -3144,13 +3051,13 @@
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -3166,19 +3073,15 @@
       <c r="Z16" s="8"/>
       <c r="AA16" s="8"/>
       <c r="AB16" s="8"/>
-      <c r="AC16" s="8"/>
-      <c r="AD16" s="8"/>
-      <c r="AE16" s="8"/>
-      <c r="AF16" s="8"/>
-    </row>
-    <row r="17" spans="1:32">
+    </row>
+    <row r="17" spans="1:28">
       <c r="A17" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
@@ -3188,13 +3091,11 @@
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>221</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="M17" s="8"/>
       <c r="N17" s="8" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -3210,19 +3111,15 @@
       <c r="Z17" s="8"/>
       <c r="AA17" s="8"/>
       <c r="AB17" s="8"/>
-      <c r="AC17" s="8"/>
-      <c r="AD17" s="8"/>
-      <c r="AE17" s="8"/>
-      <c r="AF17" s="8"/>
-    </row>
-    <row r="18" spans="1:32">
+    </row>
+    <row r="18" spans="1:28">
       <c r="A18" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
@@ -3232,11 +3129,11 @@
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M18" s="8"/>
       <c r="N18" s="8" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -3252,19 +3149,15 @@
       <c r="Z18" s="8"/>
       <c r="AA18" s="8"/>
       <c r="AB18" s="8"/>
-      <c r="AC18" s="8"/>
-      <c r="AD18" s="8"/>
-      <c r="AE18" s="8"/>
-      <c r="AF18" s="8"/>
-    </row>
-    <row r="19" spans="1:32">
+    </row>
+    <row r="19" spans="1:28">
       <c r="A19" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
@@ -3274,11 +3167,11 @@
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M19" s="8"/>
       <c r="N19" s="8" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -3294,19 +3187,15 @@
       <c r="Z19" s="8"/>
       <c r="AA19" s="8"/>
       <c r="AB19" s="8"/>
-      <c r="AC19" s="8"/>
-      <c r="AD19" s="8"/>
-      <c r="AE19" s="8"/>
-      <c r="AF19" s="8"/>
-    </row>
-    <row r="20" spans="1:32">
+    </row>
+    <row r="20" spans="1:28">
       <c r="A20" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
@@ -3316,12 +3205,10 @@
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="M20" s="8"/>
-      <c r="N20" s="8" t="s">
-        <v>237</v>
-      </c>
+      <c r="N20" s="8"/>
       <c r="O20" s="8"/>
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
@@ -3336,19 +3223,15 @@
       <c r="Z20" s="8"/>
       <c r="AA20" s="8"/>
       <c r="AB20" s="8"/>
-      <c r="AC20" s="8"/>
-      <c r="AD20" s="8"/>
-      <c r="AE20" s="8"/>
-      <c r="AF20" s="8"/>
-    </row>
-    <row r="21" spans="1:32">
+    </row>
+    <row r="21" spans="1:28">
       <c r="A21" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
@@ -3358,7 +3241,7 @@
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
@@ -3376,19 +3259,15 @@
       <c r="Z21" s="8"/>
       <c r="AA21" s="8"/>
       <c r="AB21" s="8"/>
-      <c r="AC21" s="8"/>
-      <c r="AD21" s="8"/>
-      <c r="AE21" s="8"/>
-      <c r="AF21" s="8"/>
-    </row>
-    <row r="22" spans="1:32">
+    </row>
+    <row r="22" spans="1:28">
       <c r="A22" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
@@ -3398,7 +3277,7 @@
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
       <c r="L22" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
@@ -3416,19 +3295,15 @@
       <c r="Z22" s="8"/>
       <c r="AA22" s="8"/>
       <c r="AB22" s="8"/>
-      <c r="AC22" s="8"/>
-      <c r="AD22" s="8"/>
-      <c r="AE22" s="8"/>
-      <c r="AF22" s="8"/>
-    </row>
-    <row r="23" spans="1:32">
+    </row>
+    <row r="23" spans="1:28">
       <c r="A23" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
@@ -3438,7 +3313,7 @@
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
       <c r="L23" s="8" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
@@ -3456,19 +3331,15 @@
       <c r="Z23" s="8"/>
       <c r="AA23" s="8"/>
       <c r="AB23" s="8"/>
-      <c r="AC23" s="8"/>
-      <c r="AD23" s="8"/>
-      <c r="AE23" s="8"/>
-      <c r="AF23" s="8"/>
-    </row>
-    <row r="24" spans="1:32">
+    </row>
+    <row r="24" spans="1:28">
       <c r="A24" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
@@ -3478,7 +3349,7 @@
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
@@ -3496,19 +3367,15 @@
       <c r="Z24" s="8"/>
       <c r="AA24" s="8"/>
       <c r="AB24" s="8"/>
-      <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="8"/>
-      <c r="AF24" s="8"/>
-    </row>
-    <row r="25" spans="1:32">
+    </row>
+    <row r="25" spans="1:28">
       <c r="A25" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
@@ -3518,7 +3385,7 @@
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
@@ -3536,19 +3403,15 @@
       <c r="Z25" s="8"/>
       <c r="AA25" s="8"/>
       <c r="AB25" s="8"/>
-      <c r="AC25" s="8"/>
-      <c r="AD25" s="8"/>
-      <c r="AE25" s="8"/>
-      <c r="AF25" s="8"/>
-    </row>
-    <row r="26" spans="1:32">
+    </row>
+    <row r="26" spans="1:28">
       <c r="A26" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
@@ -3558,7 +3421,7 @@
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
@@ -3576,19 +3439,15 @@
       <c r="Z26" s="8"/>
       <c r="AA26" s="8"/>
       <c r="AB26" s="8"/>
-      <c r="AC26" s="8"/>
-      <c r="AD26" s="8"/>
-      <c r="AE26" s="8"/>
-      <c r="AF26" s="8"/>
-    </row>
-    <row r="27" spans="1:32">
+    </row>
+    <row r="27" spans="1:28">
       <c r="A27" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
@@ -3598,7 +3457,7 @@
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
       <c r="L27" s="8" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
@@ -3616,19 +3475,15 @@
       <c r="Z27" s="8"/>
       <c r="AA27" s="8"/>
       <c r="AB27" s="8"/>
-      <c r="AC27" s="8"/>
-      <c r="AD27" s="8"/>
-      <c r="AE27" s="8"/>
-      <c r="AF27" s="8"/>
-    </row>
-    <row r="28" spans="1:32">
+    </row>
+    <row r="28" spans="1:28">
       <c r="A28" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
@@ -3638,7 +3493,7 @@
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
       <c r="L28" s="8" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="M28" s="8"/>
       <c r="N28" s="8"/>
@@ -3656,19 +3511,15 @@
       <c r="Z28" s="8"/>
       <c r="AA28" s="8"/>
       <c r="AB28" s="8"/>
-      <c r="AC28" s="8"/>
-      <c r="AD28" s="8"/>
-      <c r="AE28" s="8"/>
-      <c r="AF28" s="8"/>
-    </row>
-    <row r="29" spans="1:32">
+    </row>
+    <row r="29" spans="1:28">
       <c r="A29" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
@@ -3678,7 +3529,7 @@
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
       <c r="L29" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M29" s="8"/>
       <c r="N29" s="8"/>
@@ -3696,19 +3547,15 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8"/>
-      <c r="AC29" s="8"/>
-      <c r="AD29" s="8"/>
-      <c r="AE29" s="8"/>
-      <c r="AF29" s="8"/>
-    </row>
-    <row r="30" spans="1:32">
+    </row>
+    <row r="30" spans="1:28">
       <c r="A30" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
@@ -3718,7 +3565,7 @@
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
       <c r="L30" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
@@ -3736,19 +3583,15 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8"/>
-      <c r="AC30" s="8"/>
-      <c r="AD30" s="8"/>
-      <c r="AE30" s="8"/>
-      <c r="AF30" s="8"/>
-    </row>
-    <row r="31" spans="1:32">
+    </row>
+    <row r="31" spans="1:28">
       <c r="A31" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
@@ -3758,7 +3601,7 @@
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
       <c r="L31" s="8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M31" s="8"/>
       <c r="N31" s="8"/>
@@ -3776,19 +3619,15 @@
       <c r="Z31" s="8"/>
       <c r="AA31" s="8"/>
       <c r="AB31" s="8"/>
-      <c r="AC31" s="8"/>
-      <c r="AD31" s="8"/>
-      <c r="AE31" s="8"/>
-      <c r="AF31" s="8"/>
-    </row>
-    <row r="32" spans="1:32">
+    </row>
+    <row r="32" spans="1:28">
       <c r="A32" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8" t="s">
-        <v>168</v>
+        <v>261</v>
       </c>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
@@ -3798,7 +3637,7 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
       <c r="L32" s="8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="M32" s="8"/>
       <c r="N32" s="8"/>
@@ -3816,19 +3655,15 @@
       <c r="Z32" s="8"/>
       <c r="AA32" s="8"/>
       <c r="AB32" s="8"/>
-      <c r="AC32" s="8"/>
-      <c r="AD32" s="8"/>
-      <c r="AE32" s="8"/>
-      <c r="AF32" s="8"/>
-    </row>
-    <row r="33" spans="1:32">
+    </row>
+    <row r="33" spans="1:28">
       <c r="A33" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
@@ -3838,7 +3673,7 @@
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
       <c r="L33" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="M33" s="8"/>
       <c r="N33" s="8"/>
@@ -3856,19 +3691,15 @@
       <c r="Z33" s="8"/>
       <c r="AA33" s="8"/>
       <c r="AB33" s="8"/>
-      <c r="AC33" s="8"/>
-      <c r="AD33" s="8"/>
-      <c r="AE33" s="8"/>
-      <c r="AF33" s="8"/>
-    </row>
-    <row r="34" spans="1:32">
+    </row>
+    <row r="34" spans="1:28">
       <c r="A34" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
@@ -3878,7 +3709,7 @@
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
       <c r="L34" s="8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M34" s="8"/>
       <c r="N34" s="8"/>
@@ -3896,20 +3727,14 @@
       <c r="Z34" s="8"/>
       <c r="AA34" s="8"/>
       <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="8"/>
-      <c r="AF34" s="8"/>
-    </row>
-    <row r="35" spans="1:32">
+    </row>
+    <row r="35" spans="1:28">
       <c r="A35" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
-      <c r="D35" s="8" t="s">
-        <v>268</v>
-      </c>
+      <c r="D35" s="8"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
@@ -3918,7 +3743,7 @@
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
       <c r="L35" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="M35" s="8"/>
       <c r="N35" s="8"/>
@@ -3936,14 +3761,10 @@
       <c r="Z35" s="8"/>
       <c r="AA35" s="8"/>
       <c r="AB35" s="8"/>
-      <c r="AC35" s="8"/>
-      <c r="AD35" s="8"/>
-      <c r="AE35" s="8"/>
-      <c r="AF35" s="8"/>
-    </row>
-    <row r="36" spans="1:32">
+    </row>
+    <row r="36" spans="1:28">
       <c r="A36" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -3956,7 +3777,7 @@
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
       <c r="L36" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M36" s="8"/>
       <c r="N36" s="8"/>
@@ -3974,14 +3795,10 @@
       <c r="Z36" s="8"/>
       <c r="AA36" s="8"/>
       <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="8"/>
-      <c r="AF36" s="8"/>
-    </row>
-    <row r="37" spans="1:32">
+    </row>
+    <row r="37" spans="1:28">
       <c r="A37" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -3994,7 +3811,7 @@
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
       <c r="L37" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M37" s="8"/>
       <c r="N37" s="8"/>
@@ -4012,14 +3829,10 @@
       <c r="Z37" s="8"/>
       <c r="AA37" s="8"/>
       <c r="AB37" s="8"/>
-      <c r="AC37" s="8"/>
-      <c r="AD37" s="8"/>
-      <c r="AE37" s="8"/>
-      <c r="AF37" s="8"/>
-    </row>
-    <row r="38" spans="1:32">
+    </row>
+    <row r="38" spans="1:28">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -4032,7 +3845,7 @@
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
       <c r="L38" s="8" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="M38" s="8"/>
       <c r="N38" s="8"/>
@@ -4050,14 +3863,10 @@
       <c r="Z38" s="8"/>
       <c r="AA38" s="8"/>
       <c r="AB38" s="8"/>
-      <c r="AC38" s="8"/>
-      <c r="AD38" s="8"/>
-      <c r="AE38" s="8"/>
-      <c r="AF38" s="8"/>
-    </row>
-    <row r="39" spans="1:32">
+    </row>
+    <row r="39" spans="1:28">
       <c r="A39" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -4070,7 +3879,7 @@
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
       <c r="L39" s="8" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="M39" s="8"/>
       <c r="N39" s="8"/>
@@ -4088,14 +3897,10 @@
       <c r="Z39" s="8"/>
       <c r="AA39" s="8"/>
       <c r="AB39" s="8"/>
-      <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="8"/>
-      <c r="AF39" s="8"/>
-    </row>
-    <row r="40" spans="1:32">
+    </row>
+    <row r="40" spans="1:28">
       <c r="A40" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -4108,7 +3913,7 @@
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
       <c r="L40" s="8" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="M40" s="8"/>
       <c r="N40" s="8"/>
@@ -4126,14 +3931,10 @@
       <c r="Z40" s="8"/>
       <c r="AA40" s="8"/>
       <c r="AB40" s="8"/>
-      <c r="AC40" s="8"/>
-      <c r="AD40" s="8"/>
-      <c r="AE40" s="8"/>
-      <c r="AF40" s="8"/>
-    </row>
-    <row r="41" spans="1:32">
+    </row>
+    <row r="41" spans="1:28">
       <c r="A41" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -4146,7 +3947,7 @@
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
       <c r="L41" s="8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="M41" s="8"/>
       <c r="N41" s="8"/>
@@ -4164,14 +3965,10 @@
       <c r="Z41" s="8"/>
       <c r="AA41" s="8"/>
       <c r="AB41" s="8"/>
-      <c r="AC41" s="8"/>
-      <c r="AD41" s="8"/>
-      <c r="AE41" s="8"/>
-      <c r="AF41" s="8"/>
-    </row>
-    <row r="42" spans="1:32">
+    </row>
+    <row r="42" spans="1:28">
       <c r="A42" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -4184,7 +3981,7 @@
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
       <c r="L42" s="8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="M42" s="8"/>
       <c r="N42" s="8"/>
@@ -4202,14 +3999,10 @@
       <c r="Z42" s="8"/>
       <c r="AA42" s="8"/>
       <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="8"/>
-      <c r="AF42" s="8"/>
-    </row>
-    <row r="43" spans="1:32">
+    </row>
+    <row r="43" spans="1:28">
       <c r="A43" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -4221,9 +4014,7 @@
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
-      <c r="L43" s="8" t="s">
-        <v>209</v>
-      </c>
+      <c r="L43" s="8"/>
       <c r="M43" s="8"/>
       <c r="N43" s="8"/>
       <c r="O43" s="8"/>
@@ -4240,14 +4031,10 @@
       <c r="Z43" s="8"/>
       <c r="AA43" s="8"/>
       <c r="AB43" s="8"/>
-      <c r="AC43" s="8"/>
-      <c r="AD43" s="8"/>
-      <c r="AE43" s="8"/>
-      <c r="AF43" s="8"/>
-    </row>
-    <row r="44" spans="1:32">
+    </row>
+    <row r="44" spans="1:28">
       <c r="A44" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -4276,14 +4063,10 @@
       <c r="Z44" s="8"/>
       <c r="AA44" s="8"/>
       <c r="AB44" s="8"/>
-      <c r="AC44" s="8"/>
-      <c r="AD44" s="8"/>
-      <c r="AE44" s="8"/>
-      <c r="AF44" s="8"/>
-    </row>
-    <row r="45" spans="1:32">
+    </row>
+    <row r="45" spans="1:28">
       <c r="A45" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -4312,14 +4095,10 @@
       <c r="Z45" s="8"/>
       <c r="AA45" s="8"/>
       <c r="AB45" s="8"/>
-      <c r="AC45" s="8"/>
-      <c r="AD45" s="8"/>
-      <c r="AE45" s="8"/>
-      <c r="AF45" s="8"/>
-    </row>
-    <row r="46" spans="1:32">
+    </row>
+    <row r="46" spans="1:28">
       <c r="A46" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -4348,14 +4127,10 @@
       <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
       <c r="AB46" s="8"/>
-      <c r="AC46" s="8"/>
-      <c r="AD46" s="8"/>
-      <c r="AE46" s="8"/>
-      <c r="AF46" s="8"/>
-    </row>
-    <row r="47" spans="1:32">
+    </row>
+    <row r="47" spans="1:28">
       <c r="A47" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -4384,14 +4159,10 @@
       <c r="Z47" s="8"/>
       <c r="AA47" s="8"/>
       <c r="AB47" s="8"/>
-      <c r="AC47" s="8"/>
-      <c r="AD47" s="8"/>
-      <c r="AE47" s="8"/>
-      <c r="AF47" s="8"/>
-    </row>
-    <row r="48" spans="1:32">
+    </row>
+    <row r="48" spans="1:28">
       <c r="A48" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -4420,14 +4191,10 @@
       <c r="Z48" s="8"/>
       <c r="AA48" s="8"/>
       <c r="AB48" s="8"/>
-      <c r="AC48" s="8"/>
-      <c r="AD48" s="8"/>
-      <c r="AE48" s="8"/>
-      <c r="AF48" s="8"/>
-    </row>
-    <row r="49" spans="1:32">
+    </row>
+    <row r="49" spans="1:28">
       <c r="A49" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -4456,14 +4223,10 @@
       <c r="Z49" s="8"/>
       <c r="AA49" s="8"/>
       <c r="AB49" s="8"/>
-      <c r="AC49" s="8"/>
-      <c r="AD49" s="8"/>
-      <c r="AE49" s="8"/>
-      <c r="AF49" s="8"/>
-    </row>
-    <row r="50" spans="1:32">
+    </row>
+    <row r="50" spans="1:28">
       <c r="A50" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -4492,14 +4255,10 @@
       <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
       <c r="AB50" s="8"/>
-      <c r="AC50" s="8"/>
-      <c r="AD50" s="8"/>
-      <c r="AE50" s="8"/>
-      <c r="AF50" s="8"/>
-    </row>
-    <row r="51" spans="1:32">
+    </row>
+    <row r="51" spans="1:28">
       <c r="A51" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -4528,14 +4287,10 @@
       <c r="Z51" s="8"/>
       <c r="AA51" s="8"/>
       <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="8"/>
-      <c r="AF51" s="8"/>
-    </row>
-    <row r="52" spans="1:32">
+    </row>
+    <row r="52" spans="1:28">
       <c r="A52" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -4564,14 +4319,10 @@
       <c r="Z52" s="8"/>
       <c r="AA52" s="8"/>
       <c r="AB52" s="8"/>
-      <c r="AC52" s="8"/>
-      <c r="AD52" s="8"/>
-      <c r="AE52" s="8"/>
-      <c r="AF52" s="8"/>
-    </row>
-    <row r="53" spans="1:32">
+    </row>
+    <row r="53" spans="1:28">
       <c r="A53" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -4600,14 +4351,10 @@
       <c r="Z53" s="8"/>
       <c r="AA53" s="8"/>
       <c r="AB53" s="8"/>
-      <c r="AC53" s="8"/>
-      <c r="AD53" s="8"/>
-      <c r="AE53" s="8"/>
-      <c r="AF53" s="8"/>
-    </row>
-    <row r="54" spans="1:32">
+    </row>
+    <row r="54" spans="1:28">
       <c r="A54" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -4636,14 +4383,10 @@
       <c r="Z54" s="8"/>
       <c r="AA54" s="8"/>
       <c r="AB54" s="8"/>
-      <c r="AC54" s="8"/>
-      <c r="AD54" s="8"/>
-      <c r="AE54" s="8"/>
-      <c r="AF54" s="8"/>
-    </row>
-    <row r="55" spans="1:32">
+    </row>
+    <row r="55" spans="1:28">
       <c r="A55" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -4672,14 +4415,10 @@
       <c r="Z55" s="8"/>
       <c r="AA55" s="8"/>
       <c r="AB55" s="8"/>
-      <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="8"/>
-      <c r="AF55" s="8"/>
-    </row>
-    <row r="56" spans="1:32">
+    </row>
+    <row r="56" spans="1:28">
       <c r="A56" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -4708,14 +4447,10 @@
       <c r="Z56" s="8"/>
       <c r="AA56" s="8"/>
       <c r="AB56" s="8"/>
-      <c r="AC56" s="8"/>
-      <c r="AD56" s="8"/>
-      <c r="AE56" s="8"/>
-      <c r="AF56" s="8"/>
-    </row>
-    <row r="57" spans="1:32">
+    </row>
+    <row r="57" spans="1:28">
       <c r="A57" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -4744,14 +4479,10 @@
       <c r="Z57" s="8"/>
       <c r="AA57" s="8"/>
       <c r="AB57" s="8"/>
-      <c r="AC57" s="8"/>
-      <c r="AD57" s="8"/>
-      <c r="AE57" s="8"/>
-      <c r="AF57" s="8"/>
-    </row>
-    <row r="58" spans="1:32">
+    </row>
+    <row r="58" spans="1:28">
       <c r="A58" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -4780,14 +4511,10 @@
       <c r="Z58" s="8"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="8"/>
-      <c r="AF58" s="8"/>
-    </row>
-    <row r="59" spans="1:32">
+    </row>
+    <row r="59" spans="1:28">
       <c r="A59" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
@@ -4816,14 +4543,10 @@
       <c r="Z59" s="8"/>
       <c r="AA59" s="8"/>
       <c r="AB59" s="8"/>
-      <c r="AC59" s="8"/>
-      <c r="AD59" s="8"/>
-      <c r="AE59" s="8"/>
-      <c r="AF59" s="8"/>
-    </row>
-    <row r="60" spans="1:32">
+    </row>
+    <row r="60" spans="1:28">
       <c r="A60" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -4852,14 +4575,10 @@
       <c r="Z60" s="8"/>
       <c r="AA60" s="8"/>
       <c r="AB60" s="8"/>
-      <c r="AC60" s="8"/>
-      <c r="AD60" s="8"/>
-      <c r="AE60" s="8"/>
-      <c r="AF60" s="8"/>
-    </row>
-    <row r="61" spans="1:32">
+    </row>
+    <row r="61" spans="1:28">
       <c r="A61" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -4888,14 +4607,10 @@
       <c r="Z61" s="8"/>
       <c r="AA61" s="8"/>
       <c r="AB61" s="8"/>
-      <c r="AC61" s="8"/>
-      <c r="AD61" s="8"/>
-      <c r="AE61" s="8"/>
-      <c r="AF61" s="8"/>
-    </row>
-    <row r="62" spans="1:32">
+    </row>
+    <row r="62" spans="1:28">
       <c r="A62" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -4924,14 +4639,10 @@
       <c r="Z62" s="8"/>
       <c r="AA62" s="8"/>
       <c r="AB62" s="8"/>
-      <c r="AC62" s="8"/>
-      <c r="AD62" s="8"/>
-      <c r="AE62" s="8"/>
-      <c r="AF62" s="8"/>
-    </row>
-    <row r="63" spans="1:32">
+    </row>
+    <row r="63" spans="1:28">
       <c r="A63" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -4960,14 +4671,10 @@
       <c r="Z63" s="8"/>
       <c r="AA63" s="8"/>
       <c r="AB63" s="8"/>
-      <c r="AC63" s="8"/>
-      <c r="AD63" s="8"/>
-      <c r="AE63" s="8"/>
-      <c r="AF63" s="8"/>
-    </row>
-    <row r="64" spans="1:32">
+    </row>
+    <row r="64" spans="1:28">
       <c r="A64" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -4996,14 +4703,10 @@
       <c r="Z64" s="8"/>
       <c r="AA64" s="8"/>
       <c r="AB64" s="8"/>
-      <c r="AC64" s="8"/>
-      <c r="AD64" s="8"/>
-      <c r="AE64" s="8"/>
-      <c r="AF64" s="8"/>
-    </row>
-    <row r="65" spans="1:32">
+    </row>
+    <row r="65" spans="1:28">
       <c r="A65" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -5032,14 +4735,10 @@
       <c r="Z65" s="8"/>
       <c r="AA65" s="8"/>
       <c r="AB65" s="8"/>
-      <c r="AC65" s="8"/>
-      <c r="AD65" s="8"/>
-      <c r="AE65" s="8"/>
-      <c r="AF65" s="8"/>
-    </row>
-    <row r="66" spans="1:32">
+    </row>
+    <row r="66" spans="1:28">
       <c r="A66" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -5068,14 +4767,10 @@
       <c r="Z66" s="8"/>
       <c r="AA66" s="8"/>
       <c r="AB66" s="8"/>
-      <c r="AC66" s="8"/>
-      <c r="AD66" s="8"/>
-      <c r="AE66" s="8"/>
-      <c r="AF66" s="8"/>
-    </row>
-    <row r="67" spans="1:32">
+    </row>
+    <row r="67" spans="1:28">
       <c r="A67" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -5104,14 +4799,10 @@
       <c r="Z67" s="8"/>
       <c r="AA67" s="8"/>
       <c r="AB67" s="8"/>
-      <c r="AC67" s="8"/>
-      <c r="AD67" s="8"/>
-      <c r="AE67" s="8"/>
-      <c r="AF67" s="8"/>
-    </row>
-    <row r="68" spans="1:32">
+    </row>
+    <row r="68" spans="1:28">
       <c r="A68" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -5140,14 +4831,10 @@
       <c r="Z68" s="8"/>
       <c r="AA68" s="8"/>
       <c r="AB68" s="8"/>
-      <c r="AC68" s="8"/>
-      <c r="AD68" s="8"/>
-      <c r="AE68" s="8"/>
-      <c r="AF68" s="8"/>
-    </row>
-    <row r="69" spans="1:32">
+    </row>
+    <row r="69" spans="1:28">
       <c r="A69" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -5176,14 +4863,10 @@
       <c r="Z69" s="8"/>
       <c r="AA69" s="8"/>
       <c r="AB69" s="8"/>
-      <c r="AC69" s="8"/>
-      <c r="AD69" s="8"/>
-      <c r="AE69" s="8"/>
-      <c r="AF69" s="8"/>
-    </row>
-    <row r="70" spans="1:32">
+    </row>
+    <row r="70" spans="1:28">
       <c r="A70" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
@@ -5212,14 +4895,10 @@
       <c r="Z70" s="8"/>
       <c r="AA70" s="8"/>
       <c r="AB70" s="8"/>
-      <c r="AC70" s="8"/>
-      <c r="AD70" s="8"/>
-      <c r="AE70" s="8"/>
-      <c r="AF70" s="8"/>
-    </row>
-    <row r="71" spans="1:32">
+    </row>
+    <row r="71" spans="1:28">
       <c r="A71" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
@@ -5248,14 +4927,10 @@
       <c r="Z71" s="8"/>
       <c r="AA71" s="8"/>
       <c r="AB71" s="8"/>
-      <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-      <c r="AE71" s="8"/>
-      <c r="AF71" s="8"/>
-    </row>
-    <row r="72" spans="1:32">
+    </row>
+    <row r="72" spans="1:28">
       <c r="A72" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
@@ -5284,14 +4959,10 @@
       <c r="Z72" s="8"/>
       <c r="AA72" s="8"/>
       <c r="AB72" s="8"/>
-      <c r="AC72" s="8"/>
-      <c r="AD72" s="8"/>
-      <c r="AE72" s="8"/>
-      <c r="AF72" s="8"/>
-    </row>
-    <row r="73" spans="1:32">
+    </row>
+    <row r="73" spans="1:28">
       <c r="A73" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
@@ -5320,14 +4991,10 @@
       <c r="Z73" s="8"/>
       <c r="AA73" s="8"/>
       <c r="AB73" s="8"/>
-      <c r="AC73" s="8"/>
-      <c r="AD73" s="8"/>
-      <c r="AE73" s="8"/>
-      <c r="AF73" s="8"/>
-    </row>
-    <row r="74" spans="1:32">
+    </row>
+    <row r="74" spans="1:28">
       <c r="A74" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -5356,14 +5023,10 @@
       <c r="Z74" s="8"/>
       <c r="AA74" s="8"/>
       <c r="AB74" s="8"/>
-      <c r="AC74" s="8"/>
-      <c r="AD74" s="8"/>
-      <c r="AE74" s="8"/>
-      <c r="AF74" s="8"/>
-    </row>
-    <row r="75" spans="1:32">
+    </row>
+    <row r="75" spans="1:28">
       <c r="A75" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
@@ -5392,14 +5055,10 @@
       <c r="Z75" s="8"/>
       <c r="AA75" s="8"/>
       <c r="AB75" s="8"/>
-      <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="8"/>
-      <c r="AF75" s="8"/>
-    </row>
-    <row r="76" spans="1:32">
+    </row>
+    <row r="76" spans="1:28">
       <c r="A76" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
@@ -5428,14 +5087,10 @@
       <c r="Z76" s="8"/>
       <c r="AA76" s="8"/>
       <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="8"/>
-      <c r="AF76" s="8"/>
-    </row>
-    <row r="77" spans="1:32">
+    </row>
+    <row r="77" spans="1:28">
       <c r="A77" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
@@ -5464,14 +5119,10 @@
       <c r="Z77" s="8"/>
       <c r="AA77" s="8"/>
       <c r="AB77" s="8"/>
-      <c r="AC77" s="8"/>
-      <c r="AD77" s="8"/>
-      <c r="AE77" s="8"/>
-      <c r="AF77" s="8"/>
-    </row>
-    <row r="78" spans="1:32">
+    </row>
+    <row r="78" spans="1:28">
       <c r="A78" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
@@ -5500,14 +5151,10 @@
       <c r="Z78" s="8"/>
       <c r="AA78" s="8"/>
       <c r="AB78" s="8"/>
-      <c r="AC78" s="8"/>
-      <c r="AD78" s="8"/>
-      <c r="AE78" s="8"/>
-      <c r="AF78" s="8"/>
-    </row>
-    <row r="79" spans="1:32">
+    </row>
+    <row r="79" spans="1:28">
       <c r="A79" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
@@ -5536,14 +5183,10 @@
       <c r="Z79" s="8"/>
       <c r="AA79" s="8"/>
       <c r="AB79" s="8"/>
-      <c r="AC79" s="8"/>
-      <c r="AD79" s="8"/>
-      <c r="AE79" s="8"/>
-      <c r="AF79" s="8"/>
-    </row>
-    <row r="80" spans="1:32">
+    </row>
+    <row r="80" spans="1:28">
       <c r="A80" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -5572,14 +5215,10 @@
       <c r="Z80" s="8"/>
       <c r="AA80" s="8"/>
       <c r="AB80" s="8"/>
-      <c r="AC80" s="8"/>
-      <c r="AD80" s="8"/>
-      <c r="AE80" s="8"/>
-      <c r="AF80" s="8"/>
-    </row>
-    <row r="81" spans="1:32">
+    </row>
+    <row r="81" spans="1:28">
       <c r="A81" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
@@ -5608,14 +5247,10 @@
       <c r="Z81" s="8"/>
       <c r="AA81" s="8"/>
       <c r="AB81" s="8"/>
-      <c r="AC81" s="8"/>
-      <c r="AD81" s="8"/>
-      <c r="AE81" s="8"/>
-      <c r="AF81" s="8"/>
-    </row>
-    <row r="82" spans="1:32">
+    </row>
+    <row r="82" spans="1:28">
       <c r="A82" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
@@ -5644,14 +5279,10 @@
       <c r="Z82" s="8"/>
       <c r="AA82" s="8"/>
       <c r="AB82" s="8"/>
-      <c r="AC82" s="8"/>
-      <c r="AD82" s="8"/>
-      <c r="AE82" s="8"/>
-      <c r="AF82" s="8"/>
-    </row>
-    <row r="83" spans="1:32">
+    </row>
+    <row r="83" spans="1:28">
       <c r="A83" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
@@ -5680,14 +5311,10 @@
       <c r="Z83" s="8"/>
       <c r="AA83" s="8"/>
       <c r="AB83" s="8"/>
-      <c r="AC83" s="8"/>
-      <c r="AD83" s="8"/>
-      <c r="AE83" s="8"/>
-      <c r="AF83" s="8"/>
-    </row>
-    <row r="84" spans="1:32">
+    </row>
+    <row r="84" spans="1:28">
       <c r="A84" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
@@ -5716,14 +5343,10 @@
       <c r="Z84" s="8"/>
       <c r="AA84" s="8"/>
       <c r="AB84" s="8"/>
-      <c r="AC84" s="8"/>
-      <c r="AD84" s="8"/>
-      <c r="AE84" s="8"/>
-      <c r="AF84" s="8"/>
-    </row>
-    <row r="85" spans="1:32">
+    </row>
+    <row r="85" spans="1:28">
       <c r="A85" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
@@ -5752,14 +5375,10 @@
       <c r="Z85" s="8"/>
       <c r="AA85" s="8"/>
       <c r="AB85" s="8"/>
-      <c r="AC85" s="8"/>
-      <c r="AD85" s="8"/>
-      <c r="AE85" s="8"/>
-      <c r="AF85" s="8"/>
-    </row>
-    <row r="86" spans="1:32">
+    </row>
+    <row r="86" spans="1:28">
       <c r="A86" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
@@ -5788,14 +5407,10 @@
       <c r="Z86" s="8"/>
       <c r="AA86" s="8"/>
       <c r="AB86" s="8"/>
-      <c r="AC86" s="8"/>
-      <c r="AD86" s="8"/>
-      <c r="AE86" s="8"/>
-      <c r="AF86" s="8"/>
-    </row>
-    <row r="87" spans="1:32">
+    </row>
+    <row r="87" spans="1:28">
       <c r="A87" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
@@ -5824,14 +5439,10 @@
       <c r="Z87" s="8"/>
       <c r="AA87" s="8"/>
       <c r="AB87" s="8"/>
-      <c r="AC87" s="8"/>
-      <c r="AD87" s="8"/>
-      <c r="AE87" s="8"/>
-      <c r="AF87" s="8"/>
-    </row>
-    <row r="88" spans="1:32">
+    </row>
+    <row r="88" spans="1:28">
       <c r="A88" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
@@ -5860,14 +5471,10 @@
       <c r="Z88" s="8"/>
       <c r="AA88" s="8"/>
       <c r="AB88" s="8"/>
-      <c r="AC88" s="8"/>
-      <c r="AD88" s="8"/>
-      <c r="AE88" s="8"/>
-      <c r="AF88" s="8"/>
-    </row>
-    <row r="89" spans="1:32">
+    </row>
+    <row r="89" spans="1:28">
       <c r="A89" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
@@ -5896,14 +5503,10 @@
       <c r="Z89" s="8"/>
       <c r="AA89" s="8"/>
       <c r="AB89" s="8"/>
-      <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="8"/>
-      <c r="AF89" s="8"/>
-    </row>
-    <row r="90" spans="1:32">
+    </row>
+    <row r="90" spans="1:28">
       <c r="A90" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
@@ -5932,14 +5535,10 @@
       <c r="Z90" s="8"/>
       <c r="AA90" s="8"/>
       <c r="AB90" s="8"/>
-      <c r="AC90" s="8"/>
-      <c r="AD90" s="8"/>
-      <c r="AE90" s="8"/>
-      <c r="AF90" s="8"/>
-    </row>
-    <row r="91" spans="1:32">
+    </row>
+    <row r="91" spans="1:28">
       <c r="A91" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
@@ -5968,14 +5567,10 @@
       <c r="Z91" s="8"/>
       <c r="AA91" s="8"/>
       <c r="AB91" s="8"/>
-      <c r="AC91" s="8"/>
-      <c r="AD91" s="8"/>
-      <c r="AE91" s="8"/>
-      <c r="AF91" s="8"/>
-    </row>
-    <row r="92" spans="1:32">
+    </row>
+    <row r="92" spans="1:28">
       <c r="A92" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
@@ -6004,14 +5599,10 @@
       <c r="Z92" s="8"/>
       <c r="AA92" s="8"/>
       <c r="AB92" s="8"/>
-      <c r="AC92" s="8"/>
-      <c r="AD92" s="8"/>
-      <c r="AE92" s="8"/>
-      <c r="AF92" s="8"/>
-    </row>
-    <row r="93" spans="1:32">
+    </row>
+    <row r="93" spans="1:28">
       <c r="A93" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
@@ -6040,14 +5631,10 @@
       <c r="Z93" s="8"/>
       <c r="AA93" s="8"/>
       <c r="AB93" s="8"/>
-      <c r="AC93" s="8"/>
-      <c r="AD93" s="8"/>
-      <c r="AE93" s="8"/>
-      <c r="AF93" s="8"/>
-    </row>
-    <row r="94" spans="1:32">
+    </row>
+    <row r="94" spans="1:28">
       <c r="A94" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
@@ -6076,14 +5663,10 @@
       <c r="Z94" s="8"/>
       <c r="AA94" s="8"/>
       <c r="AB94" s="8"/>
-      <c r="AC94" s="8"/>
-      <c r="AD94" s="8"/>
-      <c r="AE94" s="8"/>
-      <c r="AF94" s="8"/>
-    </row>
-    <row r="95" spans="1:32">
+    </row>
+    <row r="95" spans="1:28">
       <c r="A95" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
@@ -6112,14 +5695,10 @@
       <c r="Z95" s="8"/>
       <c r="AA95" s="8"/>
       <c r="AB95" s="8"/>
-      <c r="AC95" s="8"/>
-      <c r="AD95" s="8"/>
-      <c r="AE95" s="8"/>
-      <c r="AF95" s="8"/>
-    </row>
-    <row r="96" spans="1:32">
+    </row>
+    <row r="96" spans="1:28">
       <c r="A96" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
@@ -6148,14 +5727,10 @@
       <c r="Z96" s="8"/>
       <c r="AA96" s="8"/>
       <c r="AB96" s="8"/>
-      <c r="AC96" s="8"/>
-      <c r="AD96" s="8"/>
-      <c r="AE96" s="8"/>
-      <c r="AF96" s="8"/>
-    </row>
-    <row r="97" spans="1:32">
+    </row>
+    <row r="97" spans="1:28">
       <c r="A97" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
@@ -6184,14 +5759,10 @@
       <c r="Z97" s="8"/>
       <c r="AA97" s="8"/>
       <c r="AB97" s="8"/>
-      <c r="AC97" s="8"/>
-      <c r="AD97" s="8"/>
-      <c r="AE97" s="8"/>
-      <c r="AF97" s="8"/>
-    </row>
-    <row r="98" spans="1:32">
+    </row>
+    <row r="98" spans="1:28">
       <c r="A98" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
@@ -6220,14 +5791,10 @@
       <c r="Z98" s="8"/>
       <c r="AA98" s="8"/>
       <c r="AB98" s="8"/>
-      <c r="AC98" s="8"/>
-      <c r="AD98" s="8"/>
-      <c r="AE98" s="8"/>
-      <c r="AF98" s="8"/>
-    </row>
-    <row r="99" spans="1:32">
+    </row>
+    <row r="99" spans="1:28">
       <c r="A99" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
@@ -6256,14 +5823,10 @@
       <c r="Z99" s="8"/>
       <c r="AA99" s="8"/>
       <c r="AB99" s="8"/>
-      <c r="AC99" s="8"/>
-      <c r="AD99" s="8"/>
-      <c r="AE99" s="8"/>
-      <c r="AF99" s="8"/>
-    </row>
-    <row r="100" spans="1:32">
+    </row>
+    <row r="100" spans="1:28">
       <c r="A100" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
@@ -6292,14 +5855,10 @@
       <c r="Z100" s="8"/>
       <c r="AA100" s="8"/>
       <c r="AB100" s="8"/>
-      <c r="AC100" s="8"/>
-      <c r="AD100" s="8"/>
-      <c r="AE100" s="8"/>
-      <c r="AF100" s="8"/>
-    </row>
-    <row r="101" spans="1:32">
+    </row>
+    <row r="101" spans="1:28">
       <c r="A101" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
@@ -6328,14 +5887,10 @@
       <c r="Z101" s="8"/>
       <c r="AA101" s="8"/>
       <c r="AB101" s="8"/>
-      <c r="AC101" s="8"/>
-      <c r="AD101" s="8"/>
-      <c r="AE101" s="8"/>
-      <c r="AF101" s="8"/>
-    </row>
-    <row r="102" spans="1:32">
+    </row>
+    <row r="102" spans="1:28">
       <c r="A102" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
@@ -6364,14 +5919,10 @@
       <c r="Z102" s="8"/>
       <c r="AA102" s="8"/>
       <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="8"/>
-      <c r="AF102" s="8"/>
-    </row>
-    <row r="103" spans="1:32">
+    </row>
+    <row r="103" spans="1:28">
       <c r="A103" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
@@ -6400,14 +5951,10 @@
       <c r="Z103" s="8"/>
       <c r="AA103" s="8"/>
       <c r="AB103" s="8"/>
-      <c r="AC103" s="8"/>
-      <c r="AD103" s="8"/>
-      <c r="AE103" s="8"/>
-      <c r="AF103" s="8"/>
-    </row>
-    <row r="104" spans="1:32">
+    </row>
+    <row r="104" spans="1:28">
       <c r="A104" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
@@ -6436,14 +5983,10 @@
       <c r="Z104" s="8"/>
       <c r="AA104" s="8"/>
       <c r="AB104" s="8"/>
-      <c r="AC104" s="8"/>
-      <c r="AD104" s="8"/>
-      <c r="AE104" s="8"/>
-      <c r="AF104" s="8"/>
-    </row>
-    <row r="105" spans="1:32">
+    </row>
+    <row r="105" spans="1:28">
       <c r="A105" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
@@ -6472,68 +6015,22 @@
       <c r="Z105" s="8"/>
       <c r="AA105" s="8"/>
       <c r="AB105" s="8"/>
-      <c r="AC105" s="8"/>
-      <c r="AD105" s="8"/>
-      <c r="AE105" s="8"/>
-      <c r="AF105" s="8"/>
-    </row>
-    <row r="106" spans="1:32">
-      <c r="A106" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B106" s="8"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
-      <c r="G106" s="8"/>
-      <c r="H106" s="8"/>
-      <c r="I106" s="8"/>
-      <c r="J106" s="8"/>
-      <c r="K106" s="8"/>
-      <c r="L106" s="8"/>
-      <c r="M106" s="8"/>
-      <c r="N106" s="8"/>
-      <c r="O106" s="8"/>
-      <c r="P106" s="8"/>
-      <c r="Q106" s="8"/>
-      <c r="R106" s="8"/>
-      <c r="S106" s="8"/>
-      <c r="T106" s="8"/>
-      <c r="U106" s="8"/>
-      <c r="V106" s="8"/>
-      <c r="W106" s="8"/>
-      <c r="X106" s="8"/>
-      <c r="Y106" s="8"/>
-      <c r="Z106" s="8"/>
-      <c r="AA106" s="8"/>
-      <c r="AB106" s="8"/>
-      <c r="AC106" s="8"/>
-      <c r="AD106" s="8"/>
-      <c r="AE106" s="8"/>
-      <c r="AF106" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:F6" xr:uid="{865A20BB-1F5D-416D-8AD5-2BCD3ABC6B25}">
-      <formula1>$G$6:$DG$6</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:F5" xr:uid="{865A20BB-1F5D-416D-8AD5-2BCD3ABC6B25}">
+      <formula1>$G$5:$DC$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A60B9CC8-BE80-475D-B087-1A2396777CC1}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4AA31AED-C3AE-4163-A2DF-E8904C96AB3D}">
           <x14:formula1>
-            <xm:f>description!$E$7:$H$7</xm:f>
+            <xm:f>description!$D$3:$H$3</xm:f>
           </x14:formula1>
-          <xm:sqref>B4:Q4</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5D11CD02-4B1B-4864-99D9-48419F1D75FF}">
-          <x14:formula1>
-            <xm:f>description!$E$6:$I$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>B3:AE3</xm:sqref>
+          <xm:sqref>B2:XFD2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6543,193 +6040,142 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A68D4BA7-81A7-496D-83F7-4CE2A3B40B1B}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="80.44140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="80.44140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>6</v>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="G3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H3" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="57.6">
+      <c r="A5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="57.6">
+      <c r="A6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="57.6">
-      <c r="A4" t="s">
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
         <v>130</v>
       </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="57.6">
-      <c r="A5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" t="s">
-        <v>112</v>
-      </c>
-      <c r="I6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data/raw_results/lanupro_vocabulary_general.xlsx
+++ b/data/raw_results/lanupro_vocabulary_general.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B848A5-0F2B-4CE8-B7F1-2AF1AF1F67FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93660A4A-1B8C-42B3-9B2B-2446EF5F4812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="270">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -420,12 +420,6 @@
     <t>deprecated_names</t>
   </si>
   <si>
-    <t>atol_ontology_sample_type_milk</t>
-  </si>
-  <si>
-    <t>atol_ontology_sample_type_meat</t>
-  </si>
-  <si>
     <t>colostrum</t>
   </si>
   <si>
@@ -465,14 +459,6 @@
     <t>any other deprecated names separated by a comma and space [, ]</t>
   </si>
   <si>
-    <t>number in the ATOL ontology when the sample type is milk
-In some cases the synonym depends on the sample type. E.g. in lanupro_ontology a generic name is used for e.g. fatty acids independent of the sample type, while ATOL uses separate numbers for milk or meat.</t>
-  </si>
-  <si>
-    <t>number in the ATOL ontology when the sample type is meat
-In some cases the synonym depends on the sample type. E.g. in lanupro_ontology a generic name is used for e.g. fatty acids independent of the sample type, while ATOL uses separate numbers for milk or meat.</t>
-  </si>
-  <si>
     <t>default variable unit when no units are specified in the variable name</t>
   </si>
   <si>
@@ -855,6 +841,12 @@
   </si>
   <si>
     <t>Format of the variable</t>
+  </si>
+  <si>
+    <t>test_variable</t>
+  </si>
+  <si>
+    <t>test_level</t>
   </si>
 </sst>
 </file>
@@ -1710,7 +1702,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1735,6 +1727,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="112">
     <cellStyle name="20% - Accent1 2" xfId="19" xr:uid="{77E55010-737E-41F1-998F-D4B5A5EBB76A}"/>
@@ -2180,7 +2173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB33DE6-D058-433F-9B7D-5598CD0261F2}">
-  <dimension ref="A1:AB105"/>
+  <dimension ref="A1:AC105"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17" style="4" customWidth="1"/>
@@ -2204,7 +2197,7 @@
     <col min="28" max="28" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1">
+    <row r="1" spans="1:29" s="1" customFormat="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2218,79 +2211,82 @@
         <v>2</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>111</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="O1" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="S1" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="W1" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="AA1" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="Y1" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="Z1" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="AA1" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="AB1" s="6" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28">
+      <c r="AC1" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -2304,7 +2300,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>7</v>
@@ -2346,7 +2342,7 @@
         <v>6</v>
       </c>
       <c r="S2" s="8" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="T2" s="8" t="s">
         <v>6</v>
@@ -2375,28 +2371,31 @@
       <c r="AB2" s="8" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="3" spans="1:28">
+      <c r="AC2" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
       <c r="A3" s="5" t="s">
         <v>126</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>114</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>114</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>114</v>
@@ -2411,13 +2410,13 @@
         <v>114</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="O3" s="8" t="s">
         <v>114</v>
@@ -2456,13 +2455,14 @@
         <v>114</v>
       </c>
       <c r="AA3" s="8" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AB3" s="8" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="4" spans="1:28" ht="86.4">
+      <c r="AC3" s="8"/>
+    </row>
+    <row r="4" spans="1:29" ht="86.4">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
@@ -2476,39 +2476,39 @@
         <v>123</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>122</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="10"/>
       <c r="J4" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
       <c r="S4" s="10" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="T4" s="10"/>
       <c r="U4" s="10"/>
@@ -2519,10 +2519,11 @@
       <c r="Z4" s="10"/>
       <c r="AA4" s="10"/>
       <c r="AB4" s="10" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28">
+        <v>256</v>
+      </c>
+      <c r="AC4" s="8"/>
+    </row>
+    <row r="5" spans="1:29">
       <c r="A5" s="5" t="s">
         <v>112</v>
       </c>
@@ -2571,8 +2572,9 @@
       <c r="Z5" s="8"/>
       <c r="AA5" s="8"/>
       <c r="AB5" s="8"/>
-    </row>
-    <row r="6" spans="1:28">
+      <c r="AC5" s="8"/>
+    </row>
+    <row r="6" spans="1:29">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
@@ -2592,7 +2594,7 @@
         <v>114</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>114</v>
@@ -2607,13 +2609,13 @@
         <v>114</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="O6" s="8" t="s">
         <v>114</v>
@@ -2657,35 +2659,38 @@
       <c r="AB6" s="8" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="7" spans="1:28">
+      <c r="AC6" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29">
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8" t="s">
         <v>113</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -2701,8 +2706,9 @@
       <c r="Z7" s="8"/>
       <c r="AA7" s="8"/>
       <c r="AB7" s="8"/>
-    </row>
-    <row r="8" spans="1:28">
+      <c r="AC7" s="8"/>
+    </row>
+    <row r="8" spans="1:29">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -2713,23 +2719,23 @@
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
       <c r="K8" s="8"/>
       <c r="L8" s="8" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
@@ -2745,8 +2751,9 @@
       <c r="Z8" s="8"/>
       <c r="AA8" s="8"/>
       <c r="AB8" s="8"/>
-    </row>
-    <row r="9" spans="1:28">
+      <c r="AC8" s="8"/>
+    </row>
+    <row r="9" spans="1:29">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -2757,23 +2764,23 @@
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="8" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
       <c r="L9" s="8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
@@ -2789,8 +2796,9 @@
       <c r="Z9" s="8"/>
       <c r="AA9" s="8"/>
       <c r="AB9" s="8"/>
-    </row>
-    <row r="10" spans="1:28">
+      <c r="AC9" s="8"/>
+    </row>
+    <row r="10" spans="1:29">
       <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
@@ -2802,20 +2810,20 @@
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
       <c r="G10" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
       <c r="L10" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -2831,8 +2839,9 @@
       <c r="Z10" s="8"/>
       <c r="AA10" s="8"/>
       <c r="AB10" s="8"/>
-    </row>
-    <row r="11" spans="1:28">
+      <c r="AC10" s="8"/>
+    </row>
+    <row r="11" spans="1:29">
       <c r="A11" s="5" t="s">
         <v>13</v>
       </c>
@@ -2844,20 +2853,20 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
       <c r="K11" s="8"/>
       <c r="L11" s="8" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
@@ -2873,8 +2882,9 @@
       <c r="Z11" s="8"/>
       <c r="AA11" s="8"/>
       <c r="AB11" s="8"/>
-    </row>
-    <row r="12" spans="1:28">
+      <c r="AC11" s="8"/>
+    </row>
+    <row r="12" spans="1:29">
       <c r="A12" s="5" t="s">
         <v>14</v>
       </c>
@@ -2891,13 +2901,13 @@
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
@@ -2913,8 +2923,9 @@
       <c r="Z12" s="8"/>
       <c r="AA12" s="8"/>
       <c r="AB12" s="8"/>
-    </row>
-    <row r="13" spans="1:28">
+      <c r="AC12" s="8"/>
+    </row>
+    <row r="13" spans="1:29">
       <c r="A13" s="5" t="s">
         <v>15</v>
       </c>
@@ -2931,13 +2942,13 @@
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -2953,15 +2964,16 @@
       <c r="Z13" s="8"/>
       <c r="AA13" s="8"/>
       <c r="AB13" s="8"/>
-    </row>
-    <row r="14" spans="1:28">
+      <c r="AC13" s="8"/>
+    </row>
+    <row r="14" spans="1:29">
       <c r="A14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
@@ -2971,13 +2983,13 @@
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -2993,15 +3005,16 @@
       <c r="Z14" s="8"/>
       <c r="AA14" s="8"/>
       <c r="AB14" s="8"/>
-    </row>
-    <row r="15" spans="1:28">
+      <c r="AC14" s="8"/>
+    </row>
+    <row r="15" spans="1:29">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
@@ -3011,13 +3024,13 @@
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="O15" s="8"/>
       <c r="P15" s="8"/>
@@ -3033,15 +3046,16 @@
       <c r="Z15" s="8"/>
       <c r="AA15" s="8"/>
       <c r="AB15" s="8"/>
-    </row>
-    <row r="16" spans="1:28">
+      <c r="AC15" s="8"/>
+    </row>
+    <row r="16" spans="1:29">
       <c r="A16" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
@@ -3051,13 +3065,13 @@
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -3073,15 +3087,16 @@
       <c r="Z16" s="8"/>
       <c r="AA16" s="8"/>
       <c r="AB16" s="8"/>
-    </row>
-    <row r="17" spans="1:28">
+      <c r="AC16" s="8"/>
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
@@ -3091,11 +3106,11 @@
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="M17" s="8"/>
       <c r="N17" s="8" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
@@ -3111,15 +3126,16 @@
       <c r="Z17" s="8"/>
       <c r="AA17" s="8"/>
       <c r="AB17" s="8"/>
-    </row>
-    <row r="18" spans="1:28">
+      <c r="AC17" s="8"/>
+    </row>
+    <row r="18" spans="1:29">
       <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
@@ -3129,11 +3145,11 @@
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="M18" s="8"/>
       <c r="N18" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
@@ -3149,15 +3165,16 @@
       <c r="Z18" s="8"/>
       <c r="AA18" s="8"/>
       <c r="AB18" s="8"/>
-    </row>
-    <row r="19" spans="1:28">
+      <c r="AC18" s="8"/>
+    </row>
+    <row r="19" spans="1:29">
       <c r="A19" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
@@ -3167,11 +3184,11 @@
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="M19" s="8"/>
       <c r="N19" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
@@ -3187,15 +3204,16 @@
       <c r="Z19" s="8"/>
       <c r="AA19" s="8"/>
       <c r="AB19" s="8"/>
-    </row>
-    <row r="20" spans="1:28">
+      <c r="AC19" s="8"/>
+    </row>
+    <row r="20" spans="1:29">
       <c r="A20" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
@@ -3205,7 +3223,7 @@
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
@@ -3223,15 +3241,16 @@
       <c r="Z20" s="8"/>
       <c r="AA20" s="8"/>
       <c r="AB20" s="8"/>
-    </row>
-    <row r="21" spans="1:28">
+      <c r="AC20" s="8"/>
+    </row>
+    <row r="21" spans="1:29">
       <c r="A21" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
@@ -3241,7 +3260,7 @@
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
@@ -3259,15 +3278,16 @@
       <c r="Z21" s="8"/>
       <c r="AA21" s="8"/>
       <c r="AB21" s="8"/>
-    </row>
-    <row r="22" spans="1:28">
+      <c r="AC21" s="8"/>
+    </row>
+    <row r="22" spans="1:29">
       <c r="A22" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
@@ -3277,7 +3297,7 @@
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
       <c r="L22" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
@@ -3295,15 +3315,16 @@
       <c r="Z22" s="8"/>
       <c r="AA22" s="8"/>
       <c r="AB22" s="8"/>
-    </row>
-    <row r="23" spans="1:28">
+      <c r="AC22" s="8"/>
+    </row>
+    <row r="23" spans="1:29">
       <c r="A23" s="5" t="s">
         <v>25</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E23" s="8"/>
       <c r="F23" s="8"/>
@@ -3313,7 +3334,7 @@
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
       <c r="L23" s="8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
@@ -3331,15 +3352,16 @@
       <c r="Z23" s="8"/>
       <c r="AA23" s="8"/>
       <c r="AB23" s="8"/>
-    </row>
-    <row r="24" spans="1:28">
+      <c r="AC23" s="8"/>
+    </row>
+    <row r="24" spans="1:29">
       <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
@@ -3349,7 +3371,7 @@
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
@@ -3367,15 +3389,16 @@
       <c r="Z24" s="8"/>
       <c r="AA24" s="8"/>
       <c r="AB24" s="8"/>
-    </row>
-    <row r="25" spans="1:28">
+      <c r="AC24" s="8"/>
+    </row>
+    <row r="25" spans="1:29">
       <c r="A25" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
@@ -3385,7 +3408,7 @@
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
@@ -3403,15 +3426,16 @@
       <c r="Z25" s="8"/>
       <c r="AA25" s="8"/>
       <c r="AB25" s="8"/>
-    </row>
-    <row r="26" spans="1:28">
+      <c r="AC25" s="8"/>
+    </row>
+    <row r="26" spans="1:29">
       <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
@@ -3421,7 +3445,7 @@
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
@@ -3439,15 +3463,16 @@
       <c r="Z26" s="8"/>
       <c r="AA26" s="8"/>
       <c r="AB26" s="8"/>
-    </row>
-    <row r="27" spans="1:28">
+      <c r="AC26" s="8"/>
+    </row>
+    <row r="27" spans="1:29">
       <c r="A27" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
@@ -3457,7 +3482,7 @@
       <c r="J27" s="8"/>
       <c r="K27" s="8"/>
       <c r="L27" s="8" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
@@ -3475,15 +3500,16 @@
       <c r="Z27" s="8"/>
       <c r="AA27" s="8"/>
       <c r="AB27" s="8"/>
-    </row>
-    <row r="28" spans="1:28">
+      <c r="AC27" s="8"/>
+    </row>
+    <row r="28" spans="1:29">
       <c r="A28" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
@@ -3493,7 +3519,7 @@
       <c r="J28" s="8"/>
       <c r="K28" s="8"/>
       <c r="L28" s="8" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="M28" s="8"/>
       <c r="N28" s="8"/>
@@ -3511,15 +3537,16 @@
       <c r="Z28" s="8"/>
       <c r="AA28" s="8"/>
       <c r="AB28" s="8"/>
-    </row>
-    <row r="29" spans="1:28">
+      <c r="AC28" s="8"/>
+    </row>
+    <row r="29" spans="1:29">
       <c r="A29" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
@@ -3529,7 +3556,7 @@
       <c r="J29" s="8"/>
       <c r="K29" s="8"/>
       <c r="L29" s="8" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="M29" s="8"/>
       <c r="N29" s="8"/>
@@ -3547,15 +3574,16 @@
       <c r="Z29" s="8"/>
       <c r="AA29" s="8"/>
       <c r="AB29" s="8"/>
-    </row>
-    <row r="30" spans="1:28">
+      <c r="AC29" s="8"/>
+    </row>
+    <row r="30" spans="1:29">
       <c r="A30" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
@@ -3565,7 +3593,7 @@
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
       <c r="L30" s="8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
@@ -3583,15 +3611,16 @@
       <c r="Z30" s="8"/>
       <c r="AA30" s="8"/>
       <c r="AB30" s="8"/>
-    </row>
-    <row r="31" spans="1:28">
+      <c r="AC30" s="8"/>
+    </row>
+    <row r="31" spans="1:29">
       <c r="A31" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
@@ -3601,7 +3630,7 @@
       <c r="J31" s="8"/>
       <c r="K31" s="8"/>
       <c r="L31" s="8" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M31" s="8"/>
       <c r="N31" s="8"/>
@@ -3619,15 +3648,16 @@
       <c r="Z31" s="8"/>
       <c r="AA31" s="8"/>
       <c r="AB31" s="8"/>
-    </row>
-    <row r="32" spans="1:28">
+      <c r="AC31" s="8"/>
+    </row>
+    <row r="32" spans="1:29">
       <c r="A32" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
@@ -3637,7 +3667,7 @@
       <c r="J32" s="8"/>
       <c r="K32" s="8"/>
       <c r="L32" s="8" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="M32" s="8"/>
       <c r="N32" s="8"/>
@@ -3655,15 +3685,16 @@
       <c r="Z32" s="8"/>
       <c r="AA32" s="8"/>
       <c r="AB32" s="8"/>
-    </row>
-    <row r="33" spans="1:28">
+      <c r="AC32" s="8"/>
+    </row>
+    <row r="33" spans="1:29">
       <c r="A33" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
@@ -3673,7 +3704,7 @@
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
       <c r="L33" s="8" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="M33" s="8"/>
       <c r="N33" s="8"/>
@@ -3691,15 +3722,16 @@
       <c r="Z33" s="8"/>
       <c r="AA33" s="8"/>
       <c r="AB33" s="8"/>
-    </row>
-    <row r="34" spans="1:28">
+      <c r="AC33" s="8"/>
+    </row>
+    <row r="34" spans="1:29">
       <c r="A34" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
@@ -3709,7 +3741,7 @@
       <c r="J34" s="8"/>
       <c r="K34" s="8"/>
       <c r="L34" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="M34" s="8"/>
       <c r="N34" s="8"/>
@@ -3727,8 +3759,9 @@
       <c r="Z34" s="8"/>
       <c r="AA34" s="8"/>
       <c r="AB34" s="8"/>
-    </row>
-    <row r="35" spans="1:28">
+      <c r="AC34" s="8"/>
+    </row>
+    <row r="35" spans="1:29">
       <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
@@ -3743,7 +3776,7 @@
       <c r="J35" s="8"/>
       <c r="K35" s="8"/>
       <c r="L35" s="8" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M35" s="8"/>
       <c r="N35" s="8"/>
@@ -3761,8 +3794,9 @@
       <c r="Z35" s="8"/>
       <c r="AA35" s="8"/>
       <c r="AB35" s="8"/>
-    </row>
-    <row r="36" spans="1:28">
+      <c r="AC35" s="8"/>
+    </row>
+    <row r="36" spans="1:29">
       <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
@@ -3777,7 +3811,7 @@
       <c r="J36" s="8"/>
       <c r="K36" s="8"/>
       <c r="L36" s="8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="M36" s="8"/>
       <c r="N36" s="8"/>
@@ -3795,8 +3829,9 @@
       <c r="Z36" s="8"/>
       <c r="AA36" s="8"/>
       <c r="AB36" s="8"/>
-    </row>
-    <row r="37" spans="1:28">
+      <c r="AC36" s="8"/>
+    </row>
+    <row r="37" spans="1:29">
       <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
@@ -3811,7 +3846,7 @@
       <c r="J37" s="8"/>
       <c r="K37" s="8"/>
       <c r="L37" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="M37" s="8"/>
       <c r="N37" s="8"/>
@@ -3829,8 +3864,9 @@
       <c r="Z37" s="8"/>
       <c r="AA37" s="8"/>
       <c r="AB37" s="8"/>
-    </row>
-    <row r="38" spans="1:28">
+      <c r="AC37" s="8"/>
+    </row>
+    <row r="38" spans="1:29">
       <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
@@ -3845,7 +3881,7 @@
       <c r="J38" s="8"/>
       <c r="K38" s="8"/>
       <c r="L38" s="8" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="M38" s="8"/>
       <c r="N38" s="8"/>
@@ -3863,8 +3899,9 @@
       <c r="Z38" s="8"/>
       <c r="AA38" s="8"/>
       <c r="AB38" s="8"/>
-    </row>
-    <row r="39" spans="1:28">
+      <c r="AC38" s="8"/>
+    </row>
+    <row r="39" spans="1:29">
       <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
@@ -3879,7 +3916,7 @@
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
       <c r="L39" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="M39" s="8"/>
       <c r="N39" s="8"/>
@@ -3897,8 +3934,9 @@
       <c r="Z39" s="8"/>
       <c r="AA39" s="8"/>
       <c r="AB39" s="8"/>
-    </row>
-    <row r="40" spans="1:28">
+      <c r="AC39" s="8"/>
+    </row>
+    <row r="40" spans="1:29">
       <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
@@ -3913,7 +3951,7 @@
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
       <c r="L40" s="8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="M40" s="8"/>
       <c r="N40" s="8"/>
@@ -3931,8 +3969,9 @@
       <c r="Z40" s="8"/>
       <c r="AA40" s="8"/>
       <c r="AB40" s="8"/>
-    </row>
-    <row r="41" spans="1:28">
+      <c r="AC40" s="8"/>
+    </row>
+    <row r="41" spans="1:29">
       <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
@@ -3947,7 +3986,7 @@
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
       <c r="L41" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M41" s="8"/>
       <c r="N41" s="8"/>
@@ -3965,8 +4004,9 @@
       <c r="Z41" s="8"/>
       <c r="AA41" s="8"/>
       <c r="AB41" s="8"/>
-    </row>
-    <row r="42" spans="1:28">
+      <c r="AC41" s="8"/>
+    </row>
+    <row r="42" spans="1:29">
       <c r="A42" s="5" t="s">
         <v>44</v>
       </c>
@@ -3981,7 +4021,7 @@
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
       <c r="L42" s="8" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="M42" s="8"/>
       <c r="N42" s="8"/>
@@ -3999,8 +4039,9 @@
       <c r="Z42" s="8"/>
       <c r="AA42" s="8"/>
       <c r="AB42" s="8"/>
-    </row>
-    <row r="43" spans="1:28">
+      <c r="AC42" s="8"/>
+    </row>
+    <row r="43" spans="1:29">
       <c r="A43" s="5" t="s">
         <v>45</v>
       </c>
@@ -4031,8 +4072,9 @@
       <c r="Z43" s="8"/>
       <c r="AA43" s="8"/>
       <c r="AB43" s="8"/>
-    </row>
-    <row r="44" spans="1:28">
+      <c r="AC43" s="8"/>
+    </row>
+    <row r="44" spans="1:29">
       <c r="A44" s="5" t="s">
         <v>46</v>
       </c>
@@ -4063,8 +4105,9 @@
       <c r="Z44" s="8"/>
       <c r="AA44" s="8"/>
       <c r="AB44" s="8"/>
-    </row>
-    <row r="45" spans="1:28">
+      <c r="AC44" s="8"/>
+    </row>
+    <row r="45" spans="1:29">
       <c r="A45" s="5" t="s">
         <v>47</v>
       </c>
@@ -4095,8 +4138,9 @@
       <c r="Z45" s="8"/>
       <c r="AA45" s="8"/>
       <c r="AB45" s="8"/>
-    </row>
-    <row r="46" spans="1:28">
+      <c r="AC45" s="8"/>
+    </row>
+    <row r="46" spans="1:29">
       <c r="A46" s="5" t="s">
         <v>48</v>
       </c>
@@ -4127,8 +4171,9 @@
       <c r="Z46" s="8"/>
       <c r="AA46" s="8"/>
       <c r="AB46" s="8"/>
-    </row>
-    <row r="47" spans="1:28">
+      <c r="AC46" s="8"/>
+    </row>
+    <row r="47" spans="1:29">
       <c r="A47" s="5" t="s">
         <v>49</v>
       </c>
@@ -4159,8 +4204,9 @@
       <c r="Z47" s="8"/>
       <c r="AA47" s="8"/>
       <c r="AB47" s="8"/>
-    </row>
-    <row r="48" spans="1:28">
+      <c r="AC47" s="8"/>
+    </row>
+    <row r="48" spans="1:29">
       <c r="A48" s="5" t="s">
         <v>50</v>
       </c>
@@ -4191,8 +4237,9 @@
       <c r="Z48" s="8"/>
       <c r="AA48" s="8"/>
       <c r="AB48" s="8"/>
-    </row>
-    <row r="49" spans="1:28">
+      <c r="AC48" s="8"/>
+    </row>
+    <row r="49" spans="1:29">
       <c r="A49" s="5" t="s">
         <v>51</v>
       </c>
@@ -4223,8 +4270,9 @@
       <c r="Z49" s="8"/>
       <c r="AA49" s="8"/>
       <c r="AB49" s="8"/>
-    </row>
-    <row r="50" spans="1:28">
+      <c r="AC49" s="8"/>
+    </row>
+    <row r="50" spans="1:29">
       <c r="A50" s="5" t="s">
         <v>52</v>
       </c>
@@ -4255,8 +4303,9 @@
       <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
       <c r="AB50" s="8"/>
-    </row>
-    <row r="51" spans="1:28">
+      <c r="AC50" s="8"/>
+    </row>
+    <row r="51" spans="1:29">
       <c r="A51" s="5" t="s">
         <v>53</v>
       </c>
@@ -4287,8 +4336,9 @@
       <c r="Z51" s="8"/>
       <c r="AA51" s="8"/>
       <c r="AB51" s="8"/>
-    </row>
-    <row r="52" spans="1:28">
+      <c r="AC51" s="8"/>
+    </row>
+    <row r="52" spans="1:29">
       <c r="A52" s="5" t="s">
         <v>54</v>
       </c>
@@ -4319,8 +4369,9 @@
       <c r="Z52" s="8"/>
       <c r="AA52" s="8"/>
       <c r="AB52" s="8"/>
-    </row>
-    <row r="53" spans="1:28">
+      <c r="AC52" s="8"/>
+    </row>
+    <row r="53" spans="1:29">
       <c r="A53" s="5" t="s">
         <v>55</v>
       </c>
@@ -4351,8 +4402,9 @@
       <c r="Z53" s="8"/>
       <c r="AA53" s="8"/>
       <c r="AB53" s="8"/>
-    </row>
-    <row r="54" spans="1:28">
+      <c r="AC53" s="8"/>
+    </row>
+    <row r="54" spans="1:29">
       <c r="A54" s="5" t="s">
         <v>56</v>
       </c>
@@ -4383,8 +4435,9 @@
       <c r="Z54" s="8"/>
       <c r="AA54" s="8"/>
       <c r="AB54" s="8"/>
-    </row>
-    <row r="55" spans="1:28">
+      <c r="AC54" s="8"/>
+    </row>
+    <row r="55" spans="1:29">
       <c r="A55" s="5" t="s">
         <v>57</v>
       </c>
@@ -4415,8 +4468,9 @@
       <c r="Z55" s="8"/>
       <c r="AA55" s="8"/>
       <c r="AB55" s="8"/>
-    </row>
-    <row r="56" spans="1:28">
+      <c r="AC55" s="8"/>
+    </row>
+    <row r="56" spans="1:29">
       <c r="A56" s="5" t="s">
         <v>58</v>
       </c>
@@ -4447,8 +4501,9 @@
       <c r="Z56" s="8"/>
       <c r="AA56" s="8"/>
       <c r="AB56" s="8"/>
-    </row>
-    <row r="57" spans="1:28">
+      <c r="AC56" s="8"/>
+    </row>
+    <row r="57" spans="1:29">
       <c r="A57" s="5" t="s">
         <v>59</v>
       </c>
@@ -4479,8 +4534,9 @@
       <c r="Z57" s="8"/>
       <c r="AA57" s="8"/>
       <c r="AB57" s="8"/>
-    </row>
-    <row r="58" spans="1:28">
+      <c r="AC57" s="8"/>
+    </row>
+    <row r="58" spans="1:29">
       <c r="A58" s="5" t="s">
         <v>60</v>
       </c>
@@ -4511,8 +4567,9 @@
       <c r="Z58" s="8"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-    </row>
-    <row r="59" spans="1:28">
+      <c r="AC58" s="8"/>
+    </row>
+    <row r="59" spans="1:29">
       <c r="A59" s="5" t="s">
         <v>61</v>
       </c>
@@ -4543,8 +4600,9 @@
       <c r="Z59" s="8"/>
       <c r="AA59" s="8"/>
       <c r="AB59" s="8"/>
-    </row>
-    <row r="60" spans="1:28">
+      <c r="AC59" s="8"/>
+    </row>
+    <row r="60" spans="1:29">
       <c r="A60" s="5" t="s">
         <v>62</v>
       </c>
@@ -4575,8 +4633,9 @@
       <c r="Z60" s="8"/>
       <c r="AA60" s="8"/>
       <c r="AB60" s="8"/>
-    </row>
-    <row r="61" spans="1:28">
+      <c r="AC60" s="8"/>
+    </row>
+    <row r="61" spans="1:29">
       <c r="A61" s="5" t="s">
         <v>63</v>
       </c>
@@ -4607,8 +4666,9 @@
       <c r="Z61" s="8"/>
       <c r="AA61" s="8"/>
       <c r="AB61" s="8"/>
-    </row>
-    <row r="62" spans="1:28">
+      <c r="AC61" s="8"/>
+    </row>
+    <row r="62" spans="1:29">
       <c r="A62" s="5" t="s">
         <v>64</v>
       </c>
@@ -4639,8 +4699,9 @@
       <c r="Z62" s="8"/>
       <c r="AA62" s="8"/>
       <c r="AB62" s="8"/>
-    </row>
-    <row r="63" spans="1:28">
+      <c r="AC62" s="8"/>
+    </row>
+    <row r="63" spans="1:29">
       <c r="A63" s="5" t="s">
         <v>65</v>
       </c>
@@ -4671,8 +4732,9 @@
       <c r="Z63" s="8"/>
       <c r="AA63" s="8"/>
       <c r="AB63" s="8"/>
-    </row>
-    <row r="64" spans="1:28">
+      <c r="AC63" s="8"/>
+    </row>
+    <row r="64" spans="1:29">
       <c r="A64" s="5" t="s">
         <v>66</v>
       </c>
@@ -4703,8 +4765,9 @@
       <c r="Z64" s="8"/>
       <c r="AA64" s="8"/>
       <c r="AB64" s="8"/>
-    </row>
-    <row r="65" spans="1:28">
+      <c r="AC64" s="8"/>
+    </row>
+    <row r="65" spans="1:29">
       <c r="A65" s="5" t="s">
         <v>67</v>
       </c>
@@ -4735,8 +4798,9 @@
       <c r="Z65" s="8"/>
       <c r="AA65" s="8"/>
       <c r="AB65" s="8"/>
-    </row>
-    <row r="66" spans="1:28">
+      <c r="AC65" s="8"/>
+    </row>
+    <row r="66" spans="1:29">
       <c r="A66" s="5" t="s">
         <v>68</v>
       </c>
@@ -4767,8 +4831,9 @@
       <c r="Z66" s="8"/>
       <c r="AA66" s="8"/>
       <c r="AB66" s="8"/>
-    </row>
-    <row r="67" spans="1:28">
+      <c r="AC66" s="8"/>
+    </row>
+    <row r="67" spans="1:29">
       <c r="A67" s="5" t="s">
         <v>69</v>
       </c>
@@ -4799,8 +4864,9 @@
       <c r="Z67" s="8"/>
       <c r="AA67" s="8"/>
       <c r="AB67" s="8"/>
-    </row>
-    <row r="68" spans="1:28">
+      <c r="AC67" s="8"/>
+    </row>
+    <row r="68" spans="1:29">
       <c r="A68" s="5" t="s">
         <v>70</v>
       </c>
@@ -4831,8 +4897,9 @@
       <c r="Z68" s="8"/>
       <c r="AA68" s="8"/>
       <c r="AB68" s="8"/>
-    </row>
-    <row r="69" spans="1:28">
+      <c r="AC68" s="8"/>
+    </row>
+    <row r="69" spans="1:29">
       <c r="A69" s="5" t="s">
         <v>71</v>
       </c>
@@ -4863,8 +4930,9 @@
       <c r="Z69" s="8"/>
       <c r="AA69" s="8"/>
       <c r="AB69" s="8"/>
-    </row>
-    <row r="70" spans="1:28">
+      <c r="AC69" s="8"/>
+    </row>
+    <row r="70" spans="1:29">
       <c r="A70" s="5" t="s">
         <v>72</v>
       </c>
@@ -4895,8 +4963,9 @@
       <c r="Z70" s="8"/>
       <c r="AA70" s="8"/>
       <c r="AB70" s="8"/>
-    </row>
-    <row r="71" spans="1:28">
+      <c r="AC70" s="8"/>
+    </row>
+    <row r="71" spans="1:29">
       <c r="A71" s="5" t="s">
         <v>73</v>
       </c>
@@ -4927,8 +4996,9 @@
       <c r="Z71" s="8"/>
       <c r="AA71" s="8"/>
       <c r="AB71" s="8"/>
-    </row>
-    <row r="72" spans="1:28">
+      <c r="AC71" s="8"/>
+    </row>
+    <row r="72" spans="1:29">
       <c r="A72" s="5" t="s">
         <v>74</v>
       </c>
@@ -4959,8 +5029,9 @@
       <c r="Z72" s="8"/>
       <c r="AA72" s="8"/>
       <c r="AB72" s="8"/>
-    </row>
-    <row r="73" spans="1:28">
+      <c r="AC72" s="8"/>
+    </row>
+    <row r="73" spans="1:29">
       <c r="A73" s="5" t="s">
         <v>75</v>
       </c>
@@ -4991,8 +5062,9 @@
       <c r="Z73" s="8"/>
       <c r="AA73" s="8"/>
       <c r="AB73" s="8"/>
-    </row>
-    <row r="74" spans="1:28">
+      <c r="AC73" s="8"/>
+    </row>
+    <row r="74" spans="1:29">
       <c r="A74" s="5" t="s">
         <v>76</v>
       </c>
@@ -5023,8 +5095,9 @@
       <c r="Z74" s="8"/>
       <c r="AA74" s="8"/>
       <c r="AB74" s="8"/>
-    </row>
-    <row r="75" spans="1:28">
+      <c r="AC74" s="8"/>
+    </row>
+    <row r="75" spans="1:29">
       <c r="A75" s="5" t="s">
         <v>77</v>
       </c>
@@ -5055,8 +5128,9 @@
       <c r="Z75" s="8"/>
       <c r="AA75" s="8"/>
       <c r="AB75" s="8"/>
-    </row>
-    <row r="76" spans="1:28">
+      <c r="AC75" s="8"/>
+    </row>
+    <row r="76" spans="1:29">
       <c r="A76" s="5" t="s">
         <v>78</v>
       </c>
@@ -5087,8 +5161,9 @@
       <c r="Z76" s="8"/>
       <c r="AA76" s="8"/>
       <c r="AB76" s="8"/>
-    </row>
-    <row r="77" spans="1:28">
+      <c r="AC76" s="8"/>
+    </row>
+    <row r="77" spans="1:29">
       <c r="A77" s="5" t="s">
         <v>79</v>
       </c>
@@ -5119,8 +5194,9 @@
       <c r="Z77" s="8"/>
       <c r="AA77" s="8"/>
       <c r="AB77" s="8"/>
-    </row>
-    <row r="78" spans="1:28">
+      <c r="AC77" s="8"/>
+    </row>
+    <row r="78" spans="1:29">
       <c r="A78" s="5" t="s">
         <v>80</v>
       </c>
@@ -5151,8 +5227,9 @@
       <c r="Z78" s="8"/>
       <c r="AA78" s="8"/>
       <c r="AB78" s="8"/>
-    </row>
-    <row r="79" spans="1:28">
+      <c r="AC78" s="8"/>
+    </row>
+    <row r="79" spans="1:29">
       <c r="A79" s="5" t="s">
         <v>81</v>
       </c>
@@ -5183,8 +5260,9 @@
       <c r="Z79" s="8"/>
       <c r="AA79" s="8"/>
       <c r="AB79" s="8"/>
-    </row>
-    <row r="80" spans="1:28">
+      <c r="AC79" s="8"/>
+    </row>
+    <row r="80" spans="1:29">
       <c r="A80" s="5" t="s">
         <v>82</v>
       </c>
@@ -5215,8 +5293,9 @@
       <c r="Z80" s="8"/>
       <c r="AA80" s="8"/>
       <c r="AB80" s="8"/>
-    </row>
-    <row r="81" spans="1:28">
+      <c r="AC80" s="8"/>
+    </row>
+    <row r="81" spans="1:29">
       <c r="A81" s="5" t="s">
         <v>83</v>
       </c>
@@ -5247,8 +5326,9 @@
       <c r="Z81" s="8"/>
       <c r="AA81" s="8"/>
       <c r="AB81" s="8"/>
-    </row>
-    <row r="82" spans="1:28">
+      <c r="AC81" s="8"/>
+    </row>
+    <row r="82" spans="1:29">
       <c r="A82" s="5" t="s">
         <v>84</v>
       </c>
@@ -5279,8 +5359,9 @@
       <c r="Z82" s="8"/>
       <c r="AA82" s="8"/>
       <c r="AB82" s="8"/>
-    </row>
-    <row r="83" spans="1:28">
+      <c r="AC82" s="8"/>
+    </row>
+    <row r="83" spans="1:29">
       <c r="A83" s="5" t="s">
         <v>85</v>
       </c>
@@ -5311,8 +5392,9 @@
       <c r="Z83" s="8"/>
       <c r="AA83" s="8"/>
       <c r="AB83" s="8"/>
-    </row>
-    <row r="84" spans="1:28">
+      <c r="AC83" s="8"/>
+    </row>
+    <row r="84" spans="1:29">
       <c r="A84" s="5" t="s">
         <v>86</v>
       </c>
@@ -5343,8 +5425,9 @@
       <c r="Z84" s="8"/>
       <c r="AA84" s="8"/>
       <c r="AB84" s="8"/>
-    </row>
-    <row r="85" spans="1:28">
+      <c r="AC84" s="8"/>
+    </row>
+    <row r="85" spans="1:29">
       <c r="A85" s="5" t="s">
         <v>87</v>
       </c>
@@ -5375,8 +5458,9 @@
       <c r="Z85" s="8"/>
       <c r="AA85" s="8"/>
       <c r="AB85" s="8"/>
-    </row>
-    <row r="86" spans="1:28">
+      <c r="AC85" s="8"/>
+    </row>
+    <row r="86" spans="1:29">
       <c r="A86" s="5" t="s">
         <v>88</v>
       </c>
@@ -5407,8 +5491,9 @@
       <c r="Z86" s="8"/>
       <c r="AA86" s="8"/>
       <c r="AB86" s="8"/>
-    </row>
-    <row r="87" spans="1:28">
+      <c r="AC86" s="8"/>
+    </row>
+    <row r="87" spans="1:29">
       <c r="A87" s="5" t="s">
         <v>89</v>
       </c>
@@ -5439,8 +5524,9 @@
       <c r="Z87" s="8"/>
       <c r="AA87" s="8"/>
       <c r="AB87" s="8"/>
-    </row>
-    <row r="88" spans="1:28">
+      <c r="AC87" s="8"/>
+    </row>
+    <row r="88" spans="1:29">
       <c r="A88" s="5" t="s">
         <v>90</v>
       </c>
@@ -5471,8 +5557,9 @@
       <c r="Z88" s="8"/>
       <c r="AA88" s="8"/>
       <c r="AB88" s="8"/>
-    </row>
-    <row r="89" spans="1:28">
+      <c r="AC88" s="8"/>
+    </row>
+    <row r="89" spans="1:29">
       <c r="A89" s="5" t="s">
         <v>91</v>
       </c>
@@ -5503,8 +5590,9 @@
       <c r="Z89" s="8"/>
       <c r="AA89" s="8"/>
       <c r="AB89" s="8"/>
-    </row>
-    <row r="90" spans="1:28">
+      <c r="AC89" s="8"/>
+    </row>
+    <row r="90" spans="1:29">
       <c r="A90" s="5" t="s">
         <v>92</v>
       </c>
@@ -5535,8 +5623,9 @@
       <c r="Z90" s="8"/>
       <c r="AA90" s="8"/>
       <c r="AB90" s="8"/>
-    </row>
-    <row r="91" spans="1:28">
+      <c r="AC90" s="8"/>
+    </row>
+    <row r="91" spans="1:29">
       <c r="A91" s="5" t="s">
         <v>93</v>
       </c>
@@ -5567,8 +5656,9 @@
       <c r="Z91" s="8"/>
       <c r="AA91" s="8"/>
       <c r="AB91" s="8"/>
-    </row>
-    <row r="92" spans="1:28">
+      <c r="AC91" s="8"/>
+    </row>
+    <row r="92" spans="1:29">
       <c r="A92" s="5" t="s">
         <v>94</v>
       </c>
@@ -5599,8 +5689,9 @@
       <c r="Z92" s="8"/>
       <c r="AA92" s="8"/>
       <c r="AB92" s="8"/>
-    </row>
-    <row r="93" spans="1:28">
+      <c r="AC92" s="8"/>
+    </row>
+    <row r="93" spans="1:29">
       <c r="A93" s="5" t="s">
         <v>95</v>
       </c>
@@ -5631,8 +5722,9 @@
       <c r="Z93" s="8"/>
       <c r="AA93" s="8"/>
       <c r="AB93" s="8"/>
-    </row>
-    <row r="94" spans="1:28">
+      <c r="AC93" s="8"/>
+    </row>
+    <row r="94" spans="1:29">
       <c r="A94" s="5" t="s">
         <v>96</v>
       </c>
@@ -5663,8 +5755,9 @@
       <c r="Z94" s="8"/>
       <c r="AA94" s="8"/>
       <c r="AB94" s="8"/>
-    </row>
-    <row r="95" spans="1:28">
+      <c r="AC94" s="8"/>
+    </row>
+    <row r="95" spans="1:29">
       <c r="A95" s="5" t="s">
         <v>97</v>
       </c>
@@ -5695,8 +5788,9 @@
       <c r="Z95" s="8"/>
       <c r="AA95" s="8"/>
       <c r="AB95" s="8"/>
-    </row>
-    <row r="96" spans="1:28">
+      <c r="AC95" s="8"/>
+    </row>
+    <row r="96" spans="1:29">
       <c r="A96" s="5" t="s">
         <v>98</v>
       </c>
@@ -5727,8 +5821,9 @@
       <c r="Z96" s="8"/>
       <c r="AA96" s="8"/>
       <c r="AB96" s="8"/>
-    </row>
-    <row r="97" spans="1:28">
+      <c r="AC96" s="8"/>
+    </row>
+    <row r="97" spans="1:29">
       <c r="A97" s="5" t="s">
         <v>99</v>
       </c>
@@ -5759,8 +5854,9 @@
       <c r="Z97" s="8"/>
       <c r="AA97" s="8"/>
       <c r="AB97" s="8"/>
-    </row>
-    <row r="98" spans="1:28">
+      <c r="AC97" s="8"/>
+    </row>
+    <row r="98" spans="1:29">
       <c r="A98" s="5" t="s">
         <v>100</v>
       </c>
@@ -5791,8 +5887,9 @@
       <c r="Z98" s="8"/>
       <c r="AA98" s="8"/>
       <c r="AB98" s="8"/>
-    </row>
-    <row r="99" spans="1:28">
+      <c r="AC98" s="8"/>
+    </row>
+    <row r="99" spans="1:29">
       <c r="A99" s="5" t="s">
         <v>101</v>
       </c>
@@ -5823,8 +5920,9 @@
       <c r="Z99" s="8"/>
       <c r="AA99" s="8"/>
       <c r="AB99" s="8"/>
-    </row>
-    <row r="100" spans="1:28">
+      <c r="AC99" s="8"/>
+    </row>
+    <row r="100" spans="1:29">
       <c r="A100" s="5" t="s">
         <v>102</v>
       </c>
@@ -5855,8 +5953,9 @@
       <c r="Z100" s="8"/>
       <c r="AA100" s="8"/>
       <c r="AB100" s="8"/>
-    </row>
-    <row r="101" spans="1:28">
+      <c r="AC100" s="8"/>
+    </row>
+    <row r="101" spans="1:29">
       <c r="A101" s="5" t="s">
         <v>103</v>
       </c>
@@ -5887,8 +5986,9 @@
       <c r="Z101" s="8"/>
       <c r="AA101" s="8"/>
       <c r="AB101" s="8"/>
-    </row>
-    <row r="102" spans="1:28">
+      <c r="AC101" s="8"/>
+    </row>
+    <row r="102" spans="1:29">
       <c r="A102" s="5" t="s">
         <v>104</v>
       </c>
@@ -5919,8 +6019,9 @@
       <c r="Z102" s="8"/>
       <c r="AA102" s="8"/>
       <c r="AB102" s="8"/>
-    </row>
-    <row r="103" spans="1:28">
+      <c r="AC102" s="8"/>
+    </row>
+    <row r="103" spans="1:29">
       <c r="A103" s="5" t="s">
         <v>105</v>
       </c>
@@ -5951,8 +6052,9 @@
       <c r="Z103" s="8"/>
       <c r="AA103" s="8"/>
       <c r="AB103" s="8"/>
-    </row>
-    <row r="104" spans="1:28">
+      <c r="AC103" s="8"/>
+    </row>
+    <row r="104" spans="1:29">
       <c r="A104" s="5" t="s">
         <v>106</v>
       </c>
@@ -5983,8 +6085,9 @@
       <c r="Z104" s="8"/>
       <c r="AA104" s="8"/>
       <c r="AB104" s="8"/>
-    </row>
-    <row r="105" spans="1:28">
+      <c r="AC104" s="8"/>
+    </row>
+    <row r="105" spans="1:29">
       <c r="A105" s="5" t="s">
         <v>107</v>
       </c>
@@ -6015,6 +6118,7 @@
       <c r="Z105" s="8"/>
       <c r="AA105" s="8"/>
       <c r="AB105" s="8"/>
+      <c r="AC105" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -6040,7 +6144,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A68D4BA7-81A7-496D-83F7-4CE2A3B40B1B}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="27.5546875" bestFit="1" customWidth="1"/>
@@ -6082,7 +6186,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6093,7 +6197,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -6108,7 +6212,7 @@
         <v>109</v>
       </c>
       <c r="H3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -6119,62 +6223,40 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="57.6">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="57.6">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>128</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>130</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
